--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -869,7 +869,7 @@
         <v>2.88</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 01:57:31</t>
+          <t>2026-06-21 04:10:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -869,7 +869,7 @@
         <v>2.88</v>
       </c>
       <c r="J2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
         <v>3.55</v>
@@ -890,7 +890,7 @@
         <v>1.56</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 04:10:10</t>
+          <t>2026-06-21 06:22:58</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 06:22:58</t>
+          <t>2026-06-21 08:35:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -866,7 +866,7 @@
         <v>2.6</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J2" t="n">
         <v>3</v>
@@ -887,7 +887,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q2" t="n">
         <v>2.48</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 08:35:54</t>
+          <t>2026-06-21 10:48:08</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,254 +833,1778 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>VPS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>AC Oulu</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="G2" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="J2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="X2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>13</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>11</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>15</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>7</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>21</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>24</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>25</v>
+      </c>
+      <c r="BW2" t="n">
+        <v>17</v>
+      </c>
+      <c r="BX2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BY2" t="n">
+        <v>26</v>
+      </c>
+      <c r="BZ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Lahti</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>TPS</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H3" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="K3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="X3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>42</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>16</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>29</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>8</v>
+      </c>
+      <c r="BU3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BV3" t="n">
+        <v>50</v>
+      </c>
+      <c r="BW3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BX3" t="n">
+        <v>65</v>
+      </c>
+      <c r="BY3" t="n">
+        <v>22</v>
+      </c>
+      <c r="BZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>4</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O4" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W4" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="X4" t="n">
+        <v>26</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>16</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FC Inter</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>HJK Helsinki</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="J7" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>Criciuma</t>
         </is>
       </c>
-      <c r="F2" t="n">
+      <c r="F8" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G8" t="n">
         <v>3.5</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H8" t="n">
         <v>2.6</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I8" t="n">
         <v>2.86</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J8" t="n">
         <v>3</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K8" t="n">
         <v>3.55</v>
       </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>0</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-21 10:48:08</t>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-21 12:58:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -860,13 +860,13 @@
         <v>2.48</v>
       </c>
       <c r="G2" t="n">
-        <v>2.86</v>
+        <v>2.76</v>
       </c>
       <c r="H2" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
@@ -875,7 +875,7 @@
         <v>3.75</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -884,34 +884,34 @@
         <v>3.5</v>
       </c>
       <c r="O2" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T2" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="U2" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="V2" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="X2" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y2" t="n">
         <v>14</v>
@@ -923,7 +923,7 @@
         <v>65</v>
       </c>
       <c r="AB2" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC2" t="n">
         <v>9.4</v>
@@ -971,10 +971,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -983,10 +983,10 @@
         <v>6.6</v>
       </c>
       <c r="AV2" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -998,16 +998,16 @@
         <v>14.5</v>
       </c>
       <c r="BA2" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB2" t="n">
         <v>3.95</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>3.9</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
       </c>
       <c r="BD2" t="n">
-        <v>3.95</v>
+        <v>34</v>
       </c>
       <c r="BE2" t="n">
         <v>4.1</v>
@@ -1016,28 +1016,28 @@
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.92</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>7</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO2" t="n">
         <v>4.2</v>
@@ -1046,13 +1046,13 @@
         <v>21</v>
       </c>
       <c r="BQ2" t="n">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
@@ -1064,13 +1064,13 @@
         <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>17</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>26</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1153,7 +1153,7 @@
         <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U3" t="n">
         <v>2.02</v>
@@ -1273,7 +1273,7 @@
         <v>4.9</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
         <v>3.05</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1306,7 +1306,7 @@
         <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>22</v>
+        <v>10.5</v>
       </c>
       <c r="BT3" t="n">
         <v>8</v>
@@ -1318,13 +1318,13 @@
         <v>50</v>
       </c>
       <c r="BW3" t="n">
-        <v>22</v>
+        <v>11.5</v>
       </c>
       <c r="BX3" t="n">
         <v>65</v>
       </c>
       <c r="BY3" t="n">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1365,19 +1365,19 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
         <v>1.75</v>
       </c>
       <c r="H4" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
         <v>5.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
         <v>4.5</v>
@@ -1407,10 +1407,10 @@
         <v>2.92</v>
       </c>
       <c r="T4" t="n">
-        <v>1.64</v>
+        <v>1.78</v>
       </c>
       <c r="U4" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1455,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AK4" t="n">
         <v>17.5</v>
@@ -1494,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1524,61 +1524,61 @@
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ4" t="n">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1637,16 +1637,16 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="P5" t="n">
         <v>2.24</v>
@@ -1655,184 +1655,184 @@
         <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BO5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BP5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BR5" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BS5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="BT5" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BX5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
@@ -1882,7 +1882,7 @@
         <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
@@ -1891,16 +1891,16 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
         <v>2.04</v>
@@ -1909,184 +1909,184 @@
         <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="BH6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BK6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BL6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP6" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="BR6" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BT6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="BV6" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="BX6" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="BY6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2145,16 +2145,16 @@
         <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="P7" t="n">
         <v>2.62</v>
@@ -2163,184 +2163,184 @@
         <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BL7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BN7" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="BP7" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BR7" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BT7" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BV7" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="BX7" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 12:58:40</t>
+          <t>2026-06-21 15:07:48</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -926,7 +926,7 @@
         <v>12.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
         <v>16.5</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AT2" t="n">
         <v>9</v>
@@ -986,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AX2" t="n">
         <v>12.5</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,19 +1010,19 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.92</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="H3" t="n">
         <v>4.5</v>
@@ -1138,13 +1138,13 @@
         <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P3" t="n">
         <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R3" t="n">
         <v>1.34</v>
@@ -1162,10 +1162,10 @@
         <v>1.25</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="X3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Y3" t="n">
         <v>18.5</v>
@@ -1225,7 +1225,7 @@
         <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AS3" t="n">
         <v>5</v>
@@ -1240,7 +1240,7 @@
         <v>14</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AX3" t="n">
         <v>9</v>
@@ -1261,7 +1261,7 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE3" t="n">
         <v>5</v>
@@ -1288,7 +1288,7 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1640,13 +1640,13 @@
         <v>1.01</v>
       </c>
       <c r="M5" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
         <v>2.24</v>
@@ -1673,112 +1673,112 @@
         <v>2.62</v>
       </c>
       <c r="X5" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="Y5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="Z5" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AB5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC5" t="n">
         <v>13</v>
       </c>
-      <c r="AC5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>32</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>100</v>
-      </c>
-      <c r="AF5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>28</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>90</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>18</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BD5" t="n">
-        <v>3.05</v>
+        <v>6.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.1</v>
+        <v>6.2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.3</v>
+        <v>8</v>
       </c>
       <c r="BH5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
         <v>2.38</v>
@@ -1894,31 +1894,31 @@
         <v>1.31</v>
       </c>
       <c r="M6" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O6" t="n">
         <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q6" t="n">
         <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>2.8</v>
+        <v>2.96</v>
       </c>
       <c r="T6" t="n">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="U6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="V6" t="n">
         <v>1.73</v>
@@ -1927,112 +1927,112 @@
         <v>1.4</v>
       </c>
       <c r="X6" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>29</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>36</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>80</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AX6" t="n">
         <v>20</v>
       </c>
-      <c r="AA6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>44</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AY6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.54</v>
+        <v>13.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.6</v>
+        <v>5.5</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.66</v>
+        <v>5.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.66</v>
+        <v>5.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.66</v>
+        <v>5.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.63</v>
+        <v>6</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.66</v>
+        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2145,7 +2145,7 @@
         <v>6.2</v>
       </c>
       <c r="L7" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
@@ -2166,13 +2166,13 @@
         <v>1.64</v>
       </c>
       <c r="S7" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7</v>
+        <v>1.81</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V7" t="n">
         <v>3.4</v>
@@ -2298,49 +2298,49 @@
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>8</v>
+        <v>5.2</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>21</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN7" t="n">
         <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>9</v>
+        <v>5.5</v>
       </c>
       <c r="BP7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BQ7" t="n">
-        <v>21</v>
+        <v>8.4</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>42</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
         <v>4.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="BV7" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.9</v>
+        <v>4.4</v>
       </c>
       <c r="BX7" t="n">
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>14.5</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>
@@ -2381,22 +2381,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="G8" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 15:07:48</t>
+          <t>2026-06-21 17:15:53</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>7.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
@@ -1058,7 +1058,7 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="BV2" t="n">
         <v>25</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
         <v>11.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH4" t="n">
         <v>28</v>
@@ -1473,7 +1473,7 @@
         <v>95</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ4" t="n">
         <v>17.5</v>
@@ -1482,7 +1482,7 @@
         <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT4" t="n">
         <v>8.6</v>
@@ -1494,7 +1494,7 @@
         <v>16</v>
       </c>
       <c r="AW4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1515,16 +1515,16 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
         <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
         <v>2</v>
@@ -2232,10 +2232,10 @@
         <v>160</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.7</v>
+        <v>5.1</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>20</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.199999999999999</v>
@@ -2247,7 +2247,7 @@
         <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -2259,34 +2259,34 @@
         <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="AZ7" t="n">
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
       <c r="BB7" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BH7" t="n">
         <v>4.8</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 17:15:53</t>
+          <t>2026-06-21 19:23:02</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="G3" t="n">
         <v>1.97</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
@@ -1891,7 +1891,7 @@
         <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.96</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -2399,212 +2399,212 @@
         <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="P8" t="n">
         <v>1.56</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BH8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="BL8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="BO8" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BP8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BR8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT8" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BU8" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="BV8" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BX8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 19:23:02</t>
+          <t>2026-06-21 21:30:01</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -890,25 +890,25 @@
         <v>1.84</v>
       </c>
       <c r="Q2" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R2" t="n">
         <v>1.33</v>
       </c>
       <c r="S2" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="T2" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="X2" t="n">
         <v>16</v>
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
@@ -1040,7 +1040,7 @@
         <v>5.7</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BP2" t="n">
         <v>21</v>
@@ -1058,7 +1058,7 @@
         <v>6.4</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="BV2" t="n">
         <v>25</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G3" t="n">
         <v>1.97</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
         <v>6.4</v>
       </c>
       <c r="I5" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J5" t="n">
         <v>4.4</v>
@@ -1643,7 +1643,7 @@
         <v>1.05</v>
       </c>
       <c r="N5" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="O5" t="n">
         <v>1.23</v>
@@ -1667,7 +1667,7 @@
         <v>2.04</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
         <v>2.62</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
@@ -2056,7 +2056,7 @@
         <v>9.6</v>
       </c>
       <c r="BO6" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP6" t="n">
         <v>36</v>
@@ -2074,7 +2074,7 @@
         <v>7.6</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV6" t="n">
         <v>23</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2133,10 +2133,10 @@
         <v>10.5</v>
       </c>
       <c r="H7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="I7" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="J7" t="n">
         <v>5.5</v>
@@ -2175,10 +2175,10 @@
         <v>2</v>
       </c>
       <c r="V7" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="X7" t="n">
         <v>29</v>
@@ -2187,7 +2187,7 @@
         <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AA7" t="n">
         <v>14.5</v>
@@ -2247,7 +2247,7 @@
         <v>10</v>
       </c>
       <c r="AT7" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="AU7" t="n">
         <v>11</v>
@@ -2259,31 +2259,31 @@
         <v>12</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AY7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AZ7" t="n">
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB7" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="BG7" t="n">
         <v>4.2</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>
@@ -2384,13 +2384,13 @@
         <v>2.96</v>
       </c>
       <c r="G8" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
@@ -2411,16 +2411,16 @@
         <v>1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R8" t="n">
         <v>1.21</v>
       </c>
       <c r="S8" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="T8" t="n">
         <v>2.02</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 21:30:01</t>
+          <t>2026-06-21 23:36:59</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -860,94 +860,94 @@
         <v>2.52</v>
       </c>
       <c r="G2" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="H2" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="I2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R2" t="n">
         <v>1.34</v>
       </c>
-      <c r="P2" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.33</v>
-      </c>
       <c r="S2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="T2" t="n">
         <v>1.79</v>
       </c>
       <c r="U2" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="X2" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="Y2" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z2" t="n">
         <v>25</v>
       </c>
       <c r="AA2" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB2" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AC2" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AK2" t="n">
         <v>36</v>
@@ -959,49 +959,49 @@
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO2" t="n">
         <v>42</v>
       </c>
       <c r="AP2" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AR2" t="n">
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW2" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,19 +1010,19 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
         <v>5.7</v>
@@ -1049,7 +1049,7 @@
         <v>7</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
         <v>8</v>
@@ -1067,7 +1067,7 @@
         <v>7.4</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY2" t="n">
         <v>8.199999999999999</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1111,10 +1111,10 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="G3" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="H3" t="n">
         <v>4.5</v>
@@ -1123,19 +1123,19 @@
         <v>4.9</v>
       </c>
       <c r="J3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
         <v>1.34</v>
@@ -1144,25 +1144,25 @@
         <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T3" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X3" t="n">
         <v>16</v>
@@ -1171,10 +1171,10 @@
         <v>18.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB3" t="n">
         <v>10</v>
@@ -1183,7 +1183,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
@@ -1219,40 +1219,40 @@
         <v>85</v>
       </c>
       <c r="AP3" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="AS3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AX3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY3" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1261,25 +1261,25 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="BF3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ3" t="n">
         <v>10.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>10</v>
       </c>
       <c r="BK3" t="n">
         <v>7.8</v>
@@ -1297,10 +1297,10 @@
         <v>4.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BU3" t="n">
         <v>6.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I4" t="n">
         <v>5.7</v>
@@ -1383,43 +1383,43 @@
         <v>4.5</v>
       </c>
       <c r="L4" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="X4" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="Y4" t="n">
         <v>29</v>
@@ -1434,7 +1434,7 @@
         <v>9.6</v>
       </c>
       <c r="AC4" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>30</v>
@@ -1443,7 +1443,7 @@
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
@@ -1455,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
         <v>17.5</v>
@@ -1467,13 +1467,13 @@
         <v>120</v>
       </c>
       <c r="AN4" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="AQ4" t="n">
         <v>17.5</v>
@@ -1482,7 +1482,7 @@
         <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT4" t="n">
         <v>8.6</v>
@@ -1491,10 +1491,10 @@
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
@@ -1506,7 +1506,7 @@
         <v>17</v>
       </c>
       <c r="BA4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1515,22 +1515,22 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BE4" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
@@ -1551,7 +1551,7 @@
         <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ4" t="n">
         <v>8.6</v>
@@ -1563,19 +1563,19 @@
         <v>9.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU4" t="n">
         <v>6.8</v>
       </c>
       <c r="BV4" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BY4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1646,28 +1646,28 @@
         <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q5" t="n">
         <v>1.68</v>
       </c>
       <c r="R5" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="S5" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="T5" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="U5" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W5" t="n">
         <v>2.62</v>
@@ -1697,7 +1697,7 @@
         <v>90</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AG5" t="n">
         <v>10.5</v>
@@ -1721,7 +1721,7 @@
         <v>120</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AO5" t="n">
         <v>110</v>
@@ -1733,34 +1733,34 @@
         <v>20</v>
       </c>
       <c r="AR5" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU5" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV5" t="n">
         <v>20</v>
       </c>
       <c r="AW5" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ5" t="n">
         <v>17.5</v>
       </c>
       <c r="BA5" t="n">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
         <v>12.5</v>
@@ -1769,70 +1769,70 @@
         <v>13</v>
       </c>
       <c r="BD5" t="n">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="BE5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.77</v>
+        <v>7.8</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN5" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3</v>
+        <v>3.45</v>
       </c>
       <c r="BP5" t="n">
-        <v>13.5</v>
+        <v>10</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.75</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.89</v>
+        <v>7</v>
       </c>
       <c r="BT5" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.75</v>
+        <v>7.8</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.96</v>
+        <v>8.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.96</v>
+        <v>8.4</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L6" t="n">
         <v>1.31</v>
@@ -1897,40 +1897,40 @@
         <v>1.06</v>
       </c>
       <c r="N6" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P6" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q6" t="n">
         <v>1.8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="U6" t="n">
         <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
         <v>18</v>
       </c>
       <c r="Y6" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Z6" t="n">
         <v>16.5</v>
@@ -1942,13 +1942,13 @@
         <v>15.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AE6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF6" t="n">
         <v>30</v>
@@ -1984,22 +1984,22 @@
         <v>14.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AR6" t="n">
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="AT6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU6" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AV6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
         <v>19.5</v>
@@ -2008,31 +2008,31 @@
         <v>20</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG6" t="n">
         <v>13.5</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>6</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>11.5</v>
       </c>
       <c r="BH6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2157,7 +2157,7 @@
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
         <v>1.54</v>
@@ -2289,58 +2289,58 @@
         <v>4.2</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN7" t="n">
         <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BP7" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BV7" t="n">
         <v>8.4</v>
       </c>
-      <c r="BT7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>8.199999999999999</v>
-      </c>
       <c r="BW7" t="n">
-        <v>4.4</v>
+        <v>6</v>
       </c>
       <c r="BX7" t="n">
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="G8" t="n">
         <v>3.45</v>
@@ -2390,157 +2390,157 @@
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="Q8" t="n">
         <v>2.52</v>
       </c>
       <c r="R8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
         <v>5.3</v>
       </c>
       <c r="T8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="W8" t="n">
         <v>1.41</v>
       </c>
       <c r="X8" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AB8" t="n">
         <v>10.5</v>
       </c>
-      <c r="Y8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1000</v>
-      </c>
       <c r="AC8" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF8" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG8" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH8" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AJ8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK8" t="n">
         <v>55</v>
       </c>
       <c r="AL8" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN8" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO8" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.15</v>
+        <v>7.6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.12</v>
+        <v>7.2</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.29</v>
+        <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>1.29</v>
+        <v>5.8</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.29</v>
+        <v>8</v>
       </c>
       <c r="AU8" t="n">
-        <v>1.29</v>
+        <v>6.2</v>
       </c>
       <c r="AV8" t="n">
-        <v>1.29</v>
+        <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="AX8" t="n">
-        <v>1.29</v>
+        <v>17</v>
       </c>
       <c r="AY8" t="n">
-        <v>1.29</v>
+        <v>12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>1.29</v>
+        <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>1.29</v>
+        <v>5.9</v>
       </c>
       <c r="BC8" t="n">
-        <v>1.26</v>
+        <v>5.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>1.29</v>
+        <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.29</v>
+        <v>6.2</v>
       </c>
       <c r="BF8" t="n">
-        <v>1.29</v>
+        <v>5.9</v>
       </c>
       <c r="BG8" t="n">
-        <v>1.29</v>
+        <v>5.7</v>
       </c>
       <c r="BH8" t="n">
         <v>3.1</v>
@@ -2558,10 +2558,10 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BO8" t="n">
         <v>4.3</v>
@@ -2570,13 +2570,13 @@
         <v>38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="BR8" t="n">
         <v>1000</v>
       </c>
       <c r="BS8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BT8" t="n">
         <v>7</v>
@@ -2588,23 +2588,23 @@
         <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BX8" t="n">
         <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BZ8" t="n">
         <v>1000</v>
       </c>
       <c r="CA8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-21 23:36:59</t>
+          <t>2026-06-22 01:44:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="G2" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="H2" t="n">
         <v>2.98</v>
@@ -881,10 +881,10 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
         <v>1.87</v>
@@ -908,7 +908,7 @@
         <v>1.46</v>
       </c>
       <c r="W2" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
@@ -962,7 +962,7 @@
         <v>30</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AP2" t="n">
         <v>11.5</v>
@@ -983,7 +983,7 @@
         <v>7</v>
       </c>
       <c r="AV2" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AW2" t="n">
         <v>6.4</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,7 +1010,7 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
@@ -1019,7 +1019,7 @@
         <v>6.4</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI2" t="n">
         <v>2.66</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BN2" t="n">
         <v>5.7</v>
@@ -1049,10 +1049,10 @@
         <v>7</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT2" t="n">
         <v>6.4</v>
@@ -1064,13 +1064,13 @@
         <v>25</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX2" t="n">
         <v>38</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1111,13 +1111,13 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="G3" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="H3" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I3" t="n">
         <v>4.9</v>
@@ -1129,7 +1129,7 @@
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
@@ -1156,10 +1156,10 @@
         <v>1.87</v>
       </c>
       <c r="U3" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="W3" t="n">
         <v>2.04</v>
@@ -1273,13 +1273,13 @@
         <v>5.1</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BI3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK3" t="n">
         <v>7.8</v>
@@ -1297,10 +1297,10 @@
         <v>4.1</v>
       </c>
       <c r="BP3" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BR3" t="n">
         <v>29</v>
@@ -1309,7 +1309,7 @@
         <v>10.5</v>
       </c>
       <c r="BT3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BU3" t="n">
         <v>6.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1368,10 +1368,10 @@
         <v>1.68</v>
       </c>
       <c r="G4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H4" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="I4" t="n">
         <v>5.7</v>
@@ -1410,13 +1410,13 @@
         <v>1.8</v>
       </c>
       <c r="U4" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
       </c>
       <c r="W4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X4" t="n">
         <v>20</v>
@@ -1473,7 +1473,7 @@
         <v>70</v>
       </c>
       <c r="AP4" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
         <v>17.5</v>
@@ -1530,7 +1530,7 @@
         <v>3.85</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ4" t="n">
         <v>9.800000000000001</v>
@@ -1551,10 +1551,10 @@
         <v>4</v>
       </c>
       <c r="BP4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>8.6</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>24</v>
@@ -1563,19 +1563,19 @@
         <v>9.4</v>
       </c>
       <c r="BT4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU4" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV4" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX4" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="BY4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1667,7 +1667,7 @@
         <v>2.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
         <v>2.62</v>
@@ -1763,7 +1763,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BB5" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BC5" t="n">
         <v>13</v>
@@ -1787,7 +1787,7 @@
         <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK5" t="n">
         <v>7.8</v>
@@ -1802,13 +1802,13 @@
         <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>5.1</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
@@ -1820,7 +1820,7 @@
         <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV5" t="n">
         <v>55</v>
@@ -1829,7 +1829,7 @@
         <v>8.4</v>
       </c>
       <c r="BX5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY5" t="n">
         <v>8.4</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -1873,13 +1873,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="G6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="I6" t="n">
         <v>2.34</v>
@@ -1891,7 +1891,7 @@
         <v>3.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="M6" t="n">
         <v>1.06</v>
@@ -1921,10 +1921,10 @@
         <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="W6" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="X6" t="n">
         <v>18</v>
@@ -2035,58 +2035,58 @@
         <v>13.5</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>1.85</v>
+        <v>2.94</v>
       </c>
       <c r="BJ6" t="n">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.62</v>
+        <v>6.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.85</v>
+        <v>9.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>9.6</v>
+        <v>7</v>
       </c>
       <c r="BO6" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU6" t="n">
         <v>4.5</v>
       </c>
-      <c r="BP6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>50</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="BT6" t="n">
+      <c r="BV6" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>28</v>
+      </c>
+      <c r="BY6" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>23</v>
-      </c>
-      <c r="BW6" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="BX6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BY6" t="n">
-        <v>1.77</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="H7" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="J7" t="n">
         <v>5.5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L7" t="n">
         <v>1.23</v>
@@ -2157,28 +2157,28 @@
         <v>1.18</v>
       </c>
       <c r="P7" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R7" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="S7" t="n">
         <v>2.3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V7" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="X7" t="n">
         <v>29</v>
@@ -2187,25 +2187,25 @@
         <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AC7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AE7" t="n">
         <v>15</v>
       </c>
       <c r="AF7" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AG7" t="n">
         <v>36</v>
@@ -2217,7 +2217,7 @@
         <v>34</v>
       </c>
       <c r="AJ7" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AK7" t="n">
         <v>150</v>
@@ -2229,106 +2229,106 @@
         <v>140</v>
       </c>
       <c r="AN7" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AP7" t="n">
         <v>20</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AS7" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.3</v>
+        <v>7.2</v>
       </c>
       <c r="AU7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV7" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
       <c r="AZ7" t="n">
         <v>20</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BE7" t="n">
-        <v>5.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BN7" t="n">
         <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BQ7" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BV7" t="n">
         <v>8.4</v>
@@ -2340,7 +2340,7 @@
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>
@@ -2384,34 +2384,34 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="H8" t="n">
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.92</v>
+        <v>2.82</v>
       </c>
       <c r="J8" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
         <v>3.3</v>
       </c>
       <c r="L8" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="O8" t="n">
         <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="Q8" t="n">
         <v>2.52</v>
@@ -2420,19 +2420,19 @@
         <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T8" t="n">
         <v>2.04</v>
       </c>
       <c r="U8" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="W8" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X8" t="n">
         <v>9.199999999999999</v>
@@ -2453,10 +2453,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD8" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
         <v>23</v>
@@ -2489,7 +2489,7 @@
         <v>50</v>
       </c>
       <c r="AP8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AQ8" t="n">
         <v>7.2</v>
@@ -2498,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT8" t="n">
         <v>8</v>
@@ -2525,86 +2525,86 @@
         <v>6</v>
       </c>
       <c r="BB8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BD8" t="n">
         <v>6</v>
       </c>
       <c r="BE8" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF8" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG8" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.1</v>
+        <v>2.76</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>4.4</v>
+        <v>14</v>
       </c>
       <c r="BN8" t="n">
-        <v>7.4</v>
+        <v>6.2</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP8" t="n">
         <v>38</v>
       </c>
       <c r="BQ8" t="n">
-        <v>3.95</v>
+        <v>10</v>
       </c>
       <c r="BR8" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BS8" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BT8" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="BU8" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="BV8" t="n">
         <v>32</v>
       </c>
       <c r="BW8" t="n">
-        <v>3.9</v>
+        <v>9.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BY8" t="n">
-        <v>4.1</v>
+        <v>11</v>
       </c>
       <c r="BZ8" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="CA8" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 01:44:00</t>
+          <t>2026-06-22 03:51:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,16 +857,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="G2" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
       <c r="H2" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="I2" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
@@ -875,7 +875,7 @@
         <v>3.55</v>
       </c>
       <c r="L2" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.07</v>
@@ -905,10 +905,10 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.59</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
         <v>13.5</v>
@@ -935,7 +935,7 @@
         <v>44</v>
       </c>
       <c r="AF2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -947,19 +947,19 @@
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AK2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL2" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM2" t="n">
         <v>120</v>
       </c>
       <c r="AN2" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AO2" t="n">
         <v>40</v>
@@ -974,7 +974,7 @@
         <v>17.5</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -986,7 +986,7 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>14.5</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC2" t="n">
         <v>21</v>
@@ -1010,64 +1010,64 @@
         <v>34</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF2" t="n">
         <v>18</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="BJ2" t="n">
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BP2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BV2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BW2" t="n">
         <v>7.6</v>
       </c>
       <c r="BX2" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BY2" t="n">
         <v>8.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1401,7 +1401,7 @@
         <v>1.77</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S4" t="n">
         <v>2.94</v>
@@ -1455,7 +1455,7 @@
         <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK4" t="n">
         <v>17.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1619,7 +1619,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
         <v>1.61</v>
@@ -1637,7 +1637,7 @@
         <v>4.8</v>
       </c>
       <c r="L5" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="M5" t="n">
         <v>1.05</v>
@@ -1775,7 +1775,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG5" t="n">
         <v>9.199999999999999</v>
@@ -1790,7 +1790,7 @@
         <v>10.5</v>
       </c>
       <c r="BK5" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
@@ -1802,7 +1802,7 @@
         <v>4.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="BP5" t="n">
         <v>10.5</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -1873,16 +1873,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="G6" t="n">
         <v>3.5</v>
       </c>
       <c r="H6" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
@@ -1921,7 +1921,7 @@
         <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W6" t="n">
         <v>1.4</v>
@@ -2044,7 +2044,7 @@
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
         <v>110</v>
@@ -2056,7 +2056,7 @@
         <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="BP6" t="n">
         <v>26</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2130,22 +2130,22 @@
         <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="H7" t="n">
         <v>1.38</v>
       </c>
       <c r="I7" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J7" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K7" t="n">
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
@@ -2154,31 +2154,31 @@
         <v>5.7</v>
       </c>
       <c r="O7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P7" t="n">
         <v>2.64</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
         <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V7" t="n">
         <v>3.4</v>
       </c>
       <c r="W7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X7" t="n">
         <v>29</v>
@@ -2193,7 +2193,7 @@
         <v>13</v>
       </c>
       <c r="AB7" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="AC7" t="n">
         <v>13.5</v>
@@ -2208,13 +2208,13 @@
         <v>100</v>
       </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="n">
         <v>330</v>
@@ -2223,7 +2223,7 @@
         <v>150</v>
       </c>
       <c r="AL7" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
         <v>140</v>
@@ -2235,7 +2235,7 @@
         <v>4.9</v>
       </c>
       <c r="AP7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ7" t="n">
         <v>9.800000000000001</v>
@@ -2247,7 +2247,7 @@
         <v>10.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.2</v>
+        <v>21</v>
       </c>
       <c r="AU7" t="n">
         <v>12</v>
@@ -2259,31 +2259,31 @@
         <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="AY7" t="n">
-        <v>7</v>
+        <v>19.5</v>
       </c>
       <c r="AZ7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA7" t="n">
         <v>20</v>
       </c>
-      <c r="BA7" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BB7" t="n">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="BE7" t="n">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>7.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG7" t="n">
         <v>4.5</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>
@@ -2408,7 +2408,7 @@
         <v>2.8</v>
       </c>
       <c r="O8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
         <v>1.61</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 03:51:04</t>
+          <t>2026-06-22 05:58:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="G2" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="H2" t="n">
         <v>3.1</v>
@@ -872,7 +872,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -881,13 +881,13 @@
         <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="O2" t="n">
         <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Q2" t="n">
         <v>2.02</v>
@@ -908,16 +908,16 @@
         <v>1.43</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="X2" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y2" t="n">
         <v>12.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AA2" t="n">
         <v>55</v>
@@ -926,13 +926,13 @@
         <v>11</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AD2" t="n">
         <v>14</v>
       </c>
       <c r="AE2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AF2" t="n">
         <v>16</v>
@@ -941,13 +941,13 @@
         <v>12</v>
       </c>
       <c r="AH2" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI2" t="n">
         <v>60</v>
       </c>
       <c r="AJ2" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AK2" t="n">
         <v>34</v>
@@ -962,7 +962,7 @@
         <v>28</v>
       </c>
       <c r="AO2" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AP2" t="n">
         <v>11.5</v>
@@ -971,10 +971,10 @@
         <v>10.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
         <v>9.4</v>
@@ -986,37 +986,37 @@
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AX2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AY2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BA2" t="n">
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1028,13 +1028,13 @@
         <v>10</v>
       </c>
       <c r="BK2" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BN2" t="n">
         <v>5.6</v>
@@ -1049,7 +1049,7 @@
         <v>6.8</v>
       </c>
       <c r="BR2" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS2" t="n">
         <v>8</v>
@@ -1064,13 +1064,13 @@
         <v>27</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX2" t="n">
         <v>40</v>
       </c>
       <c r="BY2" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1135,16 +1135,16 @@
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O3" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P3" t="n">
         <v>1.94</v>
       </c>
       <c r="Q3" t="n">
-        <v>2</v>
+        <v>1.54</v>
       </c>
       <c r="R3" t="n">
         <v>1.35</v>
@@ -1174,16 +1174,16 @@
         <v>38</v>
       </c>
       <c r="AA3" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB3" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC3" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AE3" t="n">
         <v>75</v>
@@ -1225,10 +1225,10 @@
         <v>14</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AS3" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AT3" t="n">
         <v>7.8</v>
@@ -1240,7 +1240,7 @@
         <v>16.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
         <v>10</v>
@@ -1252,7 +1252,7 @@
         <v>17</v>
       </c>
       <c r="BA3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB3" t="n">
         <v>18</v>
@@ -1261,19 +1261,19 @@
         <v>18</v>
       </c>
       <c r="BD3" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BE3" t="n">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF3" t="n">
         <v>12.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BI3" t="n">
         <v>3.05</v>
@@ -1282,13 +1282,13 @@
         <v>10</v>
       </c>
       <c r="BK3" t="n">
-        <v>7.8</v>
+        <v>6</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BN3" t="n">
         <v>4.6</v>
@@ -1306,25 +1306,25 @@
         <v>29</v>
       </c>
       <c r="BS3" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>8</v>
       </c>
       <c r="BU3" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="BV3" t="n">
         <v>50</v>
       </c>
       <c r="BW3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX3" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1380,10 +1380,10 @@
         <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="M4" t="n">
         <v>1.05</v>
@@ -1395,22 +1395,22 @@
         <v>1.26</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S4" t="n">
         <v>2.94</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1419,10 +1419,10 @@
         <v>2.34</v>
       </c>
       <c r="X4" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z4" t="n">
         <v>60</v>
@@ -1431,10 +1431,10 @@
         <v>160</v>
       </c>
       <c r="AB4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC4" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>30</v>
@@ -1443,22 +1443,22 @@
         <v>95</v>
       </c>
       <c r="AF4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG4" t="n">
         <v>10</v>
       </c>
       <c r="AH4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>90</v>
       </c>
       <c r="AJ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AK4" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL4" t="n">
         <v>44</v>
@@ -1470,19 +1470,19 @@
         <v>9</v>
       </c>
       <c r="AO4" t="n">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
         <v>16.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AR4" t="n">
         <v>34</v>
       </c>
       <c r="AS4" t="n">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AT4" t="n">
         <v>8.6</v>
@@ -1491,22 +1491,22 @@
         <v>8.6</v>
       </c>
       <c r="AV4" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AX4" t="n">
         <v>10</v>
       </c>
       <c r="AY4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BB4" t="n">
         <v>15.5</v>
@@ -1515,16 +1515,16 @@
         <v>15</v>
       </c>
       <c r="BD4" t="n">
-        <v>10.5</v>
+        <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
@@ -1536,7 +1536,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="G5" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I5" t="n">
         <v>7</v>
       </c>
       <c r="J5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K5" t="n">
         <v>4.8</v>
@@ -1646,37 +1646,37 @@
         <v>4.7</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="R5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S5" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="T5" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V5" t="n">
         <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y5" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="Z5" t="n">
         <v>60</v>
@@ -1688,13 +1688,13 @@
         <v>10.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD5" t="n">
         <v>26</v>
       </c>
       <c r="AE5" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF5" t="n">
         <v>10.5</v>
@@ -1706,13 +1706,13 @@
         <v>22</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AK5" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AL5" t="n">
         <v>34</v>
@@ -1727,58 +1727,58 @@
         <v>110</v>
       </c>
       <c r="AP5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AR5" t="n">
-        <v>8.6</v>
+        <v>42</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AT5" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU5" t="n">
         <v>9.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="AX5" t="n">
         <v>9</v>
       </c>
       <c r="AY5" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
-        <v>8.800000000000001</v>
+        <v>34</v>
       </c>
       <c r="BB5" t="n">
         <v>13</v>
       </c>
       <c r="BC5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BD5" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="BE5" t="n">
-        <v>9.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>9.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="BH5" t="n">
         <v>4.2</v>
@@ -1808,7 +1808,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.1</v>
+        <v>7.4</v>
       </c>
       <c r="BR5" t="n">
         <v>24</v>
@@ -1820,7 +1820,7 @@
         <v>10.5</v>
       </c>
       <c r="BU5" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BV5" t="n">
         <v>55</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -1876,19 +1876,19 @@
         <v>3.35</v>
       </c>
       <c r="G6" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="H6" t="n">
         <v>2.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L6" t="n">
         <v>1.3</v>
@@ -1900,16 +1900,16 @@
         <v>4.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P6" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="R6" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1921,25 +1921,25 @@
         <v>2.28</v>
       </c>
       <c r="V6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="X6" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Z6" t="n">
         <v>16.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AB6" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AC6" t="n">
         <v>8.800000000000001</v>
@@ -1951,34 +1951,34 @@
         <v>28</v>
       </c>
       <c r="AF6" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG6" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AH6" t="n">
         <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ6" t="n">
         <v>70</v>
       </c>
       <c r="AK6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AL6" t="n">
         <v>55</v>
       </c>
       <c r="AM6" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="AN6" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AO6" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AP6" t="n">
         <v>14.5</v>
@@ -1990,7 +1990,7 @@
         <v>13</v>
       </c>
       <c r="AS6" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="AT6" t="n">
         <v>13</v>
@@ -2002,52 +2002,52 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW6" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AY6" t="n">
         <v>12.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA6" t="n">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>6.6</v>
+        <v>4.9</v>
       </c>
       <c r="BC6" t="n">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="BD6" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>6.8</v>
+        <v>4.9</v>
       </c>
       <c r="BF6" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH6" t="n">
         <v>3.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.4</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL6" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM6" t="n">
         <v>9.6</v>
@@ -2056,7 +2056,7 @@
         <v>7</v>
       </c>
       <c r="BO6" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="BP6" t="n">
         <v>26</v>
@@ -2074,7 +2074,7 @@
         <v>5.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BV6" t="n">
         <v>16.5</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
         <v>8.6</v>
       </c>
       <c r="G7" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.38</v>
@@ -2145,34 +2145,34 @@
         <v>6</v>
       </c>
       <c r="L7" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="M7" t="n">
         <v>1.03</v>
       </c>
       <c r="N7" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="O7" t="n">
         <v>1.19</v>
       </c>
       <c r="P7" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
         <v>1.65</v>
       </c>
       <c r="S7" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V7" t="n">
         <v>3.4</v>
@@ -2181,16 +2181,16 @@
         <v>1.12</v>
       </c>
       <c r="X7" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="Y7" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB7" t="n">
         <v>36</v>
@@ -2199,13 +2199,13 @@
         <v>13.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
         <v>34</v>
@@ -2238,19 +2238,19 @@
         <v>21</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AV7" t="n">
         <v>9.4</v>
@@ -2259,10 +2259,10 @@
         <v>12.5</v>
       </c>
       <c r="AX7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AZ7" t="n">
         <v>21</v>
@@ -2271,58 +2271,58 @@
         <v>20</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.800000000000001</v>
+        <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BE7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BF7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BJ7" t="n">
         <v>11.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BN7" t="n">
         <v>13</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="BP7" t="n">
         <v>70</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BR7" t="n">
         <v>65</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT7" t="n">
         <v>4.3</v>
@@ -2340,7 +2340,7 @@
         <v>22</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2381,7 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="G8" t="n">
         <v>3.4</v>
@@ -2390,31 +2390,31 @@
         <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="M8" t="n">
         <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="O8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P8" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R8" t="n">
         <v>1.2</v>
@@ -2423,13 +2423,13 @@
         <v>5.2</v>
       </c>
       <c r="T8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
         <v>1.81</v>
       </c>
       <c r="V8" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W8" t="n">
         <v>1.42</v>
@@ -2441,13 +2441,13 @@
         <v>8.4</v>
       </c>
       <c r="Z8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB8" t="n">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC8" t="n">
         <v>8.199999999999999</v>
@@ -2468,7 +2468,7 @@
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AJ8" t="n">
         <v>70</v>
@@ -2480,13 +2480,13 @@
         <v>80</v>
       </c>
       <c r="AM8" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN8" t="n">
         <v>70</v>
       </c>
       <c r="AO8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AP8" t="n">
         <v>8</v>
@@ -2498,7 +2498,7 @@
         <v>14</v>
       </c>
       <c r="AS8" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="AT8" t="n">
         <v>8</v>
@@ -2510,7 +2510,7 @@
         <v>11</v>
       </c>
       <c r="AW8" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AX8" t="n">
         <v>17</v>
@@ -2522,37 +2522,37 @@
         <v>18.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BB8" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BC8" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD8" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BE8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BG8" t="n">
         <v>6.4</v>
       </c>
-      <c r="BF8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>5.8</v>
-      </c>
       <c r="BH8" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="BI8" t="n">
         <v>2.5</v>
       </c>
       <c r="BJ8" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK8" t="n">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="BR8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS8" t="n">
         <v>11.5</v>
@@ -2585,7 +2585,7 @@
         <v>4.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
         <v>9.4</v>
@@ -2597,14 +2597,14 @@
         <v>11</v>
       </c>
       <c r="BZ8" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA8" t="n">
         <v>11.5</v>
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 05:58:29</t>
+          <t>2026-06-22 08:05:29</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB8"/>
+  <dimension ref="A1:CB10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -863,7 +863,7 @@
         <v>2.58</v>
       </c>
       <c r="H2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I2" t="n">
         <v>3.3</v>
@@ -872,7 +872,7 @@
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L2" t="n">
         <v>1.42</v>
@@ -905,10 +905,10 @@
         <v>2.16</v>
       </c>
       <c r="V2" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X2" t="n">
         <v>14</v>
@@ -935,7 +935,7 @@
         <v>46</v>
       </c>
       <c r="AF2" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG2" t="n">
         <v>12</v>
@@ -980,13 +980,13 @@
         <v>9.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AX2" t="n">
         <v>14</v>
@@ -1001,7 +1001,7 @@
         <v>36</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BC2" t="n">
         <v>20</v>
@@ -1016,7 +1016,7 @@
         <v>19.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.4</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1111,220 +1111,220 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>1.96</v>
+        <v>1.85</v>
       </c>
       <c r="H3" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="I3" t="n">
-        <v>4.9</v>
+        <v>5.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
         <v>3.85</v>
       </c>
       <c r="L3" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="M3" t="n">
         <v>1.07</v>
       </c>
       <c r="N3" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P3" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.54</v>
+        <v>1.96</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S3" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="T3" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U3" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="W3" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="X3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="Y3" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="AA3" t="n">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AE3" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AG3" t="n">
         <v>12</v>
       </c>
       <c r="AH3" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK3" t="n">
         <v>23</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>25</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>24</v>
       </c>
       <c r="AL3" t="n">
         <v>44</v>
       </c>
       <c r="AM3" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN3" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW3" t="n">
         <v>6.2</v>
       </c>
-      <c r="AT3" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5.9</v>
-      </c>
       <c r="AX3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AY3" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ3" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BC3" t="n">
         <v>17</v>
       </c>
-      <c r="BA3" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>18</v>
-      </c>
       <c r="BD3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="BH3" t="n">
         <v>3.4</v>
       </c>
       <c r="BI3" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ3" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="BP3" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BS3" t="n">
         <v>10</v>
       </c>
       <c r="BT3" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BV3" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BZ3" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G4" t="n">
         <v>1.74</v>
@@ -1389,7 +1389,7 @@
         <v>1.05</v>
       </c>
       <c r="N4" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="O4" t="n">
         <v>1.26</v>
@@ -1398,10 +1398,10 @@
         <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R4" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
         <v>2.94</v>
@@ -1410,7 +1410,7 @@
         <v>1.76</v>
       </c>
       <c r="U4" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="V4" t="n">
         <v>1.21</v>
@@ -1473,19 +1473,19 @@
         <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="AS4" t="n">
         <v>12</v>
       </c>
       <c r="AT4" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU4" t="n">
         <v>8.6</v>
@@ -1518,13 +1518,13 @@
         <v>23</v>
       </c>
       <c r="BE4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BF4" t="n">
         <v>8</v>
       </c>
       <c r="BG4" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH4" t="n">
         <v>3.85</v>
@@ -1588,14 +1588,14 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Georgian Umaglesi Liga</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,244 +1605,244 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>FC Iberia 1999</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>FC Meshakhte Tkibuli</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.55</v>
+        <v>1.15</v>
       </c>
       <c r="G5" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>950</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N5" t="n">
         <v>1.6</v>
       </c>
-      <c r="H5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7</v>
-      </c>
-      <c r="J5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N5" t="n">
-        <v>4.7</v>
-      </c>
       <c r="O5" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P5" t="n">
-        <v>2.28</v>
+        <v>1.07</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.71</v>
+        <v>1.24</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5</v>
+        <v>1.07</v>
       </c>
       <c r="S5" t="n">
-        <v>2.76</v>
+        <v>1.24</v>
       </c>
       <c r="T5" t="n">
-        <v>1.82</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.01</v>
       </c>
       <c r="W5" t="n">
-        <v>2.66</v>
+        <v>1.61</v>
       </c>
       <c r="X5" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
         <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>42</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>9.4</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>9</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>27</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>1.01</v>
       </c>
       <c r="BJ5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
-        <v>3.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR5" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU5" t="n">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV5" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -1864,229 +1864,229 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>FC Inter</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.35</v>
+        <v>1.56</v>
       </c>
       <c r="G6" t="n">
-        <v>3.55</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3</v>
+        <v>7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.85</v>
+        <v>4.8</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="M6" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N6" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X6" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH6" t="n">
         <v>4.2</v>
       </c>
-      <c r="O6" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="P6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S6" t="n">
-        <v>3</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="X6" t="n">
-        <v>22</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>36</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>40</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>70</v>
-      </c>
-      <c r="AK6" t="n">
-        <v>46</v>
-      </c>
-      <c r="AL6" t="n">
+      <c r="BI6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BV6" t="n">
         <v>55</v>
       </c>
-      <c r="AM6" t="n">
-        <v>95</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO6" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AP6" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AQ6" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AT6" t="n">
-        <v>13</v>
-      </c>
-      <c r="AU6" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>19</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>13</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI6" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="BJ6" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BK6" t="n">
-        <v>5</v>
-      </c>
-      <c r="BL6" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM6" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BN6" t="n">
-        <v>7</v>
-      </c>
-      <c r="BO6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BP6" t="n">
-        <v>26</v>
-      </c>
-      <c r="BQ6" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BR6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BS6" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BT6" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU6" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV6" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BW6" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="BX6" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
@@ -2113,192 +2113,192 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>8.6</v>
+        <v>3.35</v>
       </c>
       <c r="G7" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="S7" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X7" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>19</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>21</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ7" t="n">
         <v>9.4</v>
       </c>
-      <c r="H7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="K7" t="n">
-        <v>6</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="U7" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X7" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>34</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>32</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>330</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>11</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>12</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>11</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>11.5</v>
-      </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>6.6</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2307,40 +2307,40 @@
         <v>9</v>
       </c>
       <c r="BN7" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP7" t="n">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="BQ7" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="BR7" t="n">
-        <v>65</v>
+        <v>36</v>
       </c>
       <c r="BS7" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BT7" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.2</v>
+        <v>4.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>8.4</v>
+        <v>16</v>
       </c>
       <c r="BW7" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="BX7" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="BY7" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BZ7" t="n">
         <v>0</v>
@@ -2350,14 +2350,14 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 08:05:29</t>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2367,244 +2367,752 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>IFK Mariehamn</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Criciuma</t>
+          <t>HJK Helsinki</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3.05</v>
+        <v>8.6</v>
       </c>
       <c r="G8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N8" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V8" t="n">
         <v>3.4</v>
       </c>
-      <c r="H8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I8" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M8" t="n">
+      <c r="W8" t="n">
         <v>1.12</v>
       </c>
-      <c r="N8" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.42</v>
-      </c>
       <c r="X8" t="n">
-        <v>9.199999999999999</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>8.4</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>18.5</v>
+        <v>9.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>50</v>
+        <v>12.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.199999999999999</v>
+        <v>13.5</v>
       </c>
       <c r="AD8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE8" t="n">
-        <v>44</v>
-      </c>
       <c r="AF8" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AG8" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="AJ8" t="n">
-        <v>70</v>
+        <v>330</v>
       </c>
       <c r="AK8" t="n">
-        <v>55</v>
+        <v>150</v>
       </c>
       <c r="AL8" t="n">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM8" t="n">
-        <v>190</v>
+        <v>140</v>
       </c>
       <c r="AN8" t="n">
-        <v>70</v>
+        <v>160</v>
       </c>
       <c r="AO8" t="n">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="AP8" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="AQ8" t="n">
-        <v>7.2</v>
+        <v>9.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>8.6</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.4</v>
+        <v>11</v>
       </c>
       <c r="AT8" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="AU8" t="n">
-        <v>6.2</v>
+        <v>11.5</v>
       </c>
       <c r="AV8" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB8" t="n">
         <v>11</v>
       </c>
-      <c r="AW8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BC8" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.8</v>
+        <v>10</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BF8" t="n">
-        <v>6.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH8" t="n">
-        <v>2.74</v>
+        <v>4.7</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="BJ8" t="n">
         <v>11.5</v>
       </c>
       <c r="BK8" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>9</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BZ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Dinamo Tbilisi</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="G9" t="n">
+        <v>4</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="n">
+        <v>950</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Brazilian Serie B</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>America MG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Criciuma</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>48</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE10" t="n">
         <v>6.4</v>
       </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
+      <c r="BF10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
         <v>14</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BN10" t="n">
         <v>6.2</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BO10" t="n">
         <v>5.4</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BP10" t="n">
         <v>38</v>
       </c>
-      <c r="BQ8" t="n">
+      <c r="BQ10" t="n">
         <v>10</v>
       </c>
-      <c r="BR8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS8" t="n">
+      <c r="BR10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS10" t="n">
         <v>11.5</v>
       </c>
-      <c r="BT8" t="n">
+      <c r="BT10" t="n">
         <v>5.5</v>
       </c>
-      <c r="BU8" t="n">
+      <c r="BU10" t="n">
         <v>4.8</v>
       </c>
-      <c r="BV8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW8" t="n">
+      <c r="BV10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW10" t="n">
         <v>9.4</v>
       </c>
-      <c r="BX8" t="n">
+      <c r="BX10" t="n">
         <v>60</v>
       </c>
-      <c r="BY8" t="n">
+      <c r="BY10" t="n">
         <v>11</v>
       </c>
-      <c r="BZ8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA8" t="n">
+      <c r="BZ10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA10" t="n">
         <v>11.5</v>
       </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>2026-06-22 08:05:29</t>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-22 10:12:52</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB10"/>
+  <dimension ref="A1:CB16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -833,7 +833,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -843,251 +843,251 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Xiamen Feilu</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AC Oulu</t>
+          <t>Hubei Istar</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.46</v>
+        <v>1.86</v>
       </c>
       <c r="G2" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.05</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>3.3</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.34</v>
+        <v>1.26</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.79</v>
+        <v>1.96</v>
       </c>
       <c r="U2" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="V2" t="n">
-        <v>1.44</v>
+        <v>1.21</v>
       </c>
       <c r="W2" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="X2" t="n">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y2" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>25</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>29</v>
+      </c>
+      <c r="AL2" t="n">
         <v>55</v>
       </c>
-      <c r="AB2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>46</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>50</v>
-      </c>
       <c r="AM2" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="AO2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>11.5</v>
+        <v>3.45</v>
       </c>
       <c r="AQ2" t="n">
-        <v>10.5</v>
+        <v>3.65</v>
       </c>
       <c r="AR2" t="n">
-        <v>18</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>4.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>9.4</v>
+        <v>3</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.8</v>
+        <v>3.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>11.5</v>
+        <v>3.9</v>
       </c>
       <c r="AW2" t="n">
-        <v>6.6</v>
+        <v>4.4</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>3.45</v>
       </c>
       <c r="AY2" t="n">
-        <v>10</v>
+        <v>3.45</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.4</v>
+        <v>4</v>
       </c>
       <c r="BC2" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>4.3</v>
       </c>
       <c r="BE2" t="n">
-        <v>7.4</v>
+        <v>4.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>19.5</v>
+        <v>3.8</v>
       </c>
       <c r="BG2" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>9.4</v>
+        <v>1.42</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.6</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>4.1</v>
+        <v>3.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.8</v>
+        <v>1.42</v>
       </c>
       <c r="BR2" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>8</v>
+        <v>1.42</v>
       </c>
       <c r="BT2" t="n">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.7</v>
+        <v>1.46</v>
       </c>
       <c r="BV2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>7.4</v>
+        <v>1.42</v>
       </c>
       <c r="BX2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>1.39</v>
       </c>
       <c r="BZ2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1097,251 +1097,251 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Lahti</t>
+          <t>Changchun Xidu</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>Lanzhou Longyuan Athletic</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1.79</v>
+        <v>3.4</v>
       </c>
       <c r="G3" t="n">
-        <v>1.85</v>
+        <v>4.7</v>
       </c>
       <c r="H3" t="n">
-        <v>5.1</v>
+        <v>2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>5.5</v>
+        <v>2.58</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>2.7</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.41</v>
+        <v>1.59</v>
       </c>
       <c r="M3" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>3.7</v>
+        <v>2.18</v>
       </c>
       <c r="O3" t="n">
-        <v>1.32</v>
+        <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>1.96</v>
+        <v>1.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.96</v>
+        <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.36</v>
+        <v>1.17</v>
       </c>
       <c r="S3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T3" t="n">
-        <v>1.88</v>
+        <v>2.28</v>
       </c>
       <c r="U3" t="n">
-        <v>2.02</v>
+        <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.22</v>
+        <v>1.63</v>
       </c>
       <c r="W3" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X3" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>17</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>44</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>26</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>130</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>150</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BI3" t="n">
         <v>2.18</v>
       </c>
-      <c r="X3" t="n">
-        <v>17</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>18</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>48</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>160</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>23</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>14</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>3.1</v>
-      </c>
       <c r="BJ3" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN3" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="BP3" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR3" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BT3" t="n">
-        <v>8.6</v>
+        <v>5.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1351,251 +1351,251 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Shanghai Second</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Dalian Yingbo II</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.68</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>1.74</v>
+        <v>2.96</v>
       </c>
       <c r="H4" t="n">
-        <v>5.2</v>
+        <v>3.05</v>
       </c>
       <c r="I4" t="n">
-        <v>5.7</v>
+        <v>3.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>2.76</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>4.5</v>
+        <v>2.44</v>
       </c>
       <c r="O4" t="n">
-        <v>1.26</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>1.48</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.74</v>
+        <v>2.46</v>
       </c>
       <c r="R4" t="n">
-        <v>1.48</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>2.94</v>
+        <v>3.45</v>
       </c>
       <c r="T4" t="n">
-        <v>1.76</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>2.22</v>
+        <v>1.73</v>
       </c>
       <c r="V4" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>2.34</v>
+        <v>1.51</v>
       </c>
       <c r="X4" t="n">
-        <v>19.5</v>
+        <v>9.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>19</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI4" t="n">
         <v>95</v>
       </c>
-      <c r="AF4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>90</v>
-      </c>
       <c r="AJ4" t="n">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="AK4" t="n">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="AL4" t="n">
-        <v>44</v>
+        <v>80</v>
       </c>
       <c r="AM4" t="n">
-        <v>120</v>
+        <v>220</v>
       </c>
       <c r="AN4" t="n">
-        <v>9</v>
+        <v>55</v>
       </c>
       <c r="AO4" t="n">
         <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>17</v>
+        <v>3.45</v>
       </c>
       <c r="AQ4" t="n">
-        <v>18.5</v>
+        <v>3.55</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>4.4</v>
       </c>
       <c r="AS4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BJ4" t="n">
         <v>12</v>
       </c>
-      <c r="AT4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>23</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="BK4" t="n">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN4" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP4" t="n">
-        <v>11.5</v>
+        <v>27</v>
       </c>
       <c r="BQ4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BT4" t="n">
         <v>6.6</v>
       </c>
-      <c r="BR4" t="n">
-        <v>24</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BU4" t="n">
-        <v>5.6</v>
+        <v>1.01</v>
       </c>
       <c r="BV4" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="BX4" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1605,186 +1605,186 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>05:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FC Iberia 1999</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FC Meshakhte Tkibuli</t>
+          <t>Dalian Kewei</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.15</v>
+        <v>3.9</v>
       </c>
       <c r="G5" t="n">
-        <v>2.64</v>
+        <v>4.1</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
-        <v>1000</v>
+        <v>2.36</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>950</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="N5" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="O5" t="n">
-        <v>1.24</v>
+        <v>1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>1.07</v>
+        <v>1.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.24</v>
+        <v>2.36</v>
       </c>
       <c r="R5" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.24</v>
+        <v>1.01</v>
       </c>
       <c r="T5" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="W5" t="n">
-        <v>1.61</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AG5" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AK5" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AL5" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO5" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.03</v>
+        <v>3.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.03</v>
+        <v>3.35</v>
       </c>
       <c r="AS5" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.03</v>
+        <v>3.3</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.03</v>
+        <v>2.98</v>
       </c>
       <c r="AV5" t="n">
-        <v>1.03</v>
+        <v>3.4</v>
       </c>
       <c r="AW5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AX5" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="AY5" t="n">
-        <v>1.03</v>
+        <v>3.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BA5" t="n">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG5" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BH5" t="n">
-        <v>1000</v>
+        <v>2.8</v>
       </c>
       <c r="BI5" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1817,7 +1817,7 @@
         <v>1.01</v>
       </c>
       <c r="BT5" t="n">
-        <v>1000</v>
+        <v>4.9</v>
       </c>
       <c r="BU5" t="n">
         <v>1.01</v>
@@ -1842,14 +1842,14 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1859,251 +1859,251 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FC Inter</t>
+          <t>Haimen Codion</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Shanghai Port B</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.56</v>
+        <v>2.5</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>3.05</v>
       </c>
       <c r="H6" t="n">
-        <v>6.2</v>
+        <v>2.8</v>
       </c>
       <c r="I6" t="n">
-        <v>7</v>
+        <v>3.75</v>
       </c>
       <c r="J6" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="K6" t="n">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L6" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="M6" t="n">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="N6" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="O6" t="n">
-        <v>1.23</v>
+        <v>1.47</v>
       </c>
       <c r="P6" t="n">
-        <v>2.36</v>
+        <v>1.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.72</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W6" t="n">
         <v>1.5</v>
       </c>
-      <c r="S6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.68</v>
-      </c>
       <c r="X6" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="Y6" t="n">
-        <v>34</v>
+        <v>11.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="AA6" t="n">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="AB6" t="n">
         <v>10.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="AD6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>60</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH6" t="n">
         <v>26</v>
       </c>
-      <c r="AE6" t="n">
-        <v>90</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>22</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ6" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>46</v>
       </c>
       <c r="AL6" t="n">
-        <v>34</v>
+        <v>75</v>
       </c>
       <c r="AM6" t="n">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>7.2</v>
+        <v>55</v>
       </c>
       <c r="AO6" t="n">
-        <v>110</v>
+        <v>70</v>
       </c>
       <c r="AP6" t="n">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AR6" t="n">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AS6" t="n">
-        <v>11</v>
+        <v>1.03</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AU6" t="n">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV6" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW6" t="n">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX6" t="n">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AY6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AZ6" t="n">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA6" t="n">
-        <v>34</v>
+        <v>1.03</v>
       </c>
       <c r="BB6" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BC6" t="n">
-        <v>14</v>
+        <v>1.01</v>
       </c>
       <c r="BD6" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BE6" t="n">
-        <v>38</v>
+        <v>1.03</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BG6" t="n">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH6" t="n">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.4</v>
+        <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BP6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR6" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BT6" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BV6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Chinese League 2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2113,244 +2113,244 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>08:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Guangdong Mingtu</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Guizhou Zhucheng Athletic</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.55</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.2</v>
+        <v>1.81</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28</v>
+        <v>2.08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.65</v>
+        <v>2.76</v>
       </c>
       <c r="K7" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N7" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="n">
-        <v>1.26</v>
+        <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>2.18</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.78</v>
+        <v>2.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.46</v>
+        <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="U7" t="n">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.78</v>
+        <v>1.93</v>
       </c>
       <c r="W7" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="Y7" t="n">
-        <v>14</v>
+        <v>1000</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AA7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AB7" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD7" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AE7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AG7" t="n">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AH7" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AI7" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ7" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AK7" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AL7" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AM7" t="n">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AN7" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>15.5</v>
+        <v>1.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>1.03</v>
       </c>
       <c r="AR7" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AS7" t="n">
-        <v>18.5</v>
+        <v>1.03</v>
       </c>
       <c r="AT7" t="n">
-        <v>13.5</v>
+        <v>1.03</v>
       </c>
       <c r="AU7" t="n">
-        <v>7.6</v>
+        <v>1.03</v>
       </c>
       <c r="AV7" t="n">
-        <v>10</v>
+        <v>1.03</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>1.03</v>
       </c>
       <c r="AX7" t="n">
-        <v>17.5</v>
+        <v>1.03</v>
       </c>
       <c r="AY7" t="n">
-        <v>13</v>
+        <v>1.03</v>
       </c>
       <c r="AZ7" t="n">
-        <v>14</v>
+        <v>1.03</v>
       </c>
       <c r="BA7" t="n">
-        <v>21</v>
+        <v>1.03</v>
       </c>
       <c r="BB7" t="n">
-        <v>30</v>
+        <v>1.03</v>
       </c>
       <c r="BC7" t="n">
-        <v>22</v>
+        <v>1.03</v>
       </c>
       <c r="BD7" t="n">
-        <v>25</v>
+        <v>1.03</v>
       </c>
       <c r="BE7" t="n">
-        <v>32</v>
+        <v>1.03</v>
       </c>
       <c r="BF7" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BG7" t="n">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.95</v>
+        <v>3.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="BJ7" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>6.6</v>
+        <v>1.4</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>9</v>
+        <v>1.4</v>
       </c>
       <c r="BN7" t="n">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>5.1</v>
+        <v>1.4</v>
       </c>
       <c r="BP7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="BR7" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>7.8</v>
+        <v>1.4</v>
       </c>
       <c r="BT7" t="n">
-        <v>5.5</v>
+        <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="BV7" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>11</v>
+        <v>1.4</v>
       </c>
       <c r="BX7" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
@@ -2367,234 +2367,234 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>IFK Mariehamn</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>HJK Helsinki</t>
+          <t>AC Oulu</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>8.6</v>
+        <v>2.46</v>
       </c>
       <c r="G8" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="N8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="U8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>26</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>38</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>29</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AT8" t="n">
         <v>9.4</v>
       </c>
-      <c r="H8" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="J8" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N8" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="O8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="V8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X8" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AU8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BA8" t="n">
         <v>36</v>
       </c>
-      <c r="AC8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>36</v>
-      </c>
-      <c r="AH8" t="n">
+      <c r="BB8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>20</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>7</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV8" t="n">
         <v>26</v>
       </c>
-      <c r="AI8" t="n">
-        <v>34</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>330</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>150</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>140</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>160</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>5</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>11</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>21</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>20</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>10</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>9</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>13</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>70</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>65</v>
-      </c>
-      <c r="BS8" t="n">
+      <c r="BW8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>40</v>
+      </c>
+      <c r="BY8" t="n">
         <v>8.4</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>6</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>22</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>6.8</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,14 +2604,14 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Georgian Umaglesi Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2621,498 +2621,2022 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Lahti</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.35</v>
+        <v>1.79</v>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>2.4</v>
+        <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>950</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>1.24</v>
+        <v>3.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.27</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.24</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>1.27</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.33</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y9" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF9" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AL9" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN9" t="n">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.03</v>
+        <v>30</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>1.03</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.03</v>
+        <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="BB9" t="n">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.03</v>
+        <v>6.8</v>
       </c>
       <c r="BF9" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BH9" t="n">
-        <v>1000</v>
+        <v>3.4</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BP9" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU9" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BX9" t="n">
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 10:12:52</t>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>KuPS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Ilves</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W10" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="X10" t="n">
+        <v>19</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>160</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>30</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>95</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>85</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>4</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>42</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>11</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BZ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>12:00:00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>FC Iberia 1999</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>FC Meshakhte Tkibuli</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>3</v>
+      </c>
+      <c r="X11" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>110</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>440</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>200</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>170</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>210</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>9</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BU11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>16</v>
+      </c>
+      <c r="CA11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FC Inter</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>SJK</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K12" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W12" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X12" t="n">
+        <v>21</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>34</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>26</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>90</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>10</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>15</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>120</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>110</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>21</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>19</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>34</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>13</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>21</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>36</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>24</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BU12" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BV12" t="n">
+        <v>55</v>
+      </c>
+      <c r="BW12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX12" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY12" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BZ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>13:00:00</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Jaro</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Gnistan</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U13" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X13" t="n">
+        <v>22</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>46</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>32</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>14</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>21</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>30</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>22</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>25</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>18</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>8</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BV13" t="n">
+        <v>16</v>
+      </c>
+      <c r="BW13" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BX13" t="n">
+        <v>27</v>
+      </c>
+      <c r="BY13" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BZ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Finnish Veikkausliiga</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>IFK Mariehamn</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>HJK Helsinki</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X14" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>26</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>340</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>150</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>140</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>160</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>21</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>20</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>11</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>13</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>75</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>9</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>65</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BW14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BX14" t="n">
+        <v>22</v>
+      </c>
+      <c r="BY14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Georgian Umaglesi Liga</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>14:00:00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Dinamo Tbilisi</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Dinamo Batumi</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="X15" t="n">
+        <v>970</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>48</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>150</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>85</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>44</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>970</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>95</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="BZ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Criciuma</t>
         </is>
       </c>
-      <c r="F10" t="n">
+      <c r="F16" t="n">
         <v>3.2</v>
       </c>
-      <c r="G10" t="n">
+      <c r="G16" t="n">
         <v>3.4</v>
       </c>
-      <c r="H10" t="n">
+      <c r="H16" t="n">
         <v>2.56</v>
       </c>
-      <c r="I10" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="I16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J16" t="n">
         <v>3.05</v>
       </c>
-      <c r="K10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O10" t="n">
+      <c r="K16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O16" t="n">
         <v>1.51</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P16" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q16" t="n">
         <v>2.54</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S10" t="n">
+      <c r="R16" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S16" t="n">
         <v>5.1</v>
       </c>
-      <c r="T10" t="n">
+      <c r="T16" t="n">
         <v>2.06</v>
       </c>
-      <c r="U10" t="n">
+      <c r="U16" t="n">
         <v>1.84</v>
       </c>
-      <c r="V10" t="n">
+      <c r="V16" t="n">
         <v>1.58</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="W16" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="X16" t="n">
         <v>9.4</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="Y16" t="n">
         <v>8.4</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="Z16" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AA16" t="n">
         <v>50</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AB16" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AC16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AD16" t="n">
         <v>14.5</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AE16" t="n">
         <v>44</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AF16" t="n">
         <v>23</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AG16" t="n">
         <v>16.5</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AH16" t="n">
         <v>26</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AI16" t="n">
         <v>70</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AJ16" t="n">
         <v>70</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AK16" t="n">
         <v>55</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AL16" t="n">
         <v>80</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AM16" t="n">
         <v>200</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AN16" t="n">
         <v>70</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AO16" t="n">
         <v>48</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AP16" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AQ16" t="n">
         <v>7.2</v>
       </c>
-      <c r="AR10" t="n">
+      <c r="AR16" t="n">
         <v>12.5</v>
       </c>
-      <c r="AS10" t="n">
+      <c r="AS16" t="n">
         <v>5.9</v>
       </c>
-      <c r="AT10" t="n">
+      <c r="AT16" t="n">
         <v>8</v>
       </c>
-      <c r="AU10" t="n">
+      <c r="AU16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW16" t="n">
         <v>5.8</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AX16" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>14</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>10</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY16" t="n">
         <v>11</v>
       </c>
-      <c r="AW10" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>6</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BJ10" t="n">
+      <c r="BZ16" t="n">
+        <v>1000</v>
+      </c>
+      <c r="CA16" t="n">
         <v>11.5</v>
       </c>
-      <c r="BK10" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BO10" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>38</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>60</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>11</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>2026-06-22 10:12:52</t>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>2026-06-22 12:20:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="G2" t="n">
         <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
@@ -872,40 +872,40 @@
         <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O2" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W2" t="n">
         <v>1.93</v>
@@ -929,10 +929,10 @@
         <v>970</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE2" t="n">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AF2" t="n">
         <v>970</v>
@@ -941,16 +941,16 @@
         <v>970</v>
       </c>
       <c r="AH2" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AI2" t="n">
         <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AL2" t="n">
         <v>55</v>
@@ -959,70 +959,70 @@
         <v>1000</v>
       </c>
       <c r="AN2" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AO2" t="n">
         <v>1000</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AQ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV2" t="n">
         <v>3.65</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AW2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AS2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.5</v>
-      </c>
       <c r="BF2" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
@@ -1034,7 +1034,7 @@
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1058,7 +1058,7 @@
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.46</v>
+        <v>1.66</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -1111,58 +1111,58 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2</v>
+        <v>2.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.58</v>
+        <v>2.36</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="M3" t="n">
         <v>1.14</v>
       </c>
       <c r="N3" t="n">
-        <v>2.18</v>
+        <v>2.32</v>
       </c>
       <c r="O3" t="n">
         <v>1.64</v>
       </c>
       <c r="P3" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="Q3" t="n">
         <v>2.84</v>
       </c>
       <c r="R3" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>3.5</v>
+        <v>1.05</v>
       </c>
       <c r="T3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U3" t="n">
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="X3" t="n">
         <v>8</v>
@@ -1174,16 +1174,16 @@
         <v>17</v>
       </c>
       <c r="AA3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="AC3" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AE3" t="n">
         <v>46</v>
@@ -1192,7 +1192,7 @@
         <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
@@ -1201,10 +1201,10 @@
         <v>95</v>
       </c>
       <c r="AJ3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AK3" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AL3" t="n">
         <v>150</v>
@@ -1216,125 +1216,125 @@
         <v>1000</v>
       </c>
       <c r="AO3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="BN3" t="n">
         <v>1000</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.01</v>
+        <v>1.99</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.2</v>
+        <v>4.9</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="I4" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="P4" t="n">
         <v>1.54</v>
       </c>
-      <c r="P4" t="n">
-        <v>1.48</v>
-      </c>
       <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>70</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>190</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>44</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="BI4" t="n">
         <v>2.46</v>
       </c>
-      <c r="R4" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="BJ4" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BP4" t="n">
         <v>25</v>
       </c>
-      <c r="AA4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>19</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>220</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>85</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN4" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BO4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BP4" t="n">
-        <v>27</v>
-      </c>
       <c r="BQ4" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV4" t="n">
         <v>1000</v>
       </c>
       <c r="BW4" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -1622,227 +1622,227 @@
         <v>3.9</v>
       </c>
       <c r="G5" t="n">
+        <v>4</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="O5" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="S5" t="n">
         <v>4.1</v>
       </c>
-      <c r="H5" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>1.68</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AA5" t="n">
         <v>36</v>
       </c>
       <c r="AB5" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC5" t="n">
         <v>9</v>
       </c>
       <c r="AD5" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="AE5" t="n">
         <v>38</v>
       </c>
       <c r="AF5" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AG5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AH5" t="n">
         <v>32</v>
       </c>
       <c r="AI5" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="AJ5" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AK5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AL5" t="n">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="AM5" t="n">
         <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="AO5" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>2.98</v>
+        <v>3.25</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AW5" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="AX5" t="n">
-        <v>3.95</v>
+        <v>4.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="AZ5" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BE5" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.3</v>
       </c>
-      <c r="BF5" t="n">
+      <c r="BH5" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO5" t="n">
         <v>4.3</v>
       </c>
-      <c r="BG5" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BT5" t="n">
         <v>4.9</v>
       </c>
       <c r="BU5" t="n">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -1873,172 +1873,172 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="G6" t="n">
-        <v>3.05</v>
+        <v>3.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="I6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N6" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S6" t="n">
         <v>3.75</v>
       </c>
-      <c r="J6" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="T6" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>1.79</v>
+        <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="X6" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y6" t="n">
-        <v>11.5</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AA6" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AB6" t="n">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.6</v>
+        <v>970</v>
       </c>
       <c r="AD6" t="n">
-        <v>17.5</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>70</v>
+      </c>
+      <c r="AJ6" t="n">
         <v>60</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>26</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>55</v>
       </c>
       <c r="AK6" t="n">
         <v>46</v>
       </c>
       <c r="AL6" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM6" t="n">
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AO6" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="AR6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.01</v>
+        <v>2.98</v>
       </c>
       <c r="AV6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AW6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="AZ6" t="n">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BB6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD6" t="n">
-        <v>1.03</v>
+        <v>4.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.03</v>
+        <v>2.88</v>
       </c>
       <c r="BF6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BG6" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH6" t="n">
-        <v>1000</v>
+        <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
         <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.81</v>
+        <v>1.78</v>
       </c>
       <c r="I7" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
-        <v>2.76</v>
+        <v>3.2</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
         <v>1.01</v>
@@ -2157,25 +2157,25 @@
         <v>1.39</v>
       </c>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R7" t="n">
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="T7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
         <v>1.18</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="G8" t="n">
         <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
         <v>3.25</v>
@@ -2405,28 +2405,28 @@
         <v>1.07</v>
       </c>
       <c r="N8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O8" t="n">
         <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T8" t="n">
         <v>1.79</v>
       </c>
       <c r="U8" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
         <v>1.44</v>
@@ -2441,7 +2441,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AA8" t="n">
         <v>65</v>
@@ -2459,7 +2459,7 @@
         <v>40</v>
       </c>
       <c r="AF8" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2474,7 +2474,7 @@
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AL8" t="n">
         <v>50</v>
@@ -2483,34 +2483,34 @@
         <v>120</v>
       </c>
       <c r="AN8" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AO8" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AP8" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AR8" t="n">
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2522,25 +2522,25 @@
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.4</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BD8" t="n">
         <v>32</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>36</v>
       </c>
       <c r="BF8" t="n">
         <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>6.4</v>
+        <v>22</v>
       </c>
       <c r="BH8" t="n">
         <v>3.45</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
         <v>1.85</v>
@@ -2644,13 +2644,13 @@
         <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
@@ -2674,16 +2674,16 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
         <v>1.88</v>
       </c>
       <c r="U9" t="n">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>2.18</v>
@@ -2719,7 +2719,7 @@
         <v>12</v>
       </c>
       <c r="AH9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI9" t="n">
         <v>85</v>
@@ -2749,10 +2749,10 @@
         <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT9" t="n">
         <v>7.8</v>
@@ -2785,10 +2785,10 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE9" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
         <v>1.74</v>
@@ -2913,7 +2913,7 @@
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>1.26</v>
@@ -2922,13 +2922,13 @@
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T10" t="n">
         <v>1.76</v>
@@ -3003,10 +3003,10 @@
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AS10" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -3149,19 +3149,19 @@
         <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I11" t="n">
         <v>12.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
         <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -3400,16 +3400,16 @@
         <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="K12" t="n">
         <v>4.8</v>
@@ -3424,16 +3424,16 @@
         <v>4.7</v>
       </c>
       <c r="O12" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q12" t="n">
         <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
         <v>2.82</v>
@@ -3448,7 +3448,7 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -3460,7 +3460,7 @@
         <v>60</v>
       </c>
       <c r="AA12" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
@@ -3469,13 +3469,13 @@
         <v>10.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AE12" t="n">
         <v>90</v>
       </c>
       <c r="AF12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
@@ -3499,7 +3499,7 @@
         <v>120</v>
       </c>
       <c r="AN12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AO12" t="n">
         <v>110</v>
@@ -3568,7 +3568,7 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,7 +3586,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.6</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
@@ -3598,7 +3598,7 @@
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV12" t="n">
         <v>55</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -3657,7 +3657,7 @@
         <v>3.6</v>
       </c>
       <c r="H13" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="I13" t="n">
         <v>2.28</v>
@@ -3681,7 +3681,7 @@
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q13" t="n">
         <v>1.78</v>
@@ -3690,7 +3690,7 @@
         <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="T13" t="n">
         <v>1.66</v>
@@ -3699,7 +3699,7 @@
         <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="W13" t="n">
         <v>1.39</v>
@@ -3768,7 +3768,7 @@
         <v>13.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AT13" t="n">
         <v>14</v>
@@ -3783,7 +3783,7 @@
         <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AY13" t="n">
         <v>13</v>
@@ -3804,7 +3804,7 @@
         <v>25</v>
       </c>
       <c r="BE13" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="BF13" t="n">
         <v>20</v>
@@ -3822,49 +3822,49 @@
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="BN13" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.1</v>
+        <v>5.8</v>
       </c>
       <c r="BP13" t="n">
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>18</v>
+        <v>7.2</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BT13" t="n">
         <v>5.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="BV13" t="n">
         <v>16</v>
       </c>
       <c r="BW13" t="n">
-        <v>6.2</v>
+        <v>11</v>
       </c>
       <c r="BX13" t="n">
         <v>27</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -3908,13 +3908,13 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I14" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="J14" t="n">
         <v>5.5</v>
@@ -3953,10 +3953,10 @@
         <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>28</v>
@@ -4013,7 +4013,7 @@
         <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ14" t="n">
         <v>9.6</v>
@@ -4106,13 +4106,13 @@
         <v>4.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BV14" t="n">
         <v>8.4</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>4.6</v>
       </c>
       <c r="BX14" t="n">
         <v>22</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -4171,7 +4171,7 @@
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -4183,7 +4183,7 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="O15" t="n">
         <v>1.3</v>
@@ -4201,10 +4201,10 @@
         <v>3.2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U15" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="V15" t="n">
         <v>1.18</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>
@@ -4422,7 +4422,7 @@
         <v>2.56</v>
       </c>
       <c r="I16" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="J16" t="n">
         <v>3.05</v>
@@ -4437,7 +4437,7 @@
         <v>1.11</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="O16" t="n">
         <v>1.51</v>
@@ -4452,7 +4452,7 @@
         <v>1.22</v>
       </c>
       <c r="S16" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="T16" t="n">
         <v>2.06</v>
@@ -4464,7 +4464,7 @@
         <v>1.58</v>
       </c>
       <c r="W16" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4482,7 +4482,7 @@
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -4530,7 +4530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -4542,10 +4542,10 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AY16" t="n">
         <v>12.5</v>
@@ -4560,10 +4560,10 @@
         <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BE16" t="n">
         <v>6.4</v>
@@ -4572,7 +4572,7 @@
         <v>6</v>
       </c>
       <c r="BG16" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>2.74</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 12:20:54</t>
+          <t>2026-06-22 14:28:54</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -869,10 +869,10 @@
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
         <v>1.38</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G3" t="n">
         <v>5.3</v>
@@ -1120,13 +1120,13 @@
         <v>2.04</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2.76</v>
+        <v>2.74</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
@@ -1150,7 +1150,7 @@
         <v>1.16</v>
       </c>
       <c r="S3" t="n">
-        <v>1.05</v>
+        <v>6.4</v>
       </c>
       <c r="T3" t="n">
         <v>2.3</v>
@@ -1159,7 +1159,7 @@
         <v>1.59</v>
       </c>
       <c r="V3" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="W3" t="n">
         <v>1.23</v>
@@ -1168,7 +1168,7 @@
         <v>8</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="Z3" t="n">
         <v>17</v>
@@ -1180,19 +1180,19 @@
         <v>970</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD3" t="n">
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="AF3" t="n">
         <v>38</v>
       </c>
       <c r="AG3" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AH3" t="n">
         <v>34</v>
@@ -1219,58 +1219,58 @@
         <v>50</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AR3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT3" t="n">
         <v>4.5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>4.3</v>
-      </c>
       <c r="AU3" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="AV3" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AW3" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX3" t="n">
+        <v>6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>5.6</v>
       </c>
-      <c r="AY3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="BE3" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.6</v>
+        <v>3.15</v>
       </c>
       <c r="BG3" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BH3" t="n">
         <v>2.6</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
@@ -1383,7 +1383,7 @@
         <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1422,22 +1422,22 @@
         <v>10.5</v>
       </c>
       <c r="Y4" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
         <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE4" t="n">
         <v>55</v>
@@ -1446,19 +1446,19 @@
         <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ4" t="n">
         <v>48</v>
       </c>
       <c r="AK4" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL4" t="n">
         <v>65</v>
@@ -1473,64 +1473,64 @@
         <v>65</v>
       </c>
       <c r="AP4" t="n">
-        <v>3.85</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AR4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AV4" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AW4" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BA4" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>5.7</v>
-      </c>
       <c r="BB4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="n">
         <v>2.92</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.46</v>
+        <v>2.34</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -1625,7 +1625,7 @@
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="I5" t="n">
         <v>2.22</v>
@@ -1634,7 +1634,7 @@
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L5" t="n">
         <v>1.45</v>
@@ -1649,22 +1649,22 @@
         <v>1.47</v>
       </c>
       <c r="P5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
         <v>2.38</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="S5" t="n">
         <v>4.1</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.81</v>
@@ -1682,28 +1682,28 @@
         <v>970</v>
       </c>
       <c r="AA5" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AB5" t="n">
         <v>14</v>
       </c>
       <c r="AC5" t="n">
-        <v>9</v>
+        <v>970</v>
       </c>
       <c r="AD5" t="n">
         <v>970</v>
       </c>
       <c r="AE5" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AF5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AI5" t="n">
         <v>70</v>
@@ -1727,64 +1727,64 @@
         <v>28</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.5</v>
+        <v>3.85</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="AR5" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="AT5" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AW5" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AX5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY5" t="n">
         <v>4.5</v>
       </c>
-      <c r="AY5" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AZ5" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="BB5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG5" t="n">
         <v>4.9</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>4.3</v>
       </c>
       <c r="BH5" t="n">
         <v>2.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
         <v>2.58</v>
       </c>
       <c r="G6" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="H6" t="n">
         <v>2.62</v>
@@ -1903,7 +1903,7 @@
         <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="Q6" t="n">
         <v>2.18</v>
@@ -1912,7 +1912,7 @@
         <v>1.23</v>
       </c>
       <c r="S6" t="n">
-        <v>3.75</v>
+        <v>1.05</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
@@ -1921,7 +1921,7 @@
         <v>1.86</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
         <v>1.44</v>
@@ -1942,7 +1942,7 @@
         <v>970</v>
       </c>
       <c r="AC6" t="n">
-        <v>970</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1975,13 +1975,13 @@
         <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
         <v>50</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="AQ6" t="n">
         <v>3.3</v>
@@ -1993,28 +1993,28 @@
         <v>4.2</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="AU6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AX6" t="n">
         <v>3.8</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="AZ6" t="n">
         <v>3.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BB6" t="n">
         <v>4.2</v>
@@ -2023,22 +2023,22 @@
         <v>4.1</v>
       </c>
       <c r="BD6" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE6" t="n">
         <v>4.3</v>
       </c>
-      <c r="BE6" t="n">
-        <v>2.88</v>
-      </c>
       <c r="BF6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
         <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="Q8" t="n">
         <v>2.04</v>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AI8" t="n">
         <v>60</v>
@@ -2474,7 +2474,7 @@
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AL8" t="n">
         <v>50</v>
@@ -2528,7 +2528,7 @@
         <v>21</v>
       </c>
       <c r="BC8" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BD8" t="n">
         <v>32</v>
@@ -2552,7 +2552,7 @@
         <v>10</v>
       </c>
       <c r="BK8" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
@@ -2564,7 +2564,7 @@
         <v>5.6</v>
       </c>
       <c r="BO8" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="BP8" t="n">
         <v>20</v>
@@ -2582,7 +2582,7 @@
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
       <c r="BV8" t="n">
         <v>26</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
         <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.75</v>
@@ -2674,7 +2674,7 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
         <v>1.88</v>
@@ -2683,7 +2683,7 @@
         <v>2.06</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
         <v>2.18</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
         <v>1.74</v>
       </c>
       <c r="H10" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="I10" t="n">
         <v>5.7</v>
@@ -2907,7 +2907,7 @@
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -3149,7 +3149,7 @@
         <v>1.49</v>
       </c>
       <c r="H11" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="I11" t="n">
         <v>12.5</v>
@@ -3185,7 +3185,7 @@
         <v>2.72</v>
       </c>
       <c r="T11" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U11" t="n">
         <v>1.77</v>
@@ -3251,7 +3251,7 @@
         <v>300</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AQ11" t="n">
         <v>4.5</v>
@@ -3263,10 +3263,10 @@
         <v>5.1</v>
       </c>
       <c r="AT11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AV11" t="n">
         <v>4.6</v>
@@ -3275,10 +3275,10 @@
         <v>5</v>
       </c>
       <c r="AX11" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="AZ11" t="n">
         <v>4.5</v>
@@ -3287,10 +3287,10 @@
         <v>5</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BD11" t="n">
         <v>4.7</v>
@@ -3299,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="BG11" t="n">
         <v>5.1</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -3427,19 +3427,19 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
         <v>1.72</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="S12" t="n">
         <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="U12" t="n">
         <v>2.1</v>
@@ -3580,7 +3580,7 @@
         <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="BP12" t="n">
         <v>10.5</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -3660,13 +3660,13 @@
         <v>2.2</v>
       </c>
       <c r="I13" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
         <v>1.35</v>
@@ -3690,7 +3690,7 @@
         <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.66</v>
@@ -3699,7 +3699,7 @@
         <v>2.42</v>
       </c>
       <c r="V13" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="W13" t="n">
         <v>1.39</v>
@@ -3732,7 +3732,7 @@
         <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AH13" t="n">
         <v>16.5</v>
@@ -3744,7 +3744,7 @@
         <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="AL13" t="n">
         <v>55</v>
@@ -3822,13 +3822,13 @@
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3840,16 +3840,16 @@
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BU13" t="n">
         <v>4.5</v>
@@ -3864,7 +3864,7 @@
         <v>27</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -3911,10 +3911,10 @@
         <v>9.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I14" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="J14" t="n">
         <v>5.5</v>
@@ -3935,7 +3935,7 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q14" t="n">
         <v>1.57</v>
@@ -3953,7 +3953,7 @@
         <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="W14" t="n">
         <v>1.12</v>
@@ -3995,7 +3995,7 @@
         <v>34</v>
       </c>
       <c r="AJ14" t="n">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="AK14" t="n">
         <v>150</v>
@@ -4037,7 +4037,7 @@
         <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>10</v>
+        <v>34</v>
       </c>
       <c r="AY14" t="n">
         <v>21</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -4159,79 +4159,79 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G15" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="I15" t="n">
         <v>6.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N15" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="O15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="Q15" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T15" t="n">
         <v>1.86</v>
       </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.8</v>
-      </c>
       <c r="U15" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="V15" t="n">
         <v>1.18</v>
       </c>
       <c r="W15" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X15" t="n">
         <v>970</v>
       </c>
       <c r="Y15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AA15" t="n">
         <v>150</v>
       </c>
       <c r="AB15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AE15" t="n">
         <v>85</v>
@@ -4240,149 +4240,149 @@
         <v>970</v>
       </c>
       <c r="AG15" t="n">
-        <v>12.5</v>
+        <v>970</v>
       </c>
       <c r="AH15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI15" t="n">
         <v>85</v>
       </c>
       <c r="AJ15" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AK15" t="n">
         <v>24</v>
       </c>
       <c r="AL15" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM15" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AN15" t="n">
         <v>970</v>
       </c>
       <c r="AO15" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="AP15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX15" t="n">
         <v>3.4</v>
       </c>
-      <c r="AQ15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AR15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AW15" t="n">
+      <c r="AY15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ15" t="n">
         <v>4</v>
       </c>
-      <c r="AX15" t="n">
+      <c r="BA15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>23</v>
+      </c>
+      <c r="BO15" t="n">
         <v>3.2</v>
       </c>
-      <c r="AY15" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BF15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BG15" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH15" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BI15" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BJ15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BL15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM15" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BN15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO15" t="n">
-        <v>1.29</v>
-      </c>
       <c r="BP15" t="n">
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>1.29</v>
+        <v>2.22</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BT15" t="n">
         <v>1000</v>
       </c>
       <c r="BU15" t="n">
-        <v>1.29</v>
+        <v>4.8</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>
@@ -4455,10 +4455,10 @@
         <v>5.2</v>
       </c>
       <c r="T16" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="V16" t="n">
         <v>1.58</v>
@@ -4470,13 +4470,13 @@
         <v>9.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="Z16" t="n">
         <v>18.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AB16" t="n">
         <v>10.5</v>
@@ -4488,7 +4488,7 @@
         <v>14.5</v>
       </c>
       <c r="AE16" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AF16" t="n">
         <v>23</v>
@@ -4497,7 +4497,7 @@
         <v>16.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>70</v>
@@ -4512,13 +4512,13 @@
         <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AN16" t="n">
         <v>70</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP16" t="n">
         <v>8.199999999999999</v>
@@ -4530,7 +4530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -4542,7 +4542,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX16" t="n">
         <v>17</v>
@@ -4560,10 +4560,10 @@
         <v>6</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE16" t="n">
         <v>6.4</v>
@@ -4575,13 +4575,13 @@
         <v>5.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BK16" t="n">
         <v>6.4</v>
@@ -4596,7 +4596,7 @@
         <v>6.2</v>
       </c>
       <c r="BO16" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BP16" t="n">
         <v>1000</v>
@@ -4620,13 +4620,13 @@
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 14:28:54</t>
+          <t>2026-06-22 16:36:21</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,25 +857,25 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G2" t="n">
         <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="I2" t="n">
         <v>6.2</v>
       </c>
       <c r="J2" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
@@ -911,112 +911,112 @@
         <v>1.93</v>
       </c>
       <c r="X2" t="n">
-        <v>970</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
       </c>
       <c r="Z2" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA2" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>970</v>
+        <v>9.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>970</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD2" t="n">
-        <v>24</v>
+        <v>950</v>
       </c>
       <c r="AE2" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>970</v>
+        <v>36</v>
       </c>
       <c r="AH2" t="n">
-        <v>26</v>
+        <v>950</v>
       </c>
       <c r="AI2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>900</v>
       </c>
       <c r="AK2" t="n">
-        <v>27</v>
+        <v>500</v>
       </c>
       <c r="AL2" t="n">
+        <v>500</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>580</v>
+      </c>
+      <c r="AN2" t="n">
         <v>55</v>
       </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>970</v>
-      </c>
       <c r="AO2" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AP2" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="AS2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>4.2</v>
       </c>
-      <c r="AT2" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="BA2" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BD2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BF2" t="n">
         <v>4</v>
       </c>
-      <c r="BE2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>3.55</v>
-      </c>
       <c r="BG2" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -1111,40 +1111,40 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="K3" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L3" t="n">
         <v>1.58</v>
       </c>
       <c r="M3" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="N3" t="n">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="O3" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="P3" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.84</v>
+        <v>2.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.16</v>
@@ -1153,31 +1153,31 @@
         <v>6.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="U3" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="V3" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="Z3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
-        <v>42</v>
+        <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>970</v>
+        <v>11.5</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
@@ -1186,91 +1186,91 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AF3" t="n">
-        <v>38</v>
+        <v>500</v>
       </c>
       <c r="AG3" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AH3" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AI3" t="n">
-        <v>95</v>
+        <v>500</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK3" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AL3" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="AM3" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN3" t="n">
-        <v>1000</v>
+        <v>600</v>
       </c>
       <c r="AO3" t="n">
-        <v>50</v>
+        <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.85</v>
+        <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="AS3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AY3" t="n">
         <v>6</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>5.6</v>
-      </c>
       <c r="AZ3" t="n">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>8.4</v>
       </c>
       <c r="BE3" t="n">
-        <v>3.15</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="BG3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BH3" t="n">
         <v>2.6</v>
@@ -1288,53 +1288,53 @@
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>2.04</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.99</v>
+        <v>2.68</v>
       </c>
       <c r="BT3" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.02</v>
+        <v>6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.1</v>
+        <v>2.58</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1365,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
         <v>2.94</v>
@@ -1377,10 +1377,10 @@
         <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>2.82</v>
+        <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
@@ -1389,28 +1389,28 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P4" t="n">
         <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="R4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="T4" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1419,7 +1419,7 @@
         <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
         <v>10.5</v>
@@ -1428,7 +1428,7 @@
         <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>70</v>
+        <v>420</v>
       </c>
       <c r="AB4" t="n">
         <v>9</v>
@@ -1440,7 +1440,7 @@
         <v>16</v>
       </c>
       <c r="AE4" t="n">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
         <v>17.5</v>
@@ -1452,143 +1452,143 @@
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>75</v>
+        <v>500</v>
       </c>
       <c r="AJ4" t="n">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>40</v>
+        <v>140</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
-        <v>190</v>
+        <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
-        <v>65</v>
+        <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
-        <v>4.2</v>
+        <v>8</v>
       </c>
       <c r="AR4" t="n">
-        <v>5.4</v>
+        <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AT4" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>3.7</v>
+        <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.1</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.7</v>
+        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.4</v>
+        <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BB4" t="n">
-        <v>6.2</v>
+        <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>6.2</v>
+        <v>32</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
         <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>2.18</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BO4" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BP4" t="n">
         <v>25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>2.02</v>
+        <v>6.6</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>2.1</v>
+        <v>7.6</v>
       </c>
       <c r="BT4" t="n">
         <v>6.6</v>
       </c>
       <c r="BU4" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV4" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BW4" t="n">
-        <v>2.06</v>
+        <v>7.2</v>
       </c>
       <c r="BX4" t="n">
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>2.12</v>
+        <v>55</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>2.1</v>
+        <v>7.8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>3.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="H5" t="n">
         <v>2.12</v>
@@ -1631,13 +1631,13 @@
         <v>2.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L5" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
@@ -1646,22 +1646,22 @@
         <v>2.74</v>
       </c>
       <c r="O5" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="P5" t="n">
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
         <v>1.75</v>
@@ -1670,121 +1670,121 @@
         <v>1.81</v>
       </c>
       <c r="W5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X5" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.4</v>
+        <v>15.5</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
       </c>
       <c r="AA5" t="n">
+        <v>900</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>29</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD5" t="n">
         <v>30</v>
       </c>
-      <c r="AB5" t="n">
-        <v>14</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>970</v>
-      </c>
       <c r="AE5" t="n">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="AF5" t="n">
-        <v>34</v>
+        <v>500</v>
       </c>
       <c r="AG5" t="n">
         <v>970</v>
       </c>
       <c r="AH5" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AI5" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ5" t="n">
-        <v>140</v>
+        <v>900</v>
       </c>
       <c r="AK5" t="n">
-        <v>90</v>
+        <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>110</v>
+        <v>540</v>
       </c>
       <c r="AM5" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN5" t="n">
-        <v>140</v>
+        <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>28</v>
+        <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="AQ5" t="n">
-        <v>3.45</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="AS5" t="n">
-        <v>4.9</v>
+        <v>19</v>
       </c>
       <c r="AT5" t="n">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="AU5" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AW5" t="n">
-        <v>5</v>
+        <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="AY5" t="n">
-        <v>4.5</v>
+        <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>4.8</v>
+        <v>6.8</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5.7</v>
+        <v>8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG5" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,53 +1796,53 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.36</v>
+        <v>1.78</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO5" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="BT5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>1.53</v>
+        <v>4.7</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>1.53</v>
+        <v>4.7</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -1882,13 +1882,13 @@
         <v>2.62</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="L6" t="n">
         <v>1.41</v>
@@ -1897,19 +1897,19 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="O6" t="n">
         <v>1.41</v>
       </c>
       <c r="P6" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="Q6" t="n">
         <v>2.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
@@ -1918,185 +1918,185 @@
         <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="W6" t="n">
         <v>1.44</v>
       </c>
       <c r="X6" t="n">
-        <v>970</v>
+        <v>22</v>
       </c>
       <c r="Y6" t="n">
         <v>970</v>
       </c>
       <c r="Z6" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AA6" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>8.800000000000001</v>
+        <v>16</v>
       </c>
       <c r="AD6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE6" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>23</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
-        <v>23</v>
+        <v>950</v>
       </c>
       <c r="AI6" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>60</v>
+        <v>900</v>
       </c>
       <c r="AK6" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>70</v>
+        <v>500</v>
       </c>
       <c r="AM6" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>500</v>
       </c>
       <c r="AO6" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="AP6" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AS6" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="AT6" t="n">
-        <v>3.25</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AW6" t="n">
-        <v>4.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="AZ6" t="n">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>5.7</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>4.1</v>
+        <v>5.7</v>
       </c>
       <c r="BG6" t="n">
-        <v>4.1</v>
+        <v>5.8</v>
       </c>
       <c r="BH6" t="n">
         <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.01</v>
+        <v>1.23</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.01</v>
+        <v>1.2</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -2145,10 +2145,10 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
         <v>2.5</v>
@@ -2166,7 +2166,7 @@
         <v>1.18</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
         <v>1.11</v>
@@ -2175,118 +2175,118 @@
         <v>1.11</v>
       </c>
       <c r="V7" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="W7" t="n">
         <v>1.18</v>
       </c>
       <c r="X7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="Y7" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AA7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AC7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AD7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AE7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AF7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AG7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AJ7" t="n">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AK7" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AL7" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AM7" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="AP7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AR7" t="n">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.03</v>
+        <v>1.55</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.03</v>
+        <v>1.54</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.03</v>
+        <v>1.59</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.03</v>
+        <v>1.6</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.03</v>
+        <v>1.58</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.03</v>
+        <v>1.61</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="BG7" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BH7" t="n">
         <v>3.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -2381,16 +2381,16 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="I8" t="n">
         <v>3.1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>3.25</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
@@ -2414,7 +2414,7 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
@@ -2429,10 +2429,10 @@
         <v>2.18</v>
       </c>
       <c r="V8" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2444,7 +2444,7 @@
         <v>22</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AB8" t="n">
         <v>11</v>
@@ -2456,7 +2456,7 @@
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AF8" t="n">
         <v>16</v>
@@ -2468,7 +2468,7 @@
         <v>18</v>
       </c>
       <c r="AI8" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
         <v>38</v>
@@ -2477,16 +2477,16 @@
         <v>28</v>
       </c>
       <c r="AL8" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>120</v>
+        <v>500</v>
       </c>
       <c r="AN8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AP8" t="n">
         <v>12</v>
@@ -2498,16 +2498,16 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
       </c>
       <c r="AV8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW8" t="n">
         <v>22</v>
@@ -2516,22 +2516,22 @@
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
       </c>
       <c r="BA8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC8" t="n">
         <v>19.5</v>
       </c>
       <c r="BD8" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE8" t="n">
         <v>36</v>
@@ -2540,7 +2540,7 @@
         <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BH8" t="n">
         <v>3.45</v>
@@ -2558,10 +2558,10 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BO8" t="n">
         <v>4.7</v>
@@ -2570,13 +2570,13 @@
         <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR8" t="n">
         <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2588,13 +2588,13 @@
         <v>26</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BX8" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -2635,10 +2635,10 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
         <v>5.1</v>
@@ -2647,10 +2647,10 @@
         <v>5.5</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
@@ -2668,19 +2668,19 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="R9" t="n">
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2689,16 +2689,16 @@
         <v>2.18</v>
       </c>
       <c r="X9" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y9" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Z9" t="n">
         <v>48</v>
       </c>
       <c r="AA9" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
         <v>8.6</v>
@@ -2710,7 +2710,7 @@
         <v>24</v>
       </c>
       <c r="AE9" t="n">
-        <v>85</v>
+        <v>160</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
@@ -2722,7 +2722,7 @@
         <v>23</v>
       </c>
       <c r="AI9" t="n">
-        <v>85</v>
+        <v>190</v>
       </c>
       <c r="AJ9" t="n">
         <v>22</v>
@@ -2734,28 +2734,28 @@
         <v>44</v>
       </c>
       <c r="AM9" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN9" t="n">
         <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,19 +2764,19 @@
         <v>18</v>
       </c>
       <c r="AW9" t="n">
-        <v>6.6</v>
+        <v>32</v>
       </c>
       <c r="AX9" t="n">
         <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>17.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>6.6</v>
+        <v>34</v>
       </c>
       <c r="BB9" t="n">
         <v>16.5</v>
@@ -2785,16 +2785,16 @@
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.6</v>
+        <v>24</v>
       </c>
       <c r="BE9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>6.8</v>
+        <v>12</v>
       </c>
       <c r="BH9" t="n">
         <v>3.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -2889,22 +2889,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="G10" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
@@ -2916,19 +2916,19 @@
         <v>4.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P10" t="n">
         <v>2.22</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="T10" t="n">
         <v>1.76</v>
@@ -2937,13 +2937,13 @@
         <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Y10" t="n">
         <v>21</v>
@@ -2952,7 +2952,7 @@
         <v>60</v>
       </c>
       <c r="AA10" t="n">
-        <v>160</v>
+        <v>900</v>
       </c>
       <c r="AB10" t="n">
         <v>10</v>
@@ -2964,7 +2964,7 @@
         <v>30</v>
       </c>
       <c r="AE10" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AF10" t="n">
         <v>11.5</v>
@@ -2976,10 +2976,10 @@
         <v>19</v>
       </c>
       <c r="AI10" t="n">
-        <v>90</v>
+        <v>320</v>
       </c>
       <c r="AJ10" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AK10" t="n">
         <v>17</v>
@@ -2988,10 +2988,10 @@
         <v>44</v>
       </c>
       <c r="AM10" t="n">
-        <v>120</v>
+        <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AO10" t="n">
         <v>85</v>
@@ -3003,10 +3003,10 @@
         <v>18.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -3018,7 +3018,7 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3042,40 +3042,40 @@
         <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF10" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BJ10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="BN10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO10" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BP10" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BQ10" t="n">
         <v>6.6</v>
@@ -3084,25 +3084,25 @@
         <v>24</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BT10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
       <c r="BV10" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BW10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BX10" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY10" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -3143,22 +3143,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.49</v>
+        <v>1.45</v>
       </c>
       <c r="H11" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I11" t="n">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="L11" t="n">
         <v>1.3</v>
@@ -3167,13 +3167,13 @@
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="Q11" t="n">
         <v>1.79</v>
@@ -3182,7 +3182,7 @@
         <v>1.4</v>
       </c>
       <c r="S11" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="T11" t="n">
         <v>2.06</v>
@@ -3194,13 +3194,13 @@
         <v>1.1</v>
       </c>
       <c r="W11" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="X11" t="n">
         <v>22</v>
       </c>
       <c r="Y11" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="Z11" t="n">
         <v>110</v>
@@ -3212,97 +3212,97 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AE11" t="n">
         <v>200</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AG11" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
         <v>170</v>
       </c>
       <c r="AJ11" t="n">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK11" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL11" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AM11" t="n">
         <v>210</v>
       </c>
       <c r="AN11" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO11" t="n">
         <v>300</v>
       </c>
       <c r="AP11" t="n">
-        <v>4.2</v>
+        <v>6.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="AR11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AY11" t="n">
         <v>4.9</v>
       </c>
-      <c r="AS11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="AZ11" t="n">
-        <v>4.5</v>
+        <v>7</v>
       </c>
       <c r="BA11" t="n">
-        <v>5</v>
+        <v>8.6</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.85</v>
+        <v>5.3</v>
       </c>
       <c r="BC11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF11" t="n">
         <v>4.1</v>
       </c>
-      <c r="BD11" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>3.4</v>
-      </c>
       <c r="BG11" t="n">
-        <v>5.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH11" t="n">
         <v>3.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -3400,7 +3400,7 @@
         <v>1.56</v>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H12" t="n">
         <v>6.2</v>
@@ -3430,7 +3430,7 @@
         <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
         <v>1.51</v>
@@ -3448,7 +3448,7 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X12" t="n">
         <v>21</v>
@@ -3460,7 +3460,7 @@
         <v>60</v>
       </c>
       <c r="AA12" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
         <v>10.5</v>
@@ -3472,10 +3472,10 @@
         <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>90</v>
+        <v>700</v>
       </c>
       <c r="AF12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AG12" t="n">
         <v>10.5</v>
@@ -3484,7 +3484,7 @@
         <v>22</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AJ12" t="n">
         <v>15</v>
@@ -3496,16 +3496,16 @@
         <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>120</v>
+        <v>700</v>
       </c>
       <c r="AN12" t="n">
         <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>110</v>
+        <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>18.5</v>
+        <v>16</v>
       </c>
       <c r="AQ12" t="n">
         <v>21</v>
@@ -3514,7 +3514,7 @@
         <v>42</v>
       </c>
       <c r="AS12" t="n">
-        <v>11.5</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
@@ -3532,10 +3532,10 @@
         <v>9</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA12" t="n">
         <v>34</v>
@@ -3568,7 +3568,7 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>8</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3586,7 +3586,7 @@
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -3651,22 +3651,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="G13" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>1.35</v>
@@ -3675,46 +3675,46 @@
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="O13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="S13" t="n">
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8</v>
+        <v>1.84</v>
       </c>
       <c r="W13" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="X13" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AB13" t="n">
         <v>18.5</v>
@@ -3723,10 +3723,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AD13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AE13" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="AF13" t="n">
         <v>32</v>
@@ -3738,97 +3738,97 @@
         <v>16.5</v>
       </c>
       <c r="AI13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AK13" t="n">
         <v>40</v>
       </c>
       <c r="AL13" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AM13" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AN13" t="n">
         <v>32</v>
       </c>
       <c r="AO13" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT13" t="n">
         <v>14.5</v>
       </c>
-      <c r="AP13" t="n">
-        <v>16</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>14</v>
-      </c>
       <c r="AU13" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
         <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AY13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BC13" t="n">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="BD13" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BF13" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BG13" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="n">
         <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3840,13 +3840,13 @@
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>5.4</v>
@@ -3855,7 +3855,7 @@
         <v>4.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW13" t="n">
         <v>11</v>
@@ -3864,7 +3864,7 @@
         <v>27</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -3911,13 +3911,13 @@
         <v>9.4</v>
       </c>
       <c r="H14" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I14" t="n">
         <v>1.4</v>
       </c>
-      <c r="I14" t="n">
-        <v>1.42</v>
-      </c>
       <c r="J14" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K14" t="n">
         <v>5.9</v>
@@ -3944,7 +3944,7 @@
         <v>1.65</v>
       </c>
       <c r="S14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
         <v>1.88</v>
@@ -3953,13 +3953,13 @@
         <v>2.06</v>
       </c>
       <c r="V14" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Y14" t="n">
         <v>11</v>
@@ -3977,46 +3977,46 @@
         <v>13</v>
       </c>
       <c r="AD14" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AF14" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AG14" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI14" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AJ14" t="n">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="AK14" t="n">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM14" t="n">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="AN14" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AO14" t="n">
         <v>5</v>
       </c>
       <c r="AP14" t="n">
-        <v>18.5</v>
+        <v>22</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR14" t="n">
         <v>8.6</v>
@@ -4025,7 +4025,7 @@
         <v>11</v>
       </c>
       <c r="AT14" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="AU14" t="n">
         <v>11.5</v>
@@ -4040,31 +4040,31 @@
         <v>34</v>
       </c>
       <c r="AY14" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="AZ14" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="BB14" t="n">
-        <v>11</v>
+        <v>16.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BD14" t="n">
-        <v>10.5</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
-        <v>10.5</v>
+        <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BH14" t="n">
         <v>4.7</v>
@@ -4106,13 +4106,13 @@
         <v>4.2</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="BV14" t="n">
         <v>8.4</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.6</v>
+        <v>6</v>
       </c>
       <c r="BX14" t="n">
         <v>22</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -4159,166 +4159,166 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
         <v>1.38</v>
       </c>
       <c r="M15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="O15" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S15" t="n">
         <v>3.35</v>
       </c>
       <c r="T15" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U15" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
-        <v>970</v>
+        <v>90</v>
       </c>
       <c r="Y15" t="n">
-        <v>21</v>
+        <v>950</v>
       </c>
       <c r="Z15" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AA15" t="n">
-        <v>150</v>
+        <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AC15" t="n">
         <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>25</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
-        <v>85</v>
+        <v>700</v>
       </c>
       <c r="AF15" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>36</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>60</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>700</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>970</v>
       </c>
-      <c r="AG15" t="n">
-        <v>970</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>85</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>22</v>
-      </c>
       <c r="AK15" t="n">
-        <v>24</v>
+        <v>500</v>
       </c>
       <c r="AL15" t="n">
-        <v>46</v>
+        <v>500</v>
       </c>
       <c r="AM15" t="n">
-        <v>140</v>
+        <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>970</v>
+        <v>29</v>
       </c>
       <c r="AO15" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>3.75</v>
+        <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="AR15" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="AV15" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ15" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BA15" t="n">
         <v>4.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BC15" t="n">
-        <v>4</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>4.3</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
         <v>4.6</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BH15" t="n">
         <v>3.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>
@@ -4413,22 +4413,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H16" t="n">
-        <v>2.56</v>
+        <v>2.68</v>
       </c>
       <c r="I16" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="J16" t="n">
         <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.5</v>
@@ -4449,7 +4449,7 @@
         <v>2.54</v>
       </c>
       <c r="R16" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="S16" t="n">
         <v>5.2</v>
@@ -4461,10 +4461,10 @@
         <v>1.85</v>
       </c>
       <c r="V16" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4551,7 +4551,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>18.5</v>
+        <v>5.4</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 16:36:21</t>
+          <t>2026-06-22 19:18:26</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,22 +857,22 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.84</v>
+        <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="H2" t="n">
         <v>4.5</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L2" t="n">
         <v>1.39</v>
@@ -887,28 +887,28 @@
         <v>1.37</v>
       </c>
       <c r="P2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S2" t="n">
         <v>3.6</v>
       </c>
       <c r="T2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U2" t="n">
         <v>1.9</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
       <c r="V2" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W2" t="n">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="X2" t="n">
         <v>27</v>
@@ -938,7 +938,7 @@
         <v>500</v>
       </c>
       <c r="AG2" t="n">
-        <v>36</v>
+        <v>500</v>
       </c>
       <c r="AH2" t="n">
         <v>950</v>
@@ -965,58 +965,58 @@
         <v>700</v>
       </c>
       <c r="AP2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BE2" t="n">
         <v>3.8</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF2" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="BG2" t="n">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="BH2" t="n">
         <v>3.65</v>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1117,19 +1117,19 @@
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I3" t="n">
         <v>2.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="M3" t="n">
         <v>1.15</v>
@@ -1222,7 +1222,7 @@
         <v>5.8</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AR3" t="n">
         <v>5.5</v>
@@ -1231,10 +1231,10 @@
         <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AV3" t="n">
         <v>5.5</v>
@@ -1249,25 +1249,25 @@
         <v>6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>6.4</v>
       </c>
       <c r="BA3" t="n">
         <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC3" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BD3" t="n">
         <v>8</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BE3" t="n">
         <v>8.4</v>
       </c>
-      <c r="BE3" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BF3" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="BG3" t="n">
         <v>7.2</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
         <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
@@ -1410,7 +1410,7 @@
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1491,10 +1491,10 @@
         <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AX4" t="n">
         <v>13.5</v>
@@ -1512,7 +1512,7 @@
         <v>14.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>9.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BD4" t="n">
         <v>28</v>
@@ -1524,7 +1524,7 @@
         <v>32</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BH4" t="n">
         <v>2.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1622,7 @@
         <v>3.9</v>
       </c>
       <c r="G5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
         <v>2.12</v>
@@ -1634,7 +1634,7 @@
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L5" t="n">
         <v>1.52</v>
@@ -1643,28 +1643,28 @@
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="P5" t="n">
         <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="V5" t="n">
         <v>1.81</v>
@@ -1727,7 +1727,7 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AQ5" t="n">
         <v>4.2</v>
@@ -1745,19 +1745,19 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW5" t="n">
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BA5" t="n">
         <v>7.6</v>
@@ -1775,31 +1775,31 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG5" t="n">
         <v>5.9</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.78</v>
+        <v>1.35</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="BO5" t="n">
         <v>5.4</v>
@@ -1808,7 +1808,7 @@
         <v>1000</v>
       </c>
       <c r="BQ5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BR5" t="n">
         <v>1000</v>
@@ -1820,7 +1820,7 @@
         <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>3.25</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="K6" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="O6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="S6" t="n">
         <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="U6" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V6" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="W6" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1939,22 +1939,22 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AD6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AE6" t="n">
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>500</v>
+        <v>950</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1963,22 +1963,22 @@
         <v>500</v>
       </c>
       <c r="AJ6" t="n">
-        <v>900</v>
+        <v>500</v>
       </c>
       <c r="AK6" t="n">
         <v>500</v>
       </c>
       <c r="AL6" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AM6" t="n">
-        <v>500</v>
+        <v>580</v>
       </c>
       <c r="AN6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AO6" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="AP6" t="n">
         <v>4.4</v>
@@ -1987,10 +1987,10 @@
         <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>5</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>5</v>
+        <v>3.9</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1999,104 +1999,104 @@
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.2</v>
+        <v>3.9</v>
       </c>
       <c r="AX6" t="n">
-        <v>5</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>4.8</v>
+        <v>5.8</v>
       </c>
       <c r="BA6" t="n">
-        <v>4.7</v>
+        <v>3.15</v>
       </c>
       <c r="BB6" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC6" t="n">
         <v>5.7</v>
       </c>
-      <c r="BC6" t="n">
-        <v>5.5</v>
-      </c>
       <c r="BD6" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="BE6" t="n">
         <v>4</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>5.8</v>
+        <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.04</v>
+        <v>1.17</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.38</v>
+        <v>1.11</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.35</v>
+        <v>3.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.38</v>
+        <v>1.13</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="G7" t="n">
         <v>6.4</v>
@@ -2136,7 +2136,7 @@
         <v>1.78</v>
       </c>
       <c r="I7" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
         <v>3.2</v>
@@ -2145,61 +2145,61 @@
         <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.5</v>
+        <v>2.72</v>
       </c>
       <c r="O7" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.59</v>
+        <v>1.63</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.18</v>
+        <v>1.23</v>
       </c>
       <c r="S7" t="n">
-        <v>3.05</v>
+        <v>1.23</v>
       </c>
       <c r="T7" t="n">
-        <v>1.11</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="V7" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="X7" t="n">
-        <v>950</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>970</v>
+        <v>48</v>
       </c>
       <c r="Z7" t="n">
-        <v>500</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AC7" t="n">
-        <v>950</v>
+        <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>950</v>
+        <v>36</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2211,7 +2211,7 @@
         <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2232,10 +2232,10 @@
         <v>700</v>
       </c>
       <c r="AO7" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -2244,55 +2244,55 @@
         <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1.59</v>
+        <v>5.7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.55</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
         <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>1.54</v>
+        <v>4.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>1.59</v>
+        <v>5.9</v>
       </c>
       <c r="AX7" t="n">
-        <v>1.61</v>
+        <v>3.45</v>
       </c>
       <c r="AY7" t="n">
-        <v>1.6</v>
+        <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>1.58</v>
+        <v>3.75</v>
       </c>
       <c r="BA7" t="n">
-        <v>1.61</v>
+        <v>2.38</v>
       </c>
       <c r="BB7" t="n">
-        <v>1.62</v>
+        <v>2.42</v>
       </c>
       <c r="BC7" t="n">
-        <v>1.62</v>
+        <v>2.46</v>
       </c>
       <c r="BD7" t="n">
-        <v>1.62</v>
+        <v>2.44</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.62</v>
+        <v>2.8</v>
       </c>
       <c r="BF7" t="n">
-        <v>1.62</v>
+        <v>2.78</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.6</v>
+        <v>5.6</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
@@ -2304,31 +2304,31 @@
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.4</v>
+        <v>1.79</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>1.4</v>
+        <v>3.05</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
@@ -2340,17 +2340,17 @@
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.4</v>
+        <v>1.04</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
         <v>3.55</v>
@@ -2408,7 +2408,7 @@
         <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P8" t="n">
         <v>1.9</v>
@@ -2459,7 +2459,7 @@
         <v>38</v>
       </c>
       <c r="AF8" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AG8" t="n">
         <v>12</v>
@@ -2501,7 +2501,7 @@
         <v>27</v>
       </c>
       <c r="AT8" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2635,7 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G9" t="n">
         <v>1.84</v>
@@ -2644,10 +2644,10 @@
         <v>5.1</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K9" t="n">
         <v>3.9</v>
@@ -2659,7 +2659,7 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
         <v>1.32</v>
@@ -2674,13 +2674,13 @@
         <v>1.37</v>
       </c>
       <c r="S9" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
         <v>1.89</v>
       </c>
       <c r="U9" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
@@ -2704,7 +2704,7 @@
         <v>8.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
         <v>24</v>
@@ -2716,7 +2716,7 @@
         <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH9" t="n">
         <v>23</v>
@@ -2743,7 +2743,7 @@
         <v>700</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>15.5</v>
@@ -2752,7 +2752,7 @@
         <v>23</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
         <v>8</v>
@@ -2770,10 +2770,10 @@
         <v>9.6</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA9" t="n">
         <v>34</v>
@@ -2794,7 +2794,7 @@
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="BH9" t="n">
         <v>3.4</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
@@ -2901,10 +2901,10 @@
         <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.28</v>
@@ -2970,7 +2970,7 @@
         <v>11.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AH10" t="n">
         <v>19</v>
@@ -3006,7 +3006,7 @@
         <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT10" t="n">
         <v>8.800000000000001</v>
@@ -3018,7 +3018,7 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3030,7 +3030,7 @@
         <v>16.5</v>
       </c>
       <c r="BA10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3042,13 +3042,13 @@
         <v>23</v>
       </c>
       <c r="BE10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="H11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
@@ -3158,7 +3158,7 @@
         <v>4.7</v>
       </c>
       <c r="K11" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="L11" t="n">
         <v>1.3</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -3403,31 +3403,31 @@
         <v>1.59</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J12" t="n">
         <v>4.5</v>
       </c>
       <c r="K12" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L12" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
         <v>1.71</v>
@@ -3436,7 +3436,7 @@
         <v>1.51</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="T12" t="n">
         <v>1.83</v>
@@ -3568,7 +3568,7 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>8</v>
+        <v>5.1</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
@@ -3580,13 +3580,13 @@
         <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="BP12" t="n">
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>7.8</v>
+        <v>5.1</v>
       </c>
       <c r="BR12" t="n">
         <v>24</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -3660,7 +3660,7 @@
         <v>2.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
         <v>3.85</v>
@@ -3681,7 +3681,7 @@
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q13" t="n">
         <v>1.76</v>
@@ -3699,13 +3699,13 @@
         <v>2.38</v>
       </c>
       <c r="V13" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="W13" t="n">
         <v>1.38</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y13" t="n">
         <v>12.5</v>
@@ -3777,7 +3777,7 @@
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW13" t="n">
         <v>18.5</v>
@@ -3789,7 +3789,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>27</v>
@@ -3807,7 +3807,7 @@
         <v>34</v>
       </c>
       <c r="BF13" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="BG13" t="n">
         <v>11.5</v>
@@ -3822,13 +3822,13 @@
         <v>9.4</v>
       </c>
       <c r="BK13" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3840,16 +3840,16 @@
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BU13" t="n">
         <v>4.5</v>
@@ -3864,7 +3864,7 @@
         <v>27</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="H14" t="n">
         <v>1.39</v>
@@ -3935,22 +3935,22 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="Q14" t="n">
         <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S14" t="n">
         <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="U14" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
         <v>3.5</v>
@@ -3968,7 +3968,7 @@
         <v>9.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AB14" t="n">
         <v>36</v>
@@ -3998,7 +3998,7 @@
         <v>320</v>
       </c>
       <c r="AK14" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AL14" t="n">
         <v>100</v>
@@ -4010,10 +4010,10 @@
         <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AP14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ14" t="n">
         <v>9.800000000000001</v>
@@ -4049,13 +4049,13 @@
         <v>26</v>
       </c>
       <c r="BB14" t="n">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC14" t="n">
         <v>40</v>
       </c>
       <c r="BD14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -4162,16 +4162,16 @@
         <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
         <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -4183,22 +4183,22 @@
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.65</v>
+        <v>1.77</v>
       </c>
       <c r="O15" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="R15" t="n">
         <v>1.3</v>
       </c>
-      <c r="P15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.35</v>
-      </c>
       <c r="S15" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
         <v>1.89</v>
@@ -4210,10 +4210,10 @@
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
@@ -4231,7 +4231,7 @@
         <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AE15" t="n">
         <v>700</v>
@@ -4261,7 +4261,7 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>13.5</v>
       </c>
       <c r="AO15" t="n">
         <v>700</v>
@@ -4279,46 +4279,46 @@
         <v>6.2</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AZ15" t="n">
         <v>5.1</v>
       </c>
       <c r="BA15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE15" t="n">
         <v>4.5</v>
       </c>
-      <c r="BB15" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD15" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BE15" t="n">
-        <v>4.6</v>
-      </c>
       <c r="BF15" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BG15" t="n">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BH15" t="n">
         <v>3.6</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
         <v>3.3</v>
@@ -4428,7 +4428,7 @@
         <v>3.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="L16" t="n">
         <v>1.5</v>
@@ -4464,7 +4464,7 @@
         <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4524,7 +4524,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AR16" t="n">
         <v>12.5</v>
@@ -4575,7 +4575,7 @@
         <v>5.8</v>
       </c>
       <c r="BH16" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="BI16" t="n">
         <v>2.54</v>
@@ -4590,10 +4590,10 @@
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BN16" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BO16" t="n">
         <v>5.3</v>
@@ -4608,19 +4608,19 @@
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BT16" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BU16" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV16" t="n">
         <v>1000</v>
       </c>
       <c r="BW16" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BX16" t="n">
         <v>1000</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 19:18:26</t>
+          <t>2026-06-22 21:25:39</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -860,58 +860,58 @@
         <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="P2" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="R2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6</v>
+        <v>2.96</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U2" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.9</v>
       </c>
-      <c r="V2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.98</v>
-      </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -923,19 +923,19 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>9.4</v>
+        <v>14</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.800000000000001</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AE2" t="n">
         <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG2" t="n">
         <v>500</v>
@@ -959,128 +959,128 @@
         <v>580</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="AO2" t="n">
         <v>700</v>
       </c>
       <c r="AP2" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AQ2" t="n">
         <v>3.25</v>
       </c>
-      <c r="AQ2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="AR2" t="n">
-        <v>3.55</v>
+        <v>2.18</v>
       </c>
       <c r="AS2" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU2" t="n">
         <v>3.85</v>
       </c>
-      <c r="AT2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.15</v>
-      </c>
       <c r="AV2" t="n">
-        <v>3.65</v>
+        <v>2.16</v>
       </c>
       <c r="AW2" t="n">
-        <v>3.2</v>
+        <v>2.06</v>
       </c>
       <c r="AX2" t="n">
-        <v>3.15</v>
+        <v>5.2</v>
       </c>
       <c r="AY2" t="n">
-        <v>3.4</v>
+        <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>3.3</v>
+        <v>2.06</v>
       </c>
       <c r="BB2" t="n">
-        <v>3.85</v>
+        <v>4.6</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="BD2" t="n">
         <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="BF2" t="n">
-        <v>3.4</v>
+        <v>2.54</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.75</v>
+        <v>2.26</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.65</v>
+        <v>6.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.42</v>
+        <v>1.08</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>1.66</v>
+        <v>2.34</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.42</v>
+        <v>1.04</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.39</v>
+        <v>1.04</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.42</v>
+        <v>1.05</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="I3" t="n">
         <v>2.56</v>
@@ -1126,13 +1126,13 @@
         <v>2.72</v>
       </c>
       <c r="K3" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="M3" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="N3" t="n">
         <v>2.24</v>
@@ -1165,7 +1165,7 @@
         <v>1.26</v>
       </c>
       <c r="X3" t="n">
-        <v>7.6</v>
+        <v>14</v>
       </c>
       <c r="Y3" t="n">
         <v>7.2</v>
@@ -1186,7 +1186,7 @@
         <v>970</v>
       </c>
       <c r="AE3" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AF3" t="n">
         <v>500</v>
@@ -1228,49 +1228,49 @@
         <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AT3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AU3" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="AV3" t="n">
         <v>5.5</v>
       </c>
       <c r="AW3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.4</v>
+        <v>5.5</v>
       </c>
       <c r="BA3" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BB3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BC3" t="n">
         <v>8</v>
       </c>
-      <c r="BC3" t="n">
-        <v>7.8</v>
-      </c>
       <c r="BD3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF3" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BH3" t="n">
         <v>2.6</v>
@@ -1282,16 +1282,16 @@
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>1.71</v>
+        <v>2.04</v>
       </c>
       <c r="BN3" t="n">
-        <v>30</v>
+        <v>7.4</v>
       </c>
       <c r="BO3" t="n">
         <v>5.4</v>
@@ -1300,16 +1300,16 @@
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.68</v>
+        <v>2.14</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="BU3" t="n">
         <v>4</v>
@@ -1318,23 +1318,23 @@
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.58</v>
+        <v>2.08</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="H4" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
         <v>3.6</v>
@@ -1380,7 +1380,7 @@
         <v>2.88</v>
       </c>
       <c r="K4" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
         <v>1.52</v>
@@ -1389,7 +1389,7 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O4" t="n">
         <v>1.5</v>
@@ -1410,7 +1410,7 @@
         <v>1.98</v>
       </c>
       <c r="U4" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="V4" t="n">
         <v>1.39</v>
@@ -1419,7 +1419,7 @@
         <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="Y4" t="n">
         <v>10.5</v>
@@ -1473,7 +1473,7 @@
         <v>600</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.6</v>
+        <v>4.2</v>
       </c>
       <c r="AQ4" t="n">
         <v>8</v>
@@ -1482,22 +1482,22 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="AU4" t="n">
         <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX4" t="n">
-        <v>13.5</v>
+        <v>5.9</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
@@ -1506,25 +1506,25 @@
         <v>17.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>14.5</v>
+        <v>7.4</v>
       </c>
       <c r="BC4" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>28</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF4" t="n">
-        <v>32</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BH4" t="n">
         <v>2.9</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -1619,40 +1619,40 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I5" t="n">
         <v>2.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="O5" t="n">
         <v>1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
@@ -1661,19 +1661,19 @@
         <v>5</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="V5" t="n">
         <v>1.81</v>
       </c>
       <c r="W5" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="Y5" t="n">
         <v>15.5</v>
@@ -1727,16 +1727,16 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="AT5" t="n">
         <v>6.4</v>
@@ -1745,13 +1745,13 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="AW5" t="n">
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
@@ -1763,10 +1763,10 @@
         <v>7.6</v>
       </c>
       <c r="BB5" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC5" t="n">
         <v>8</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>7.8</v>
       </c>
       <c r="BD5" t="n">
         <v>7.8</v>
@@ -1778,7 +1778,7 @@
         <v>5.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="BH5" t="n">
         <v>2.9</v>
@@ -1790,13 +1790,13 @@
         <v>1000</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BL5" t="n">
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="BN5" t="n">
         <v>1000</v>
@@ -1814,7 +1814,7 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>4.9</v>
+        <v>1.48</v>
       </c>
       <c r="BT5" t="n">
         <v>5</v>
@@ -1838,11 +1838,11 @@
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -1876,13 +1876,13 @@
         <v>2.24</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="H6" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J6" t="n">
         <v>2.96</v>
@@ -1891,22 +1891,22 @@
         <v>3.6</v>
       </c>
       <c r="L6" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>2.76</v>
+        <v>1.9</v>
       </c>
       <c r="O6" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="P6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
@@ -1915,10 +1915,10 @@
         <v>1.05</v>
       </c>
       <c r="T6" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="U6" t="n">
-        <v>1.87</v>
+        <v>1.93</v>
       </c>
       <c r="V6" t="n">
         <v>1.33</v>
@@ -1939,10 +1939,10 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>19</v>
+        <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1954,7 +1954,7 @@
         <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>950</v>
+        <v>500</v>
       </c>
       <c r="AH6" t="n">
         <v>950</v>
@@ -1966,7 +1966,7 @@
         <v>500</v>
       </c>
       <c r="AK6" t="n">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="AL6" t="n">
         <v>450</v>
@@ -1987,10 +1987,10 @@
         <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1999,37 +1999,37 @@
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.9</v>
+        <v>3.35</v>
       </c>
       <c r="AX6" t="n">
-        <v>7.6</v>
+        <v>5.7</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.8</v>
+        <v>5.3</v>
       </c>
       <c r="BA6" t="n">
-        <v>3.15</v>
+        <v>2.22</v>
       </c>
       <c r="BB6" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="BC6" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="BE6" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
@@ -2038,7 +2038,7 @@
         <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
@@ -2050,53 +2050,53 @@
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.17</v>
+        <v>1.3</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.11</v>
+        <v>1.23</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -2127,64 +2127,64 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="G7" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="H7" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L7" t="n">
         <v>1.47</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.07</v>
       </c>
       <c r="N7" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="O7" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="R7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S7" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="T7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V7" t="n">
         <v>2.02</v>
       </c>
-      <c r="U7" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="V7" t="n">
-        <v>2</v>
-      </c>
       <c r="W7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="Y7" t="n">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="Z7" t="n">
         <v>40</v>
@@ -2193,7 +2193,7 @@
         <v>900</v>
       </c>
       <c r="AB7" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AC7" t="n">
         <v>16</v>
@@ -2211,7 +2211,7 @@
         <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2235,7 +2235,7 @@
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.3</v>
+        <v>5.9</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -2244,46 +2244,46 @@
         <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>6</v>
       </c>
       <c r="AU7" t="n">
         <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.9</v>
+        <v>4.3</v>
       </c>
       <c r="AX7" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="AY7" t="n">
         <v>5.7</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.38</v>
+        <v>2.84</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.46</v>
+        <v>2.88</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.44</v>
+        <v>2.82</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
@@ -2350,7 +2350,7 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
         <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
         <v>3.05</v>
@@ -2393,7 +2393,7 @@
         <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>3.55</v>
@@ -2423,16 +2423,16 @@
         <v>3.65</v>
       </c>
       <c r="T8" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="U8" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V8" t="n">
         <v>1.47</v>
       </c>
       <c r="W8" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2441,7 +2441,7 @@
         <v>12.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AA8" t="n">
         <v>55</v>
@@ -2465,7 +2465,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI8" t="n">
         <v>50</v>
@@ -2480,7 +2480,7 @@
         <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>500</v>
+        <v>320</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -2489,7 +2489,7 @@
         <v>36</v>
       </c>
       <c r="AP8" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2525,7 +2525,7 @@
         <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
         <v>19.5</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="I9" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="J9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K9" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
@@ -2662,115 +2662,115 @@
         <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="R9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="X9" t="n">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="Z9" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AA9" t="n">
-        <v>900</v>
+        <v>140</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AE9" t="n">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
       </c>
       <c r="AG9" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AI9" t="n">
-        <v>190</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM9" t="n">
         <v>580</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>12.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>700</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
         <v>12.5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT9" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="AX9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY9" t="n">
         <v>9.6</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>8.6</v>
       </c>
       <c r="AZ9" t="n">
         <v>17</v>
@@ -2779,16 +2779,16 @@
         <v>34</v>
       </c>
       <c r="BB9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC9" t="n">
         <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="BF9" t="n">
         <v>10.5</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BN9" t="n">
         <v>4.4</v>
@@ -2830,13 +2830,13 @@
         <v>28</v>
       </c>
       <c r="BS9" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>7.4</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -2901,7 +2901,7 @@
         <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
@@ -2919,7 +2919,7 @@
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q10" t="n">
         <v>1.74</v>
@@ -2934,7 +2934,7 @@
         <v>1.76</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.2</v>
@@ -2946,7 +2946,7 @@
         <v>19.5</v>
       </c>
       <c r="Y10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z10" t="n">
         <v>60</v>
@@ -3000,16 +3000,16 @@
         <v>17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AR10" t="n">
         <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AT10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3018,7 +3018,7 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
@@ -3027,10 +3027,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ10" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BB10" t="n">
         <v>15.5</v>
@@ -3039,16 +3039,16 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -3146,10 +3146,10 @@
         <v>1.4</v>
       </c>
       <c r="G11" t="n">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="H11" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
         <v>11</v>
@@ -3173,7 +3173,7 @@
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="Q11" t="n">
         <v>1.79</v>
@@ -3299,10 +3299,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BF11" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG11" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BH11" t="n">
         <v>3.8</v>
@@ -3366,7 +3366,7 @@
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -3397,22 +3397,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="G12" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K12" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
         <v>1.31</v>
@@ -3421,16 +3421,16 @@
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R12" t="n">
         <v>1.51</v>
@@ -3439,7 +3439,7 @@
         <v>2.8</v>
       </c>
       <c r="T12" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="U12" t="n">
         <v>2.1</v>
@@ -3448,13 +3448,13 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Y12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="Z12" t="n">
         <v>60</v>
@@ -3466,7 +3466,7 @@
         <v>10.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD12" t="n">
         <v>25</v>
@@ -3475,13 +3475,13 @@
         <v>700</v>
       </c>
       <c r="AF12" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG12" t="n">
         <v>10</v>
       </c>
-      <c r="AG12" t="n">
-        <v>10.5</v>
-      </c>
       <c r="AH12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI12" t="n">
         <v>390</v>
@@ -3499,13 +3499,13 @@
         <v>700</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AO12" t="n">
         <v>700</v>
       </c>
       <c r="AP12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
         <v>21</v>
@@ -3514,31 +3514,31 @@
         <v>42</v>
       </c>
       <c r="AS12" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV12" t="n">
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="AX12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY12" t="n">
         <v>9</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,16 +3547,16 @@
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="BE12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -3663,10 +3663,10 @@
         <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="K13" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.35</v>
@@ -3693,7 +3693,7 @@
         <v>2.92</v>
       </c>
       <c r="T13" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="U13" t="n">
         <v>2.38</v>
@@ -3705,10 +3705,10 @@
         <v>1.38</v>
       </c>
       <c r="X13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="Y13" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="Z13" t="n">
         <v>15</v>
@@ -3720,7 +3720,7 @@
         <v>18.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AD13" t="n">
         <v>11</v>
@@ -3783,7 +3783,7 @@
         <v>18.5</v>
       </c>
       <c r="AX13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY13" t="n">
         <v>13.5</v>
@@ -3792,7 +3792,7 @@
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB13" t="n">
         <v>50</v>
@@ -3804,19 +3804,19 @@
         <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="BF13" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BH13" t="n">
         <v>3.95</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
         <v>9.4</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="H14" t="n">
         <v>1.39</v>
@@ -3917,7 +3917,7 @@
         <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K14" t="n">
         <v>5.9</v>
@@ -3944,7 +3944,7 @@
         <v>1.66</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.87</v>
@@ -3998,7 +3998,7 @@
         <v>320</v>
       </c>
       <c r="AK14" t="n">
-        <v>260</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="n">
         <v>100</v>
@@ -4055,7 +4055,7 @@
         <v>40</v>
       </c>
       <c r="BD14" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -4162,7 +4162,7 @@
         <v>1.7</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="H15" t="n">
         <v>5.1</v>
@@ -4171,7 +4171,7 @@
         <v>6.2</v>
       </c>
       <c r="J15" t="n">
-        <v>3.7</v>
+        <v>3.95</v>
       </c>
       <c r="K15" t="n">
         <v>4.3</v>
@@ -4210,7 +4210,7 @@
         <v>1.2</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="X15" t="n">
         <v>29</v>
@@ -4231,7 +4231,7 @@
         <v>10.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>500</v>
+        <v>75</v>
       </c>
       <c r="AE15" t="n">
         <v>700</v>
@@ -4276,25 +4276,25 @@
         <v>5.6</v>
       </c>
       <c r="AS15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AT15" t="n">
         <v>3.65</v>
       </c>
       <c r="AU15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AW15" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AX15" t="n">
         <v>4</v>
       </c>
       <c r="AY15" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="AZ15" t="n">
         <v>5.1</v>
@@ -4306,13 +4306,13 @@
         <v>4.8</v>
       </c>
       <c r="BC15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BE15" t="n">
-        <v>4.5</v>
+        <v>5.9</v>
       </c>
       <c r="BF15" t="n">
         <v>4.4</v>
@@ -4382,7 +4382,7 @@
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>
@@ -4413,10 +4413,10 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G16" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="H16" t="n">
         <v>2.68</v>
@@ -4425,10 +4425,10 @@
         <v>2.78</v>
       </c>
       <c r="J16" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="K16" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L16" t="n">
         <v>1.5</v>
@@ -4464,7 +4464,7 @@
         <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4551,7 +4551,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.4</v>
+        <v>19</v>
       </c>
       <c r="BA16" t="n">
         <v>6</v>
@@ -4569,10 +4569,10 @@
         <v>6.4</v>
       </c>
       <c r="BF16" t="n">
+        <v>46</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>5.8</v>
       </c>
       <c r="BH16" t="n">
         <v>2.76</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 21:25:39</t>
+          <t>2026-06-22 23:32:32</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -860,58 +860,58 @@
         <v>1.91</v>
       </c>
       <c r="G2" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="I2" t="n">
-        <v>5.6</v>
+        <v>5.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="M2" t="n">
         <v>1.08</v>
       </c>
       <c r="N2" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.02</v>
+        <v>2.12</v>
       </c>
       <c r="R2" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S2" t="n">
-        <v>2.96</v>
+        <v>3.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="U2" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="V2" t="n">
         <v>1.24</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="X2" t="n">
-        <v>90</v>
+        <v>27</v>
       </c>
       <c r="Y2" t="n">
         <v>970</v>
@@ -923,10 +923,10 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>14</v>
+        <v>8.4</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="n">
         <v>970</v>
@@ -968,73 +968,73 @@
         <v>5.7</v>
       </c>
       <c r="AQ2" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="AS2" t="n">
-        <v>2.28</v>
+        <v>5.3</v>
       </c>
       <c r="AT2" t="n">
-        <v>3.7</v>
+        <v>5.7</v>
       </c>
       <c r="AU2" t="n">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.16</v>
+        <v>7.2</v>
       </c>
       <c r="AW2" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="AX2" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
       <c r="AY2" t="n">
         <v>4.8</v>
       </c>
       <c r="AZ2" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>2.06</v>
+        <v>5.1</v>
       </c>
       <c r="BB2" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BC2" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD2" t="n">
         <v>3.6</v>
       </c>
       <c r="BE2" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="BH2" t="n">
         <v>6.2</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
         <v>1000</v>
       </c>
       <c r="BK2" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>1.04</v>
+        <v>1.2</v>
       </c>
       <c r="BN2" t="n">
         <v>1000</v>
@@ -1046,41 +1046,41 @@
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.05</v>
+        <v>1.21</v>
       </c>
       <c r="BT2" t="n">
         <v>1000</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.05</v>
+        <v>1.25</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
         <v>4.8</v>
       </c>
       <c r="H3" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="I3" t="n">
         <v>2.56</v>
@@ -1126,25 +1126,25 @@
         <v>2.72</v>
       </c>
       <c r="K3" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Q3" t="n">
         <v>3.05</v>
-      </c>
-      <c r="L3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M3" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.96</v>
       </c>
       <c r="R3" t="n">
         <v>1.16</v>
@@ -1153,19 +1153,19 @@
         <v>6.4</v>
       </c>
       <c r="T3" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V3" t="n">
         <v>1.64</v>
       </c>
       <c r="W3" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X3" t="n">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="Y3" t="n">
         <v>7.2</v>
@@ -1177,13 +1177,13 @@
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC3" t="n">
         <v>8</v>
       </c>
       <c r="AD3" t="n">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AE3" t="n">
         <v>85</v>
@@ -1219,7 +1219,7 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AQ3" t="n">
         <v>5.6</v>
@@ -1228,7 +1228,7 @@
         <v>5.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
         <v>4.9</v>
@@ -1243,31 +1243,31 @@
         <v>7.2</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AY3" t="n">
-        <v>6.2</v>
+        <v>16</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="BA3" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BD3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BE3" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BF3" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG3" t="n">
         <v>7.4</v>
@@ -1276,65 +1276,65 @@
         <v>2.6</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ3" t="n">
         <v>1000</v>
       </c>
       <c r="BK3" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BO3" t="n">
         <v>5.7</v>
       </c>
-      <c r="BL3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="BN3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BO3" t="n">
-        <v>5.4</v>
-      </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>2.14</v>
+        <v>4.4</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>2.08</v>
+        <v>4.1</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J4" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="K4" t="n">
         <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="M4" t="n">
         <v>1.11</v>
@@ -1392,88 +1392,88 @@
         <v>2.62</v>
       </c>
       <c r="O4" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="P4" t="n">
         <v>1.54</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.44</v>
+        <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="T4" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4" t="n">
         <v>1.52</v>
       </c>
       <c r="X4" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z4" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="AB4" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="AF4" t="n">
         <v>17.5</v>
       </c>
       <c r="AG4" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AJ4" t="n">
         <v>110</v>
       </c>
       <c r="AK4" t="n">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="AL4" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>500</v>
+        <v>110</v>
       </c>
       <c r="AO4" t="n">
-        <v>600</v>
+        <v>150</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ4" t="n">
         <v>8</v>
@@ -1482,70 +1482,70 @@
         <v>17</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.4</v>
+        <v>8.4</v>
       </c>
       <c r="AT4" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
         <v>5.9</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.1</v>
+        <v>12</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="AX4" t="n">
-        <v>5.9</v>
+        <v>13.5</v>
       </c>
       <c r="AY4" t="n">
         <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>7.4</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>7.2</v>
+        <v>17</v>
       </c>
       <c r="BD4" t="n">
-        <v>6.4</v>
+        <v>26</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.800000000000001</v>
+        <v>29</v>
       </c>
       <c r="BG4" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.9</v>
+        <v>2.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.5</v>
+        <v>9</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BO4" t="n">
         <v>4.6</v>
@@ -1554,16 +1554,16 @@
         <v>25</v>
       </c>
       <c r="BQ4" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR4" t="n">
         <v>1000</v>
       </c>
       <c r="BS4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BU4" t="n">
         <v>5.1</v>
@@ -1584,11 +1584,11 @@
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -1619,64 +1619,64 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="G5" t="n">
         <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="I5" t="n">
         <v>2.22</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="O5" t="n">
         <v>1.49</v>
       </c>
       <c r="P5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.4</v>
+        <v>2.52</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="T5" t="n">
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="V5" t="n">
         <v>1.81</v>
       </c>
       <c r="W5" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X5" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y5" t="n">
-        <v>15.5</v>
+        <v>7.6</v>
       </c>
       <c r="Z5" t="n">
         <v>970</v>
@@ -1688,10 +1688,10 @@
         <v>29</v>
       </c>
       <c r="AC5" t="n">
-        <v>14</v>
+        <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="AE5" t="n">
         <v>110</v>
@@ -1715,7 +1715,7 @@
         <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>540</v>
+        <v>500</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1727,10 +1727,10 @@
         <v>600</v>
       </c>
       <c r="AP5" t="n">
-        <v>4.7</v>
+        <v>7.4</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
@@ -1745,28 +1745,28 @@
         <v>4.4</v>
       </c>
       <c r="AV5" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
         <v>11.5</v>
       </c>
       <c r="AX5" t="n">
-        <v>7.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY5" t="n">
         <v>11.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BA5" t="n">
+        <v>15</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC5" t="n">
         <v>7.6</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>8</v>
       </c>
       <c r="BD5" t="n">
         <v>7.8</v>
@@ -1775,16 +1775,16 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="BG5" t="n">
         <v>6.8</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="BJ5" t="n">
         <v>1000</v>
@@ -1796,13 +1796,13 @@
         <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>1.46</v>
+        <v>2.94</v>
       </c>
       <c r="BN5" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
       <c r="BP5" t="n">
         <v>1000</v>
@@ -1814,19 +1814,19 @@
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="BT5" t="n">
         <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BV5" t="n">
         <v>1000</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BX5" t="n">
         <v>1000</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -1873,58 +1873,58 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="G6" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="H6" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J6" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K6" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M6" t="n">
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>1.9</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R6" t="n">
         <v>1.24</v>
       </c>
       <c r="S6" t="n">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="V6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W6" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
@@ -1942,7 +1942,7 @@
         <v>500</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,13 +1951,13 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
+        <v>44</v>
+      </c>
+      <c r="AG6" t="n">
         <v>970</v>
       </c>
-      <c r="AG6" t="n">
-        <v>500</v>
-      </c>
       <c r="AH6" t="n">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="AI6" t="n">
         <v>500</v>
@@ -1987,10 +1987,10 @@
         <v>5.1</v>
       </c>
       <c r="AR6" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="AT6" t="n">
         <v>4.9</v>
@@ -1999,37 +1999,37 @@
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AW6" t="n">
-        <v>3.35</v>
+        <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.2</v>
+        <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="BF6" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
@@ -2044,7 +2044,7 @@
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
@@ -2056,13 +2056,13 @@
         <v>1000</v>
       </c>
       <c r="BO6" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="BP6" t="n">
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>1.23</v>
+        <v>2.04</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
@@ -2074,13 +2074,13 @@
         <v>1000</v>
       </c>
       <c r="BU6" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV6" t="n">
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="G7" t="n">
         <v>6.8</v>
@@ -2139,40 +2139,40 @@
         <v>1.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="R7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>1.17</v>
+        <v>4</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
         <v>2.02</v>
@@ -2181,13 +2181,13 @@
         <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>90</v>
+        <v>17</v>
       </c>
       <c r="Y7" t="n">
         <v>27</v>
       </c>
       <c r="Z7" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2199,7 +2199,7 @@
         <v>16</v>
       </c>
       <c r="AD7" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="AE7" t="n">
         <v>500</v>
@@ -2235,7 +2235,7 @@
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>5.9</v>
+        <v>10.5</v>
       </c>
       <c r="AQ7" t="n">
         <v>4.2</v>
@@ -2244,61 +2244,61 @@
         <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT7" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
         <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AW7" t="n">
-        <v>4.3</v>
+        <v>5.3</v>
       </c>
       <c r="AX7" t="n">
         <v>4.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AZ7" t="n">
-        <v>3.7</v>
+        <v>9.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.82</v>
+        <v>3.15</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.86</v>
+        <v>4.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.88</v>
+        <v>3.15</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
@@ -2310,13 +2310,13 @@
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.79</v>
+        <v>3.25</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
@@ -2328,29 +2328,29 @@
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.04</v>
+        <v>1.51</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -2384,22 +2384,22 @@
         <v>2.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="L8" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="M8" t="n">
         <v>1.07</v>
@@ -2408,31 +2408,31 @@
         <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>1.35</v>
       </c>
       <c r="S8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="U8" t="n">
         <v>2.2</v>
       </c>
       <c r="V8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="W8" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X8" t="n">
         <v>14</v>
@@ -2480,7 +2480,7 @@
         <v>44</v>
       </c>
       <c r="AM8" t="n">
-        <v>320</v>
+        <v>110</v>
       </c>
       <c r="AN8" t="n">
         <v>24</v>
@@ -2498,7 +2498,7 @@
         <v>18</v>
       </c>
       <c r="AS8" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AT8" t="n">
         <v>10</v>
@@ -2510,7 +2510,7 @@
         <v>12</v>
       </c>
       <c r="AW8" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="AX8" t="n">
         <v>14</v>
@@ -2525,31 +2525,31 @@
         <v>36</v>
       </c>
       <c r="BB8" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="BD8" t="n">
         <v>34</v>
       </c>
       <c r="BE8" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BF8" t="n">
         <v>19.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="BH8" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BI8" t="n">
         <v>2.66</v>
       </c>
       <c r="BJ8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
         <v>7.2</v>
@@ -2558,7 +2558,7 @@
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BN8" t="n">
         <v>5.7</v>
@@ -2570,13 +2570,13 @@
         <v>20</v>
       </c>
       <c r="BQ8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BR8" t="n">
         <v>34</v>
       </c>
       <c r="BS8" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
@@ -2585,16 +2585,16 @@
         <v>5.3</v>
       </c>
       <c r="BV8" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BX8" t="n">
         <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -2635,22 +2635,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="H9" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="I9" t="n">
         <v>5.3</v>
       </c>
-      <c r="I9" t="n">
-        <v>5.6</v>
-      </c>
       <c r="J9" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="K9" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L9" t="n">
         <v>1.41</v>
@@ -2659,31 +2659,31 @@
         <v>1.07</v>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.99</v>
+        <v>1.97</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>2.16</v>
@@ -2692,25 +2692,25 @@
         <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z9" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AB9" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AC9" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
@@ -2719,10 +2719,10 @@
         <v>10.5</v>
       </c>
       <c r="AH9" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>320</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
@@ -2731,16 +2731,16 @@
         <v>19.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>580</v>
+        <v>390</v>
       </c>
       <c r="AN9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
         <v>12.5</v>
@@ -2752,10 +2752,10 @@
         <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,10 +2764,10 @@
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AX9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AY9" t="n">
         <v>9.6</v>
@@ -2776,37 +2776,37 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="BD9" t="n">
         <v>34</v>
       </c>
-      <c r="BB9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>32</v>
-      </c>
       <c r="BE9" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BF9" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG9" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BK9" t="n">
-        <v>6.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL9" t="n">
         <v>1000</v>
@@ -2815,19 +2815,19 @@
         <v>15</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="BP9" t="n">
         <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BR9" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BS9" t="n">
         <v>10.5</v>
@@ -2836,7 +2836,7 @@
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
@@ -2848,7 +2848,7 @@
         <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -2889,61 +2889,61 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.74</v>
+        <v>1.77</v>
       </c>
       <c r="R10" t="n">
         <v>1.48</v>
       </c>
       <c r="S10" t="n">
-        <v>2.88</v>
+        <v>2.96</v>
       </c>
       <c r="T10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="V10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W10" t="n">
         <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
         <v>22</v>
@@ -2955,7 +2955,7 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC10" t="n">
         <v>9.6</v>
@@ -3006,7 +3006,7 @@
         <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
@@ -3042,13 +3042,13 @@
         <v>24</v>
       </c>
       <c r="BE10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF10" t="n">
         <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>1.47</v>
+        <v>1.33</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="I11" t="n">
-        <v>11</v>
+        <v>15.5</v>
       </c>
       <c r="J11" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
       <c r="K11" t="n">
-        <v>5.3</v>
+        <v>6</v>
       </c>
       <c r="L11" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="M11" t="n">
         <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="Q11" t="n">
         <v>1.79</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="U11" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="V11" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W11" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="X11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Y11" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Z11" t="n">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="AA11" t="n">
-        <v>440</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AD11" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="AE11" t="n">
-        <v>200</v>
+        <v>320</v>
       </c>
       <c r="AF11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AG11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>44</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>250</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>16</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>48</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>260</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>510</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR11" t="n">
         <v>10.5</v>
       </c>
-      <c r="AH11" t="n">
-        <v>30</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>170</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>42</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>210</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>300</v>
-      </c>
-      <c r="AP11" t="n">
+      <c r="AS11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX11" t="n">
         <v>6.4</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>11</v>
+      </c>
+      <c r="BF11" t="n">
         <v>5.2</v>
       </c>
-      <c r="AV11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG11" t="n">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="BH11" t="n">
         <v>3.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="BJ11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>1.64</v>
+        <v>17.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="BO11" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="BR11" t="n">
         <v>27</v>
       </c>
       <c r="BS11" t="n">
-        <v>8.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BT11" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BU11" t="n">
-        <v>6</v>
+        <v>8.4</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>9.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -3403,58 +3403,58 @@
         <v>1.6</v>
       </c>
       <c r="H12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I12" t="n">
         <v>7</v>
       </c>
       <c r="J12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="O12" t="n">
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="R12" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S12" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T12" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="U12" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X12" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="Z12" t="n">
         <v>60</v>
@@ -3472,7 +3472,7 @@
         <v>25</v>
       </c>
       <c r="AE12" t="n">
-        <v>700</v>
+        <v>200</v>
       </c>
       <c r="AF12" t="n">
         <v>10.5</v>
@@ -3481,10 +3481,10 @@
         <v>10</v>
       </c>
       <c r="AH12" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>390</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="n">
         <v>15</v>
@@ -3496,37 +3496,37 @@
         <v>34</v>
       </c>
       <c r="AM12" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AO12" t="n">
-        <v>700</v>
+        <v>95</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ12" t="n">
         <v>21</v>
       </c>
       <c r="AR12" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="AS12" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="AT12" t="n">
         <v>9</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV12" t="n">
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="AX12" t="n">
         <v>9.199999999999999</v>
@@ -3538,7 +3538,7 @@
         <v>17.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="BB12" t="n">
         <v>13</v>
@@ -3547,34 +3547,34 @@
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BF12" t="n">
         <v>6.6</v>
       </c>
       <c r="BG12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BN12" t="n">
         <v>4.4</v>
@@ -3586,10 +3586,10 @@
         <v>10.5</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BR12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BS12" t="n">
         <v>7</v>
@@ -3598,19 +3598,19 @@
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BV12" t="n">
         <v>55</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BX12" t="n">
         <v>1000</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -3651,61 +3651,61 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G13" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="H13" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I13" t="n">
         <v>2.2</v>
       </c>
       <c r="J13" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.75</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.95</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="R13" t="n">
         <v>1.49</v>
       </c>
       <c r="S13" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="V13" t="n">
         <v>1.83</v>
       </c>
       <c r="W13" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="X13" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y13" t="n">
         <v>14</v>
@@ -3732,10 +3732,10 @@
         <v>32</v>
       </c>
       <c r="AG13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>32</v>
@@ -3744,7 +3744,7 @@
         <v>70</v>
       </c>
       <c r="AK13" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AL13" t="n">
         <v>44</v>
@@ -3756,7 +3756,7 @@
         <v>32</v>
       </c>
       <c r="AO13" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AP13" t="n">
         <v>16.5</v>
@@ -3771,7 +3771,7 @@
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
@@ -3789,13 +3789,13 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
       </c>
       <c r="BB13" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BC13" t="n">
         <v>32</v>
@@ -3804,13 +3804,13 @@
         <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="BF13" t="n">
         <v>26</v>
       </c>
       <c r="BG13" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BH13" t="n">
         <v>3.95</v>
@@ -3819,7 +3819,7 @@
         <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
         <v>5.1</v>
@@ -3828,7 +3828,7 @@
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3840,13 +3840,13 @@
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT13" t="n">
         <v>5.3</v>
@@ -3861,10 +3861,10 @@
         <v>11</v>
       </c>
       <c r="BX13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -3917,46 +3917,46 @@
         <v>1.4</v>
       </c>
       <c r="J14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="K14" t="n">
         <v>5.9</v>
       </c>
       <c r="L14" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="M14" t="n">
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="S14" t="n">
         <v>2.4</v>
       </c>
       <c r="T14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U14" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V14" t="n">
         <v>3.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -3965,7 +3965,7 @@
         <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA14" t="n">
         <v>12</v>
@@ -3998,28 +3998,28 @@
         <v>320</v>
       </c>
       <c r="AK14" t="n">
-        <v>130</v>
+        <v>260</v>
       </c>
       <c r="AL14" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AM14" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AN14" t="n">
         <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AP14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AQ14" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AR14" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS14" t="n">
         <v>11</v>
@@ -4037,88 +4037,88 @@
         <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="AY14" t="n">
         <v>29</v>
       </c>
       <c r="AZ14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA14" t="n">
         <v>26</v>
       </c>
       <c r="BB14" t="n">
-        <v>17.5</v>
+        <v>20</v>
       </c>
       <c r="BC14" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="BD14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BE14" t="n">
         <v>40</v>
       </c>
       <c r="BF14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BG14" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="BH14" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="BJ14" t="n">
         <v>11.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL14" t="n">
         <v>1000</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BN14" t="n">
         <v>13</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP14" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BQ14" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BR14" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BW14" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="BX14" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -4159,61 +4159,61 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.7</v>
+        <v>1.78</v>
       </c>
       <c r="G15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="I15" t="n">
-        <v>6.2</v>
+        <v>5.4</v>
       </c>
       <c r="J15" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>1.77</v>
+        <v>3.9</v>
       </c>
       <c r="O15" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="P15" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U15" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="W15" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="X15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="Y15" t="n">
         <v>950</v>
@@ -4228,10 +4228,10 @@
         <v>14</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.5</v>
+        <v>14</v>
       </c>
       <c r="AD15" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE15" t="n">
         <v>700</v>
@@ -4252,7 +4252,7 @@
         <v>970</v>
       </c>
       <c r="AK15" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AL15" t="n">
         <v>500</v>
@@ -4261,7 +4261,7 @@
         <v>580</v>
       </c>
       <c r="AN15" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AO15" t="n">
         <v>700</v>
@@ -4270,61 +4270,61 @@
         <v>4.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>4.9</v>
+        <v>6.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>5.6</v>
+        <v>7.8</v>
       </c>
       <c r="AS15" t="n">
         <v>6</v>
       </c>
       <c r="AT15" t="n">
-        <v>3.65</v>
+        <v>4.4</v>
       </c>
       <c r="AU15" t="n">
-        <v>3.95</v>
+        <v>4.9</v>
       </c>
       <c r="AV15" t="n">
-        <v>5.3</v>
+        <v>4.8</v>
       </c>
       <c r="AW15" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BA15" t="n">
         <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>4.8</v>
+        <v>6.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.9</v>
+        <v>6.4</v>
       </c>
       <c r="BD15" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="BE15" t="n">
-        <v>5.9</v>
+        <v>4.1</v>
       </c>
       <c r="BF15" t="n">
-        <v>4.4</v>
+        <v>5.3</v>
       </c>
       <c r="BG15" t="n">
         <v>6</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="BJ15" t="n">
         <v>1000</v>
@@ -4336,10 +4336,10 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>1.16</v>
+        <v>3.6</v>
       </c>
       <c r="BN15" t="n">
-        <v>23</v>
+        <v>4.7</v>
       </c>
       <c r="BO15" t="n">
         <v>3.2</v>
@@ -4348,41 +4348,41 @@
         <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>2.22</v>
+        <v>5.7</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>1.35</v>
+        <v>3.3</v>
       </c>
       <c r="BT15" t="n">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>1.35</v>
+        <v>3.45</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>1.15</v>
+        <v>3.5</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>
@@ -4413,7 +4413,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
         <v>3.25</v>
@@ -4431,13 +4431,13 @@
         <v>3.2</v>
       </c>
       <c r="L16" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="M16" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="O16" t="n">
         <v>1.51</v>
@@ -4446,13 +4446,13 @@
         <v>1.6</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R16" t="n">
         <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T16" t="n">
         <v>2.08</v>
@@ -4464,7 +4464,7 @@
         <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4482,7 +4482,7 @@
         <v>10.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -4512,10 +4512,10 @@
         <v>80</v>
       </c>
       <c r="AM16" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AN16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AO16" t="n">
         <v>46</v>
@@ -4530,7 +4530,7 @@
         <v>12.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AT16" t="n">
         <v>8</v>
@@ -4542,7 +4542,7 @@
         <v>11</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>17</v>
@@ -4554,22 +4554,22 @@
         <v>19</v>
       </c>
       <c r="BA16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BC16" t="n">
         <v>6</v>
       </c>
-      <c r="BB16" t="n">
-        <v>6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>5.9</v>
-      </c>
       <c r="BD16" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BF16" t="n">
         <v>6.2</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>46</v>
       </c>
       <c r="BG16" t="n">
         <v>6</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-22 23:32:32</t>
+          <t>2026-06-23 01:40:18</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,64 +857,64 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.91</v>
+        <v>1.98</v>
       </c>
       <c r="G2" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
         <v>3.35</v>
       </c>
       <c r="K2" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="L2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="M2" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2" t="n">
         <v>3.3</v>
       </c>
       <c r="O2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="P2" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="R2" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="S2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="T2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="W2" t="n">
         <v>1.92</v>
       </c>
-      <c r="U2" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.94</v>
-      </c>
       <c r="X2" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="Y2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z2" t="n">
         <v>500</v>
@@ -923,37 +923,37 @@
         <v>900</v>
       </c>
       <c r="AB2" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AC2" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD2" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="AE2" t="n">
         <v>700</v>
       </c>
       <c r="AF2" t="n">
-        <v>970</v>
+        <v>40</v>
       </c>
       <c r="AG2" t="n">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>950</v>
+        <v>60</v>
       </c>
       <c r="AI2" t="n">
         <v>700</v>
       </c>
       <c r="AJ2" t="n">
-        <v>900</v>
+        <v>130</v>
       </c>
       <c r="AK2" t="n">
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="AL2" t="n">
-        <v>500</v>
+        <v>180</v>
       </c>
       <c r="AM2" t="n">
         <v>580</v>
@@ -965,122 +965,122 @@
         <v>700</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AR2" t="n">
-        <v>2.42</v>
+        <v>7.8</v>
       </c>
       <c r="AS2" t="n">
         <v>5.3</v>
       </c>
       <c r="AT2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AX2" t="n">
         <v>5.7</v>
       </c>
-      <c r="AU2" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.8</v>
-      </c>
       <c r="AY2" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ2" t="n">
-        <v>4.1</v>
+        <v>9.6</v>
       </c>
       <c r="BA2" t="n">
         <v>5.1</v>
       </c>
       <c r="BB2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>95</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>11</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>120</v>
+      </c>
+      <c r="BN2" t="n">
         <v>4.7</v>
       </c>
-      <c r="BC2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
       <c r="BO2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="BP2" t="n">
         <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>1.21</v>
+        <v>5.8</v>
       </c>
       <c r="BT2" t="n">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BU2" t="n">
-        <v>2.36</v>
+        <v>5.5</v>
       </c>
       <c r="BV2" t="n">
         <v>1000</v>
       </c>
       <c r="BW2" t="n">
-        <v>1.18</v>
+        <v>6</v>
       </c>
       <c r="BX2" t="n">
         <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>1.19</v>
+        <v>2.7</v>
       </c>
       <c r="BZ2" t="n">
         <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>1.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1111,91 +1111,91 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="I3" t="n">
-        <v>2.56</v>
+        <v>2.66</v>
       </c>
       <c r="J3" t="n">
-        <v>2.72</v>
+        <v>2.58</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="N3" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="O3" t="n">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="P3" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="R3" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="S3" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="T3" t="n">
-        <v>2.26</v>
+        <v>1.92</v>
       </c>
       <c r="U3" t="n">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="V3" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="X3" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="AA3" t="n">
         <v>900</v>
       </c>
       <c r="AB3" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>8</v>
+        <v>970</v>
       </c>
       <c r="AD3" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AE3" t="n">
         <v>85</v>
       </c>
       <c r="AF3" t="n">
-        <v>500</v>
+        <v>38</v>
       </c>
       <c r="AG3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH3" t="n">
         <v>950</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>500</v>
       </c>
       <c r="AI3" t="n">
         <v>500</v>
@@ -1219,122 +1219,122 @@
         <v>600</v>
       </c>
       <c r="AP3" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="AQ3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AR3" t="n">
-        <v>5.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7</v>
       </c>
-      <c r="AT3" t="n">
-        <v>4.9</v>
-      </c>
       <c r="AU3" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AV3" t="n">
-        <v>5.5</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>3.6</v>
       </c>
       <c r="AZ3" t="n">
-        <v>6.6</v>
+        <v>3.75</v>
       </c>
       <c r="BA3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>210</v>
+      </c>
+      <c r="BF3" t="n">
         <v>7.8</v>
       </c>
-      <c r="BB3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BG3" t="n">
-        <v>7.4</v>
+        <v>34</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.6</v>
+        <v>2.46</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK3" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3" t="n">
         <v>1000</v>
       </c>
       <c r="BM3" t="n">
-        <v>4.1</v>
+        <v>270</v>
       </c>
       <c r="BN3" t="n">
         <v>7.2</v>
       </c>
       <c r="BO3" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="BP3" t="n">
         <v>1000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BR3" t="n">
         <v>1000</v>
       </c>
       <c r="BS3" t="n">
-        <v>4.4</v>
+        <v>10</v>
       </c>
       <c r="BT3" t="n">
         <v>5.3</v>
       </c>
       <c r="BU3" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="BV3" t="n">
         <v>1000</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BX3" t="n">
         <v>1000</v>
       </c>
       <c r="BY3" t="n">
-        <v>4.4</v>
+        <v>9.6</v>
       </c>
       <c r="BZ3" t="n">
         <v>1000</v>
       </c>
       <c r="CA3" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.5</v>
+        <v>2.92</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>3.55</v>
+        <v>2.92</v>
       </c>
       <c r="J4" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="L4" t="n">
         <v>1.55</v>
@@ -1389,139 +1389,139 @@
         <v>1.11</v>
       </c>
       <c r="N4" t="n">
-        <v>2.62</v>
+        <v>2.72</v>
       </c>
       <c r="O4" t="n">
         <v>1.51</v>
       </c>
       <c r="P4" t="n">
-        <v>1.54</v>
+        <v>1.6</v>
       </c>
       <c r="Q4" t="n">
         <v>2.54</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="S4" t="n">
         <v>5.2</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="U4" t="n">
         <v>1.81</v>
       </c>
       <c r="V4" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="W4" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="X4" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y4" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z4" t="n">
-        <v>22</v>
+        <v>17.5</v>
       </c>
       <c r="AA4" t="n">
-        <v>160</v>
+        <v>80</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.800000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC4" t="n">
         <v>7.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>15.5</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="AF4" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
         <v>23</v>
       </c>
       <c r="AI4" t="n">
-        <v>450</v>
+        <v>160</v>
       </c>
       <c r="AJ4" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AK4" t="n">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="AL4" t="n">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="AM4" t="n">
         <v>500</v>
       </c>
       <c r="AN4" t="n">
-        <v>110</v>
+        <v>500</v>
       </c>
       <c r="AO4" t="n">
         <v>150</v>
       </c>
       <c r="AP4" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AQ4" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.4</v>
+        <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>7</v>
+        <v>7.8</v>
       </c>
       <c r="AU4" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AV4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>32</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AY4" t="n">
         <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
       </c>
       <c r="AZ4" t="n">
         <v>18.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>8.4</v>
+        <v>28</v>
       </c>
       <c r="BB4" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="BC4" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BD4" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>8.4</v>
+        <v>120</v>
       </c>
       <c r="BF4" t="n">
-        <v>29</v>
+        <v>8.6</v>
       </c>
       <c r="BG4" t="n">
         <v>9</v>
@@ -1530,46 +1530,46 @@
         <v>2.84</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BJ4" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BK4" t="n">
-        <v>9</v>
+        <v>5.8</v>
       </c>
       <c r="BL4" t="n">
         <v>1000</v>
       </c>
       <c r="BM4" t="n">
-        <v>9</v>
+        <v>150</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BP4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BU4" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BV4" t="n">
         <v>25</v>
-      </c>
-      <c r="BQ4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BR4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BT4" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BU4" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BV4" t="n">
-        <v>32</v>
       </c>
       <c r="BW4" t="n">
         <v>7.2</v>
@@ -1578,17 +1578,17 @@
         <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>55</v>
+        <v>8.6</v>
       </c>
       <c r="BZ4" t="n">
         <v>1000</v>
       </c>
       <c r="CA4" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1619,43 +1619,43 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="G5" t="n">
         <v>4.5</v>
       </c>
       <c r="H5" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="I5" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="J5" t="n">
         <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M5" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N5" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="O5" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
         <v>5.1</v>
@@ -1664,49 +1664,49 @@
         <v>2.04</v>
       </c>
       <c r="U5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="V5" t="n">
         <v>1.73</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.81</v>
-      </c>
       <c r="W5" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>9.4</v>
       </c>
       <c r="Y5" t="n">
         <v>7.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>970</v>
+        <v>13.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>900</v>
+        <v>44</v>
       </c>
       <c r="AB5" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="AC5" t="n">
         <v>7.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>21</v>
+        <v>12.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
         <v>500</v>
       </c>
       <c r="AG5" t="n">
-        <v>970</v>
+        <v>18.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="AI5" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="AJ5" t="n">
         <v>900</v>
@@ -1715,7 +1715,7 @@
         <v>500</v>
       </c>
       <c r="AL5" t="n">
-        <v>500</v>
+        <v>360</v>
       </c>
       <c r="AM5" t="n">
         <v>580</v>
@@ -1724,28 +1724,28 @@
         <v>600</v>
       </c>
       <c r="AO5" t="n">
-        <v>600</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5" t="n">
-        <v>4.2</v>
+        <v>6.2</v>
       </c>
       <c r="AR5" t="n">
         <v>10</v>
       </c>
       <c r="AS5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV5" t="n">
         <v>10</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>7.6</v>
       </c>
       <c r="AW5" t="n">
         <v>11.5</v>
@@ -1754,76 +1754,76 @@
         <v>12.5</v>
       </c>
       <c r="AY5" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="AZ5" t="n">
-        <v>6.6</v>
+        <v>19</v>
       </c>
       <c r="BA5" t="n">
         <v>15</v>
       </c>
       <c r="BB5" t="n">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC5" t="n">
-        <v>7.6</v>
+        <v>15</v>
       </c>
       <c r="BD5" t="n">
-        <v>7.8</v>
+        <v>42</v>
       </c>
       <c r="BE5" t="n">
+        <v>130</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>19</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>12</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>160</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF5" t="n">
-        <v>8</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="BI5" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="BJ5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BK5" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BL5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM5" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="BN5" t="n">
-        <v>970</v>
-      </c>
-      <c r="BO5" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ5" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BR5" t="n">
         <v>1000</v>
       </c>
       <c r="BS5" t="n">
-        <v>3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT5" t="n">
         <v>5</v>
       </c>
       <c r="BU5" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW5" t="n">
         <v>6.6</v>
@@ -1832,17 +1832,17 @@
         <v>1000</v>
       </c>
       <c r="BY5" t="n">
-        <v>4.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BZ5" t="n">
         <v>1000</v>
       </c>
       <c r="CA5" t="n">
-        <v>4.9</v>
+        <v>8.4</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -1873,19 +1873,19 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.22</v>
+        <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="H6" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="I6" t="n">
-        <v>4</v>
+        <v>3.55</v>
       </c>
       <c r="J6" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K6" t="n">
         <v>3.65</v>
@@ -1897,40 +1897,40 @@
         <v>1.09</v>
       </c>
       <c r="N6" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R6" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
         <v>1.83</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="W6" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>970</v>
+        <v>500</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1939,10 +1939,10 @@
         <v>900</v>
       </c>
       <c r="AB6" t="n">
-        <v>500</v>
+        <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,10 +1951,10 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>44</v>
+        <v>500</v>
       </c>
       <c r="AG6" t="n">
-        <v>970</v>
+        <v>34</v>
       </c>
       <c r="AH6" t="n">
         <v>970</v>
@@ -1981,55 +1981,55 @@
         <v>600</v>
       </c>
       <c r="AP6" t="n">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AQ6" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="AR6" t="n">
-        <v>6.2</v>
+        <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>3.15</v>
+        <v>7.4</v>
       </c>
       <c r="AT6" t="n">
-        <v>4.9</v>
+        <v>7.2</v>
       </c>
       <c r="AU6" t="n">
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>5.4</v>
+        <v>9</v>
       </c>
       <c r="AW6" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX6" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="AY6" t="n">
         <v>8.4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>5.6</v>
+        <v>8.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>2.16</v>
+        <v>5.8</v>
       </c>
       <c r="BB6" t="n">
-        <v>4.3</v>
+        <v>7.8</v>
       </c>
       <c r="BC6" t="n">
-        <v>2.94</v>
+        <v>6.6</v>
       </c>
       <c r="BD6" t="n">
-        <v>3.05</v>
+        <v>5.7</v>
       </c>
       <c r="BE6" t="n">
-        <v>3.15</v>
+        <v>5.3</v>
       </c>
       <c r="BF6" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
@@ -2038,19 +2038,19 @@
         <v>3.15</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.3</v>
+        <v>1.11</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2062,13 +2062,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.04</v>
+        <v>2.32</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.62</v>
+        <v>1.13</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2127,19 +2127,19 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="H7" t="n">
         <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>1.98</v>
+        <v>1.89</v>
       </c>
       <c r="J7" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K7" t="n">
         <v>3.95</v>
@@ -2148,16 +2148,16 @@
         <v>1.48</v>
       </c>
       <c r="M7" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O7" t="n">
         <v>1.42</v>
       </c>
       <c r="P7" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="Q7" t="n">
         <v>2.24</v>
@@ -2166,16 +2166,16 @@
         <v>1.25</v>
       </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="W7" t="n">
         <v>1.2</v>
@@ -2184,10 +2184,10 @@
         <v>17</v>
       </c>
       <c r="Y7" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="Z7" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="AA7" t="n">
         <v>900</v>
@@ -2244,46 +2244,46 @@
         <v>5.1</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.4</v>
+        <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>7.6</v>
+        <v>5.9</v>
       </c>
       <c r="AU7" t="n">
         <v>4.4</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.6</v>
+        <v>5</v>
       </c>
       <c r="AW7" t="n">
-        <v>5.3</v>
+        <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>4.3</v>
+        <v>2.16</v>
       </c>
       <c r="AY7" t="n">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>9.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="BB7" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="BD7" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="BE7" t="n">
-        <v>4.2</v>
+        <v>2.82</v>
       </c>
       <c r="BF7" t="n">
-        <v>3.15</v>
+        <v>2.2</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
@@ -2298,59 +2298,59 @@
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>1.64</v>
+        <v>5.3</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
       </c>
       <c r="BO7" t="n">
-        <v>3.25</v>
+        <v>4.6</v>
       </c>
       <c r="BP7" t="n">
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.51</v>
+        <v>1.19</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.04</v>
+        <v>1.19</v>
       </c>
       <c r="BT7" t="n">
         <v>1000</v>
       </c>
       <c r="BU7" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>1.57</v>
+        <v>5.8</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.51</v>
+        <v>1.21</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="H8" t="n">
         <v>3.1</v>
       </c>
       <c r="I8" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="K8" t="n">
         <v>3.45</v>
@@ -2414,19 +2414,19 @@
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="T8" t="n">
         <v>1.78</v>
       </c>
       <c r="U8" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="V8" t="n">
         <v>1.46</v>
@@ -2435,7 +2435,7 @@
         <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
@@ -2450,7 +2450,7 @@
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.8</v>
+        <v>7.2</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
@@ -2483,13 +2483,13 @@
         <v>110</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO8" t="n">
         <v>36</v>
       </c>
       <c r="AP8" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AQ8" t="n">
         <v>11</v>
@@ -2537,10 +2537,10 @@
         <v>65</v>
       </c>
       <c r="BF8" t="n">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH8" t="n">
         <v>3.4</v>
@@ -2552,13 +2552,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK8" t="n">
-        <v>7.2</v>
+        <v>5.2</v>
       </c>
       <c r="BL8" t="n">
         <v>1000</v>
       </c>
       <c r="BM8" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BN8" t="n">
         <v>5.7</v>
@@ -2567,34 +2567,34 @@
         <v>4.7</v>
       </c>
       <c r="BP8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BQ8" t="n">
         <v>7.2</v>
       </c>
       <c r="BR8" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BS8" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BT8" t="n">
         <v>6.4</v>
       </c>
       <c r="BU8" t="n">
-        <v>5.3</v>
+        <v>4.6</v>
       </c>
       <c r="BV8" t="n">
         <v>25</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BX8" t="n">
         <v>38</v>
       </c>
       <c r="BY8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2635,16 +2635,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H9" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I9" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="J9" t="n">
         <v>3.7</v>
@@ -2662,13 +2662,13 @@
         <v>4</v>
       </c>
       <c r="O9" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P9" t="n">
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
@@ -2677,22 +2677,22 @@
         <v>3.5</v>
       </c>
       <c r="T9" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U9" t="n">
         <v>2.1</v>
       </c>
       <c r="V9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="X9" t="n">
         <v>14</v>
       </c>
       <c r="Y9" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z9" t="n">
         <v>40</v>
@@ -2707,7 +2707,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE9" t="n">
         <v>70</v>
@@ -2722,13 +2722,13 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>320</v>
+        <v>700</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>19.5</v>
+        <v>23</v>
       </c>
       <c r="AL9" t="n">
         <v>38</v>
@@ -2737,25 +2737,25 @@
         <v>390</v>
       </c>
       <c r="AN9" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AP9" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AQ9" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AR9" t="n">
         <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="AT9" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU9" t="n">
         <v>7.6</v>
@@ -2764,7 +2764,7 @@
         <v>18.5</v>
       </c>
       <c r="AW9" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AX9" t="n">
         <v>10</v>
@@ -2773,25 +2773,25 @@
         <v>9.6</v>
       </c>
       <c r="AZ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB9" t="n">
         <v>17</v>
       </c>
-      <c r="BA9" t="n">
-        <v>60</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>18</v>
-      </c>
       <c r="BC9" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BD9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BE9" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BF9" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BG9" t="n">
         <v>65</v>
@@ -2812,7 +2812,7 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BN9" t="n">
         <v>4.5</v>
@@ -2824,7 +2824,7 @@
         <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BR9" t="n">
         <v>27</v>
@@ -2836,16 +2836,16 @@
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX9" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY9" t="n">
         <v>13</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -2895,55 +2895,55 @@
         <v>1.72</v>
       </c>
       <c r="H10" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
         <v>4.4</v>
       </c>
       <c r="L10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M10" t="n">
         <v>1.05</v>
       </c>
       <c r="N10" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O10" t="n">
         <v>1.25</v>
       </c>
       <c r="P10" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R10" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S10" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T10" t="n">
         <v>1.77</v>
       </c>
       <c r="U10" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="V10" t="n">
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Y10" t="n">
         <v>22</v>
@@ -2955,25 +2955,25 @@
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AC10" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>28</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>80</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG10" t="n">
         <v>9.6</v>
       </c>
-      <c r="AD10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>9.800000000000001</v>
-      </c>
       <c r="AH10" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI10" t="n">
         <v>320</v>
@@ -2982,7 +2982,7 @@
         <v>17.5</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL10" t="n">
         <v>44</v>
@@ -2991,7 +2991,7 @@
         <v>580</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AO10" t="n">
         <v>85</v>
@@ -3006,10 +3006,10 @@
         <v>38</v>
       </c>
       <c r="AS10" t="n">
-        <v>14.5</v>
+        <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU10" t="n">
         <v>8.6</v>
@@ -3018,13 +3018,13 @@
         <v>18</v>
       </c>
       <c r="AW10" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AZ10" t="n">
         <v>17</v>
@@ -3039,16 +3039,16 @@
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BE10" t="n">
-        <v>13.5</v>
+        <v>48</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BG10" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
@@ -3078,7 +3078,7 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BR10" t="n">
         <v>24</v>
@@ -3090,19 +3090,19 @@
         <v>9</v>
       </c>
       <c r="BU10" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="BV10" t="n">
         <v>44</v>
       </c>
       <c r="BW10" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BX10" t="n">
         <v>48</v>
       </c>
       <c r="BY10" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -3143,230 +3143,230 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>1.37</v>
       </c>
       <c r="G11" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="H11" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="I11" t="n">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="J11" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="K11" t="n">
-        <v>6</v>
+        <v>5.4</v>
       </c>
       <c r="L11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O11" t="n">
         <v>1.27</v>
       </c>
       <c r="P11" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="S11" t="n">
         <v>3.05</v>
       </c>
       <c r="T11" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="U11" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="V11" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="X11" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="Y11" t="n">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="Z11" t="n">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="AA11" t="n">
-        <v>1000</v>
+        <v>580</v>
       </c>
       <c r="AB11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="AE11" t="n">
-        <v>320</v>
+        <v>210</v>
       </c>
       <c r="AF11" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AG11" t="n">
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AI11" t="n">
-        <v>250</v>
+        <v>210</v>
       </c>
       <c r="AJ11" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="AK11" t="n">
         <v>16</v>
       </c>
       <c r="AL11" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>260</v>
+        <v>230</v>
       </c>
       <c r="AN11" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>510</v>
+        <v>310</v>
       </c>
       <c r="AP11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>36</v>
+      </c>
+      <c r="BE11" t="n">
         <v>16.5</v>
       </c>
-      <c r="AQ11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>11</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>13</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>11</v>
-      </c>
       <c r="BF11" t="n">
-        <v>5.2</v>
+        <v>5.7</v>
       </c>
       <c r="BG11" t="n">
-        <v>11.5</v>
+        <v>15</v>
       </c>
       <c r="BH11" t="n">
         <v>3.8</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BJ11" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BR11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BT11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ11" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="CA11" t="n">
         <v>7.8</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -3412,10 +3412,10 @@
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M12" t="n">
         <v>1.05</v>
@@ -3427,19 +3427,19 @@
         <v>1.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="T12" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="U12" t="n">
         <v>2.18</v>
@@ -3448,121 +3448,121 @@
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="X12" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="Y12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="Z12" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>700</v>
+        <v>180</v>
       </c>
       <c r="AB12" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC12" t="n">
         <v>10</v>
       </c>
       <c r="AD12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AE12" t="n">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="AF12" t="n">
         <v>10.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH12" t="n">
         <v>19.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AJ12" t="n">
         <v>15</v>
       </c>
       <c r="AK12" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM12" t="n">
         <v>95</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AO12" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AP12" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AR12" t="n">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="AS12" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="AT12" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV12" t="n">
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="AX12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AY12" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="AY12" t="n">
-        <v>9</v>
-      </c>
       <c r="AZ12" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BC12" t="n">
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BE12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BF12" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="BH12" t="n">
         <v>4.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ12" t="n">
         <v>10.5</v>
@@ -3574,13 +3574,13 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BN12" t="n">
         <v>4.4</v>
       </c>
       <c r="BO12" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="BP12" t="n">
         <v>10.5</v>
@@ -3592,7 +3592,7 @@
         <v>23</v>
       </c>
       <c r="BS12" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
@@ -3601,16 +3601,16 @@
         <v>5.2</v>
       </c>
       <c r="BV12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BW12" t="n">
         <v>8.6</v>
       </c>
       <c r="BX12" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3651,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
         <v>3.7</v>
@@ -3663,13 +3663,13 @@
         <v>2.2</v>
       </c>
       <c r="J13" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="K13" t="n">
         <v>3.7</v>
       </c>
-      <c r="K13" t="n">
-        <v>3.75</v>
-      </c>
       <c r="L13" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -3687,16 +3687,16 @@
         <v>1.77</v>
       </c>
       <c r="R13" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="S13" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T13" t="n">
         <v>1.65</v>
       </c>
       <c r="U13" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="V13" t="n">
         <v>1.83</v>
@@ -3741,7 +3741,7 @@
         <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AK13" t="n">
         <v>38</v>
@@ -3765,19 +3765,19 @@
         <v>11</v>
       </c>
       <c r="AR13" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AS13" t="n">
         <v>24</v>
       </c>
       <c r="AT13" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW13" t="n">
         <v>18.5</v>
@@ -3789,7 +3789,7 @@
         <v>13.5</v>
       </c>
       <c r="AZ13" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BA13" t="n">
         <v>28</v>
@@ -3804,7 +3804,7 @@
         <v>38</v>
       </c>
       <c r="BE13" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BF13" t="n">
         <v>26</v>
@@ -3813,7 +3813,7 @@
         <v>11.5</v>
       </c>
       <c r="BH13" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BI13" t="n">
         <v>3.1</v>
@@ -3822,49 +3822,49 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
       </c>
       <c r="BO13" t="n">
-        <v>5.8</v>
+        <v>4.3</v>
       </c>
       <c r="BP13" t="n">
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT13" t="n">
         <v>5.3</v>
       </c>
       <c r="BU13" t="n">
-        <v>4.5</v>
+        <v>3.95</v>
       </c>
       <c r="BV13" t="n">
         <v>15.5</v>
       </c>
       <c r="BW13" t="n">
-        <v>11</v>
+        <v>6.4</v>
       </c>
       <c r="BX13" t="n">
         <v>26</v>
       </c>
       <c r="BY13" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
         <v>9.4</v>
       </c>
       <c r="H14" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I14" t="n">
         <v>1.4</v>
@@ -3929,34 +3929,34 @@
         <v>1.03</v>
       </c>
       <c r="N14" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O14" t="n">
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="T14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U14" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="V14" t="n">
         <v>3.5</v>
       </c>
       <c r="W14" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="X14" t="n">
         <v>27</v>
@@ -4010,7 +4010,7 @@
         <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AP14" t="n">
         <v>24</v>
@@ -4028,7 +4028,7 @@
         <v>32</v>
       </c>
       <c r="AU14" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AV14" t="n">
         <v>9.6</v>
@@ -4049,76 +4049,76 @@
         <v>26</v>
       </c>
       <c r="BB14" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC14" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="BD14" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BE14" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BG14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BH14" t="n">
         <v>4.5</v>
       </c>
-      <c r="BH14" t="n">
-        <v>4.8</v>
-      </c>
       <c r="BI14" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="BJ14" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BK14" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BL14" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM14" t="n">
-        <v>9.199999999999999</v>
+        <v>14</v>
       </c>
       <c r="BN14" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO14" t="n">
-        <v>5.6</v>
+        <v>7</v>
       </c>
       <c r="BP14" t="n">
         <v>70</v>
       </c>
       <c r="BQ14" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BR14" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS14" t="n">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BT14" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="BU14" t="n">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="BV14" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="BX14" t="n">
         <v>21</v>
       </c>
       <c r="BY14" t="n">
-        <v>6.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ14" t="n">
         <v>0</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -4159,58 +4159,58 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="H15" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="I15" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="J15" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L15" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="M15" t="n">
         <v>1.06</v>
       </c>
       <c r="N15" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="P15" t="n">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="R15" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="S15" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="U15" t="n">
-        <v>1.98</v>
+        <v>2.1</v>
       </c>
       <c r="V15" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
@@ -4225,10 +4225,10 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC15" t="n">
-        <v>14</v>
+        <v>11.5</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -4237,7 +4237,7 @@
         <v>700</v>
       </c>
       <c r="AF15" t="n">
-        <v>17.5</v>
+        <v>40</v>
       </c>
       <c r="AG15" t="n">
         <v>36</v>
@@ -4249,7 +4249,7 @@
         <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>970</v>
+        <v>900</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -4267,67 +4267,67 @@
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>4.7</v>
+        <v>5.9</v>
       </c>
       <c r="AQ15" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD15" t="n">
         <v>6.6</v>
       </c>
-      <c r="AR15" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT15" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AU15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AV15" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AW15" t="n">
-        <v>6</v>
-      </c>
-      <c r="AX15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY15" t="n">
-        <v>5</v>
-      </c>
-      <c r="AZ15" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BA15" t="n">
-        <v>6</v>
-      </c>
-      <c r="BB15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BC15" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BD15" t="n">
+      <c r="BE15" t="n">
         <v>7.6</v>
       </c>
-      <c r="BE15" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BF15" t="n">
-        <v>5.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG15" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
       <c r="BH15" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="BJ15" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BK15" t="n">
         <v>5.2</v>
@@ -4336,16 +4336,16 @@
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>3.6</v>
+        <v>2.72</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BO15" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="BP15" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ15" t="n">
         <v>5.7</v>
@@ -4354,35 +4354,35 @@
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>3.3</v>
+        <v>7.6</v>
       </c>
       <c r="BT15" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BU15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BV15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW15" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BX15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY15" t="n">
         <v>8.6</v>
       </c>
-      <c r="BU15" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BV15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW15" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BX15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY15" t="n">
-        <v>3.5</v>
-      </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.2</v>
+        <v>7</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="G16" t="n">
         <v>3.1</v>
       </c>
-      <c r="G16" t="n">
-        <v>3.25</v>
-      </c>
       <c r="H16" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
         <v>2.78</v>
@@ -4437,13 +4437,13 @@
         <v>1.12</v>
       </c>
       <c r="N16" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O16" t="n">
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="Q16" t="n">
         <v>2.56</v>
@@ -4452,19 +4452,19 @@
         <v>1.21</v>
       </c>
       <c r="S16" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="T16" t="n">
         <v>2.08</v>
       </c>
       <c r="U16" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V16" t="n">
         <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4479,10 +4479,10 @@
         <v>48</v>
       </c>
       <c r="AB16" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD16" t="n">
         <v>14.5</v>
@@ -4494,7 +4494,7 @@
         <v>23</v>
       </c>
       <c r="AG16" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AH16" t="n">
         <v>25</v>
@@ -4524,25 +4524,25 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AQ16" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="AS16" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="AT16" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AU16" t="n">
         <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>11</v>
+        <v>5.2</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AX16" t="n">
         <v>17</v>
@@ -4551,28 +4551,28 @@
         <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>19</v>
+        <v>5.3</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BB16" t="n">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BC16" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BD16" t="n">
         <v>6</v>
       </c>
-      <c r="BD16" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE16" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="BH16" t="n">
         <v>2.76</v>
@@ -4584,13 +4584,13 @@
         <v>11</v>
       </c>
       <c r="BK16" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BL16" t="n">
         <v>1000</v>
       </c>
       <c r="BM16" t="n">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="BN16" t="n">
         <v>6</v>
@@ -4602,13 +4602,13 @@
         <v>1000</v>
       </c>
       <c r="BQ16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR16" t="n">
         <v>1000</v>
       </c>
       <c r="BS16" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BT16" t="n">
         <v>5.8</v>
@@ -4617,7 +4617,7 @@
         <v>5.1</v>
       </c>
       <c r="BV16" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BW16" t="n">
         <v>9.6</v>
@@ -4626,17 +4626,17 @@
         <v>1000</v>
       </c>
       <c r="BY16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BZ16" t="n">
         <v>1000</v>
       </c>
       <c r="CA16" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-23 01:40:18</t>
+          <t>2026-06-23 03:47:57</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="G2" t="n">
-        <v>2.08</v>
+        <v>1.89</v>
       </c>
       <c r="H2" t="n">
-        <v>4.1</v>
+        <v>8.4</v>
       </c>
       <c r="I2" t="n">
-        <v>4.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>3.35</v>
+        <v>2.76</v>
       </c>
       <c r="K2" t="n">
-        <v>3.65</v>
+        <v>2.9</v>
       </c>
       <c r="L2" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="N2" t="n">
-        <v>3.3</v>
+        <v>1.68</v>
       </c>
       <c r="O2" t="n">
-        <v>1.39</v>
+        <v>2.38</v>
       </c>
       <c r="P2" t="n">
-        <v>1.74</v>
+        <v>1.17</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.18</v>
+        <v>6.4</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3</v>
+        <v>1.04</v>
       </c>
       <c r="S2" t="n">
-        <v>4.1</v>
+        <v>19.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.91</v>
+        <v>4.7</v>
       </c>
       <c r="U2" t="n">
-        <v>1.94</v>
+        <v>1.18</v>
       </c>
       <c r="V2" t="n">
-        <v>1.27</v>
+        <v>1.11</v>
       </c>
       <c r="W2" t="n">
-        <v>1.92</v>
+        <v>2.12</v>
       </c>
       <c r="X2" t="n">
-        <v>21</v>
+        <v>4.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>500</v>
+        <v>14</v>
       </c>
       <c r="Z2" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA2" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>27</v>
+        <v>3.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>500</v>
+        <v>80</v>
       </c>
       <c r="AE2" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>40</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AG2" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="AH2" t="n">
+        <v>130</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>32</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>80</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>530</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>370</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>410</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>90</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>290</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>55</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>280</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>420</v>
+      </c>
+      <c r="BF2" t="n">
         <v>60</v>
       </c>
-      <c r="AI2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>130</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>700</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>9</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>95</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>16.5</v>
-      </c>
       <c r="BG2" t="n">
-        <v>3.3</v>
+        <v>240</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="G3" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="H3" t="n">
-        <v>2.36</v>
+        <v>3.65</v>
       </c>
       <c r="I3" t="n">
-        <v>2.66</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>2.58</v>
+        <v>1.99</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>2.06</v>
       </c>
       <c r="L3" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.19</v>
+        <v>1.63</v>
       </c>
       <c r="N3" t="n">
-        <v>2.22</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>1.72</v>
+        <v>4.1</v>
       </c>
       <c r="P3" t="n">
-        <v>1.41</v>
+        <v>1.06</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.2</v>
+        <v>14.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>7.2</v>
+        <v>80</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>6</v>
       </c>
       <c r="U3" t="n">
-        <v>1.58</v>
+        <v>1.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6</v>
+        <v>1.34</v>
       </c>
       <c r="W3" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X3" t="n">
-        <v>6.6</v>
+        <v>2.6</v>
       </c>
       <c r="Y3" t="n">
-        <v>7.4</v>
+        <v>5.4</v>
       </c>
       <c r="Z3" t="n">
+        <v>27</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>200</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>65</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>480</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>300</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>570</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>22</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AX3" t="n">
         <v>26</v>
       </c>
-      <c r="AA3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>970</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>38</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>28</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>7</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>12.5</v>
-      </c>
       <c r="AY3" t="n">
-        <v>3.6</v>
+        <v>30</v>
       </c>
       <c r="AZ3" t="n">
-        <v>3.75</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
-        <v>4.1</v>
+        <v>270</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.1</v>
+        <v>11.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.1</v>
+        <v>300</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.2</v>
+        <v>450</v>
       </c>
       <c r="BE3" t="n">
-        <v>210</v>
+        <v>11</v>
       </c>
       <c r="BF3" t="n">
-        <v>7.8</v>
+        <v>430</v>
       </c>
       <c r="BG3" t="n">
-        <v>34</v>
+        <v>280</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>270</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1365,230 +1365,230 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.92</v>
+        <v>3.6</v>
       </c>
       <c r="G4" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6</v>
+        <v>3.25</v>
       </c>
       <c r="I4" t="n">
-        <v>2.92</v>
+        <v>3.45</v>
       </c>
       <c r="J4" t="n">
-        <v>2.92</v>
+        <v>2.24</v>
       </c>
       <c r="K4" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>3.35</v>
       </c>
-      <c r="L4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="N4" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q4" t="n">
-        <v>2.54</v>
+        <v>1.41</v>
       </c>
       <c r="R4" t="n">
-        <v>1.2</v>
+        <v>1.48</v>
       </c>
       <c r="S4" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>9</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>34</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>25</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>130</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>65</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
         <v>5.2</v>
       </c>
-      <c r="T4" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="X4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>15</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>23</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>160</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>500</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>150</v>
-      </c>
-      <c r="AP4" t="n">
+      <c r="AZ4" t="n">
         <v>7.8</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AY4" t="n">
+      <c r="BA4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB4" t="n">
         <v>12</v>
       </c>
-      <c r="AZ4" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>29</v>
-      </c>
       <c r="BC4" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BD4" t="n">
         <v>28</v>
       </c>
       <c r="BE4" t="n">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="BF4" t="n">
-        <v>8.6</v>
+        <v>55</v>
       </c>
       <c r="BG4" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="BH4" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BK4" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN4" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="BP4" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BT4" t="n">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="BU4" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="BX4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1619,230 +1619,230 @@
         </is>
       </c>
       <c r="F5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="K5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="O5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>10</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="S5" t="n">
+        <v>42</v>
+      </c>
+      <c r="T5" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="X5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>95</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>34</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>210</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>70</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>450</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>630</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>350</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>3.9</v>
       </c>
-      <c r="G5" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="P5" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S5" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="T5" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U5" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>44</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AD5" t="n">
+      <c r="AR5" t="n">
         <v>12.5</v>
       </c>
-      <c r="AE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="AF5" t="n">
+      <c r="AS5" t="n">
+        <v>60</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>120</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>38</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>46</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>100</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>290</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>490</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>440</v>
+      </c>
+      <c r="BF5" t="n">
         <v>500</v>
       </c>
-      <c r="AG5" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>42</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>450</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>360</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>70</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>15</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>15</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>42</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>130</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BG5" t="n">
-        <v>19</v>
+        <v>140</v>
       </c>
       <c r="BH5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="BN5" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="BP5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="BT5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU5" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="BV5" t="n">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -1876,37 +1876,37 @@
         <v>2.34</v>
       </c>
       <c r="G6" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="H6" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="J6" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="L6" t="n">
         <v>1.48</v>
       </c>
       <c r="M6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="O6" t="n">
         <v>1.4</v>
       </c>
       <c r="P6" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R6" t="n">
         <v>1.25</v>
@@ -1915,22 +1915,22 @@
         <v>4.1</v>
       </c>
       <c r="T6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>1.9</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="W6" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="X6" t="n">
         <v>22</v>
       </c>
       <c r="Y6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="Z6" t="n">
         <v>500</v>
@@ -1942,7 +1942,7 @@
         <v>19</v>
       </c>
       <c r="AC6" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="n">
         <v>970</v>
@@ -1951,10 +1951,10 @@
         <v>500</v>
       </c>
       <c r="AF6" t="n">
-        <v>500</v>
+        <v>970</v>
       </c>
       <c r="AG6" t="n">
-        <v>34</v>
+        <v>970</v>
       </c>
       <c r="AH6" t="n">
         <v>970</v>
@@ -1990,67 +1990,67 @@
         <v>8.4</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AT6" t="n">
-        <v>7.2</v>
+        <v>4.9</v>
       </c>
       <c r="AU6" t="n">
         <v>4.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>9</v>
+        <v>6.8</v>
       </c>
       <c r="AW6" t="n">
-        <v>6.2</v>
+        <v>15.5</v>
       </c>
       <c r="AX6" t="n">
         <v>7.6</v>
       </c>
       <c r="AY6" t="n">
-        <v>8.4</v>
+        <v>5.1</v>
       </c>
       <c r="AZ6" t="n">
         <v>8.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="BB6" t="n">
         <v>7.8</v>
       </c>
       <c r="BC6" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>100</v>
+      </c>
+      <c r="BF6" t="n">
         <v>6.6</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>7</v>
       </c>
       <c r="BG6" t="n">
         <v>9</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="BJ6" t="n">
         <v>1000</v>
       </c>
       <c r="BK6" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BL6" t="n">
         <v>1000</v>
       </c>
       <c r="BM6" t="n">
-        <v>1.11</v>
+        <v>130</v>
       </c>
       <c r="BN6" t="n">
         <v>1000</v>
@@ -2062,13 +2062,13 @@
         <v>1000</v>
       </c>
       <c r="BQ6" t="n">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="BR6" t="n">
         <v>1000</v>
       </c>
       <c r="BS6" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="BT6" t="n">
         <v>1000</v>
@@ -2080,23 +2080,23 @@
         <v>1000</v>
       </c>
       <c r="BW6" t="n">
-        <v>1.13</v>
+        <v>1.63</v>
       </c>
       <c r="BX6" t="n">
         <v>1000</v>
       </c>
       <c r="BY6" t="n">
-        <v>1.11</v>
+        <v>40</v>
       </c>
       <c r="BZ6" t="n">
         <v>1000</v>
       </c>
       <c r="CA6" t="n">
-        <v>1.1</v>
+        <v>1.57</v>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2127,16 +2127,16 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="G7" t="n">
         <v>6.4</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="I7" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -2145,46 +2145,46 @@
         <v>3.95</v>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="M7" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N7" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="O7" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="P7" t="n">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R7" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S7" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="U7" t="n">
         <v>1.82</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="W7" t="n">
         <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y7" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="Z7" t="n">
         <v>40</v>
@@ -2196,7 +2196,7 @@
         <v>970</v>
       </c>
       <c r="AC7" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="AD7" t="n">
         <v>30</v>
@@ -2211,7 +2211,7 @@
         <v>950</v>
       </c>
       <c r="AH7" t="n">
-        <v>85</v>
+        <v>950</v>
       </c>
       <c r="AI7" t="n">
         <v>500</v>
@@ -2229,16 +2229,16 @@
         <v>580</v>
       </c>
       <c r="AN7" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="AO7" t="n">
         <v>85</v>
       </c>
       <c r="AP7" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR7" t="n">
         <v>5.1</v>
@@ -2247,64 +2247,64 @@
         <v>9</v>
       </c>
       <c r="AT7" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AW7" t="n">
         <v>10</v>
       </c>
       <c r="AX7" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.8</v>
+        <v>5.1</v>
       </c>
       <c r="AZ7" t="n">
         <v>9.6</v>
       </c>
       <c r="BA7" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="BB7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BC7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>2.2</v>
+        <v>2.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>2.82</v>
+        <v>100</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="BG7" t="n">
         <v>4.6</v>
       </c>
       <c r="BH7" t="n">
-        <v>3.15</v>
+        <v>3.3</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="BJ7" t="n">
         <v>1000</v>
       </c>
       <c r="BK7" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="BL7" t="n">
         <v>1000</v>
       </c>
       <c r="BM7" t="n">
-        <v>1.18</v>
+        <v>130</v>
       </c>
       <c r="BN7" t="n">
         <v>1000</v>
@@ -2316,16 +2316,16 @@
         <v>1000</v>
       </c>
       <c r="BQ7" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="BR7" t="n">
         <v>1000</v>
       </c>
       <c r="BS7" t="n">
-        <v>1.19</v>
+        <v>1.06</v>
       </c>
       <c r="BT7" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BU7" t="n">
         <v>3.35</v>
@@ -2334,23 +2334,23 @@
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="BZ7" t="n">
         <v>1000</v>
       </c>
       <c r="CA7" t="n">
-        <v>1.21</v>
+        <v>1.59</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2384,46 +2384,46 @@
         <v>2.56</v>
       </c>
       <c r="G8" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H8" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="J8" t="n">
         <v>3.35</v>
       </c>
       <c r="K8" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L8" t="n">
         <v>1.44</v>
       </c>
       <c r="M8" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N8" t="n">
         <v>3.75</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P8" t="n">
         <v>1.9</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="R8" t="n">
         <v>1.34</v>
       </c>
       <c r="S8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="T8" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U8" t="n">
         <v>2.18</v>
@@ -2435,7 +2435,7 @@
         <v>1.62</v>
       </c>
       <c r="X8" t="n">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="Y8" t="n">
         <v>12.5</v>
@@ -2450,13 +2450,13 @@
         <v>11</v>
       </c>
       <c r="AC8" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
         <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AF8" t="n">
         <v>16.5</v>
@@ -2468,16 +2468,16 @@
         <v>17.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ8" t="n">
         <v>38</v>
       </c>
       <c r="AK8" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL8" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AM8" t="n">
         <v>110</v>
@@ -2486,7 +2486,7 @@
         <v>26</v>
       </c>
       <c r="AO8" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AP8" t="n">
         <v>12</v>
@@ -2501,7 +2501,7 @@
         <v>40</v>
       </c>
       <c r="AT8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
         <v>6.8</v>
@@ -2516,7 +2516,7 @@
         <v>14</v>
       </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8" t="n">
         <v>15</v>
@@ -2528,7 +2528,7 @@
         <v>30</v>
       </c>
       <c r="BC8" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
         <v>34</v>
@@ -2537,7 +2537,7 @@
         <v>65</v>
       </c>
       <c r="BF8" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG8" t="n">
         <v>27</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2638,22 +2638,22 @@
         <v>1.82</v>
       </c>
       <c r="G9" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="M9" t="n">
         <v>1.07</v>
@@ -2665,52 +2665,52 @@
         <v>1.31</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="R9" t="n">
         <v>1.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="T9" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="U9" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W9" t="n">
         <v>2.18</v>
       </c>
       <c r="X9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Y9" t="n">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="Z9" t="n">
         <v>40</v>
       </c>
       <c r="AA9" t="n">
-        <v>130</v>
+        <v>900</v>
       </c>
       <c r="AB9" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF9" t="n">
         <v>11</v>
@@ -2722,37 +2722,37 @@
         <v>18.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>700</v>
+        <v>75</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL9" t="n">
         <v>38</v>
       </c>
       <c r="AM9" t="n">
-        <v>390</v>
+        <v>110</v>
       </c>
       <c r="AN9" t="n">
         <v>11.5</v>
       </c>
       <c r="AO9" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AP9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR9" t="n">
         <v>34</v>
       </c>
       <c r="AS9" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="AT9" t="n">
         <v>8.199999999999999</v>
@@ -2761,7 +2761,7 @@
         <v>7.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AW9" t="n">
         <v>60</v>
@@ -2770,13 +2770,13 @@
         <v>10</v>
       </c>
       <c r="AY9" t="n">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ9" t="n">
         <v>18</v>
       </c>
       <c r="BA9" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="BB9" t="n">
         <v>17</v>
@@ -2794,13 +2794,13 @@
         <v>10.5</v>
       </c>
       <c r="BG9" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="BH9" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="BJ9" t="n">
         <v>10</v>
@@ -2812,10 +2812,10 @@
         <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BN9" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO9" t="n">
         <v>4</v>
@@ -2824,32 +2824,32 @@
         <v>12.5</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BR9" t="n">
         <v>27</v>
       </c>
       <c r="BS9" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BT9" t="n">
         <v>8.4</v>
       </c>
       <c r="BU9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="BV9" t="n">
         <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX9" t="n">
+        <v>55</v>
+      </c>
+      <c r="BY9" t="n">
         <v>50</v>
       </c>
-      <c r="BY9" t="n">
-        <v>13</v>
-      </c>
       <c r="BZ9" t="n">
         <v>0</v>
       </c>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G10" t="n">
         <v>1.72</v>
@@ -2898,7 +2898,7 @@
         <v>5.4</v>
       </c>
       <c r="I10" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
       <c r="J10" t="n">
         <v>4.2</v>
@@ -2916,22 +2916,22 @@
         <v>4.8</v>
       </c>
       <c r="O10" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="P10" t="n">
         <v>2.28</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S10" t="n">
         <v>2.92</v>
       </c>
       <c r="T10" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U10" t="n">
         <v>2.24</v>
@@ -2940,34 +2940,34 @@
         <v>1.21</v>
       </c>
       <c r="W10" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Y10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA10" t="n">
         <v>900</v>
       </c>
       <c r="AB10" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AC10" t="n">
         <v>9.4</v>
       </c>
       <c r="AD10" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AE10" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="AF10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG10" t="n">
         <v>9.6</v>
@@ -2976,7 +2976,7 @@
         <v>18.5</v>
       </c>
       <c r="AI10" t="n">
-        <v>320</v>
+        <v>90</v>
       </c>
       <c r="AJ10" t="n">
         <v>17.5</v>
@@ -2985,70 +2985,70 @@
         <v>16.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="AM10" t="n">
-        <v>580</v>
+        <v>320</v>
       </c>
       <c r="AN10" t="n">
         <v>8.4</v>
       </c>
       <c r="AO10" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AQ10" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR10" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AS10" t="n">
         <v>42</v>
       </c>
       <c r="AT10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AU10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV10" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AW10" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AX10" t="n">
         <v>10</v>
       </c>
       <c r="AY10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ10" t="n">
         <v>17</v>
       </c>
       <c r="BA10" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB10" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BC10" t="n">
         <v>15</v>
       </c>
       <c r="BD10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BE10" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="BF10" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BG10" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BH10" t="n">
         <v>3.85</v>
@@ -3060,13 +3060,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL10" t="n">
         <v>1000</v>
       </c>
       <c r="BM10" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BN10" t="n">
         <v>4.4</v>
@@ -3078,31 +3078,31 @@
         <v>11</v>
       </c>
       <c r="BQ10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR10" t="n">
         <v>24</v>
       </c>
       <c r="BS10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BT10" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BU10" t="n">
         <v>6.4</v>
       </c>
       <c r="BV10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>13</v>
+      </c>
+      <c r="BX10" t="n">
         <v>44</v>
       </c>
-      <c r="BW10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>48</v>
-      </c>
       <c r="BY10" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -3143,82 +3143,82 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="G11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H11" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="I11" t="n">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="J11" t="n">
         <v>5.1</v>
       </c>
       <c r="K11" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="L11" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N11" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P11" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="R11" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>3.05</v>
+        <v>2.92</v>
       </c>
       <c r="T11" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="U11" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="V11" t="n">
         <v>1.08</v>
       </c>
       <c r="W11" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="X11" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>100</v>
+        <v>34</v>
       </c>
       <c r="Z11" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA11" t="n">
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="AB11" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AC11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AD11" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AE11" t="n">
-        <v>210</v>
+        <v>250</v>
       </c>
       <c r="AF11" t="n">
         <v>8</v>
@@ -3227,146 +3227,146 @@
         <v>11</v>
       </c>
       <c r="AH11" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AI11" t="n">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AJ11" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK11" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL11" t="n">
         <v>44</v>
       </c>
       <c r="AM11" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AN11" t="n">
         <v>6</v>
       </c>
       <c r="AO11" t="n">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="AP11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AR11" t="n">
-        <v>11.5</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AT11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AU11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AV11" t="n">
-        <v>11.5</v>
+        <v>34</v>
       </c>
       <c r="AW11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AX11" t="n">
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BB11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BC11" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD11" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BE11" t="n">
-        <v>16.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF11" t="n">
-        <v>5.7</v>
+        <v>5.4</v>
       </c>
       <c r="BG11" t="n">
         <v>15</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BI11" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="BJ11" t="n">
         <v>12.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BN11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BO11" t="n">
         <v>3.35</v>
       </c>
       <c r="BP11" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="BR11" t="n">
         <v>26</v>
       </c>
       <c r="BS11" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BU11" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BV11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BW11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BX11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BY11" t="n">
+        <v>15</v>
+      </c>
+      <c r="BZ11" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="CA11" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="BV11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BW11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BX11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BZ11" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="CA11" t="n">
-        <v>7.8</v>
-      </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="G12" t="n">
         <v>1.6</v>
@@ -3406,52 +3406,52 @@
         <v>6.4</v>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
         <v>4.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L12" t="n">
         <v>1.32</v>
       </c>
       <c r="M12" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="R12" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="S12" t="n">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="T12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U12" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V12" t="n">
         <v>1.17</v>
       </c>
       <c r="W12" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Y12" t="n">
         <v>27</v>
@@ -3460,7 +3460,7 @@
         <v>55</v>
       </c>
       <c r="AA12" t="n">
-        <v>180</v>
+        <v>700</v>
       </c>
       <c r="AB12" t="n">
         <v>11</v>
@@ -3478,7 +3478,7 @@
         <v>10.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AH12" t="n">
         <v>19.5</v>
@@ -3526,7 +3526,7 @@
         <v>21</v>
       </c>
       <c r="AW12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="AX12" t="n">
         <v>9.6</v>
@@ -3538,7 +3538,7 @@
         <v>18</v>
       </c>
       <c r="BA12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="BB12" t="n">
         <v>13.5</v>
@@ -3547,7 +3547,7 @@
         <v>14</v>
       </c>
       <c r="BD12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
@@ -3568,13 +3568,13 @@
         <v>10.5</v>
       </c>
       <c r="BK12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BL12" t="n">
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN12" t="n">
         <v>4.4</v>
@@ -3583,34 +3583,34 @@
         <v>3.5</v>
       </c>
       <c r="BP12" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BR12" t="n">
         <v>23</v>
       </c>
       <c r="BS12" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BT12" t="n">
         <v>10.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BV12" t="n">
         <v>50</v>
       </c>
       <c r="BW12" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BX12" t="n">
         <v>55</v>
       </c>
       <c r="BY12" t="n">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BZ12" t="n">
         <v>0</v>
@@ -3620,7 +3620,7 @@
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -3651,40 +3651,40 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="G13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="I13" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="L13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
       </c>
       <c r="N13" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O13" t="n">
         <v>1.25</v>
       </c>
       <c r="P13" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
         <v>1.5</v>
@@ -3699,118 +3699,118 @@
         <v>2.46</v>
       </c>
       <c r="V13" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="W13" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="X13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y13" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z13" t="n">
         <v>14</v>
       </c>
-      <c r="Z13" t="n">
-        <v>15</v>
-      </c>
       <c r="AA13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AB13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AC13" t="n">
         <v>8.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AE13" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AF13" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AG13" t="n">
+        <v>16</v>
+      </c>
+      <c r="AH13" t="n">
         <v>15.5</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>16</v>
       </c>
       <c r="AI13" t="n">
         <v>32</v>
       </c>
       <c r="AJ13" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AK13" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="AL13" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM13" t="n">
         <v>75</v>
       </c>
       <c r="AN13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AO13" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP13" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AS13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT13" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AU13" t="n">
         <v>8</v>
       </c>
       <c r="AV13" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AW13" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX13" t="n">
         <v>24</v>
       </c>
       <c r="AY13" t="n">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AZ13" t="n">
         <v>14</v>
       </c>
       <c r="BA13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB13" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BC13" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="BD13" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BE13" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="BF13" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BG13" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BH13" t="n">
         <v>4.1</v>
@@ -3822,13 +3822,13 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BK13" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BL13" t="n">
         <v>1000</v>
       </c>
       <c r="BM13" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BN13" t="n">
         <v>7.2</v>
@@ -3840,13 +3840,13 @@
         <v>27</v>
       </c>
       <c r="BQ13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BR13" t="n">
         <v>36</v>
       </c>
       <c r="BS13" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BT13" t="n">
         <v>5.3</v>
@@ -3855,7 +3855,7 @@
         <v>3.95</v>
       </c>
       <c r="BV13" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BW13" t="n">
         <v>6.4</v>
@@ -3864,7 +3864,7 @@
         <v>26</v>
       </c>
       <c r="BY13" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BZ13" t="n">
         <v>0</v>
@@ -3874,7 +3874,7 @@
       </c>
       <c r="CB13" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -3932,19 +3932,19 @@
         <v>6</v>
       </c>
       <c r="O14" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R14" t="n">
         <v>1.67</v>
       </c>
       <c r="S14" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="T14" t="n">
         <v>1.86</v>
@@ -3965,7 +3965,7 @@
         <v>11</v>
       </c>
       <c r="Z14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AA14" t="n">
         <v>12</v>
@@ -3980,7 +3980,7 @@
         <v>10.5</v>
       </c>
       <c r="AE14" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF14" t="n">
         <v>85</v>
@@ -4010,7 +4010,7 @@
         <v>120</v>
       </c>
       <c r="AO14" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="AP14" t="n">
         <v>24</v>
@@ -4037,7 +4037,7 @@
         <v>12.5</v>
       </c>
       <c r="AX14" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AY14" t="n">
         <v>29</v>
@@ -4049,7 +4049,7 @@
         <v>26</v>
       </c>
       <c r="BB14" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC14" t="n">
         <v>50</v>
@@ -4061,7 +4061,7 @@
         <v>55</v>
       </c>
       <c r="BF14" t="n">
-        <v>16.5</v>
+        <v>50</v>
       </c>
       <c r="BG14" t="n">
         <v>4.6</v>
@@ -4128,7 +4128,7 @@
       </c>
       <c r="CB14" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -4162,19 +4162,19 @@
         <v>1.74</v>
       </c>
       <c r="G15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="H15" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="I15" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J15" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>1.38</v>
@@ -4186,37 +4186,37 @@
         <v>4.2</v>
       </c>
       <c r="O15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="R15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
         <v>3.15</v>
       </c>
       <c r="T15" t="n">
-        <v>1.79</v>
+        <v>1.84</v>
       </c>
       <c r="U15" t="n">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="V15" t="n">
         <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>2.3</v>
+        <v>2.22</v>
       </c>
       <c r="X15" t="n">
         <v>32</v>
       </c>
       <c r="Y15" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="Z15" t="n">
         <v>500</v>
@@ -4225,10 +4225,10 @@
         <v>900</v>
       </c>
       <c r="AB15" t="n">
-        <v>9.800000000000001</v>
+        <v>27</v>
       </c>
       <c r="AC15" t="n">
-        <v>11.5</v>
+        <v>9</v>
       </c>
       <c r="AD15" t="n">
         <v>950</v>
@@ -4237,10 +4237,10 @@
         <v>700</v>
       </c>
       <c r="AF15" t="n">
-        <v>40</v>
+        <v>17.5</v>
       </c>
       <c r="AG15" t="n">
-        <v>36</v>
+        <v>11.5</v>
       </c>
       <c r="AH15" t="n">
         <v>60</v>
@@ -4249,7 +4249,7 @@
         <v>700</v>
       </c>
       <c r="AJ15" t="n">
-        <v>900</v>
+        <v>970</v>
       </c>
       <c r="AK15" t="n">
         <v>970</v>
@@ -4267,122 +4267,122 @@
         <v>700</v>
       </c>
       <c r="AP15" t="n">
-        <v>5.9</v>
+        <v>8.6</v>
       </c>
       <c r="AQ15" t="n">
-        <v>6.4</v>
+        <v>14.5</v>
       </c>
       <c r="AR15" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="AT15" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU15" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="AV15" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AX15" t="n">
         <v>7.6</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.2</v>
+        <v>7.6</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BA15" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="BB15" t="n">
-        <v>6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="BD15" t="n">
-        <v>6.6</v>
+        <v>14</v>
       </c>
       <c r="BE15" t="n">
-        <v>7.6</v>
+        <v>8.4</v>
       </c>
       <c r="BF15" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BG15" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BH15" t="n">
         <v>3.75</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="BJ15" t="n">
         <v>10.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BL15" t="n">
         <v>1000</v>
       </c>
       <c r="BM15" t="n">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BO15" t="n">
         <v>3.45</v>
       </c>
       <c r="BP15" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BR15" t="n">
         <v>1000</v>
       </c>
       <c r="BS15" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT15" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BU15" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BV15" t="n">
         <v>1000</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.4</v>
+        <v>2.68</v>
       </c>
       <c r="BX15" t="n">
         <v>1000</v>
       </c>
       <c r="BY15" t="n">
-        <v>8.6</v>
+        <v>2.7</v>
       </c>
       <c r="BZ15" t="n">
         <v>1000</v>
       </c>
       <c r="CA15" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="CB15" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="I16" t="n">
         <v>2.78</v>
@@ -4443,7 +4443,7 @@
         <v>1.51</v>
       </c>
       <c r="P16" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="Q16" t="n">
         <v>2.56</v>
@@ -4464,7 +4464,7 @@
         <v>1.56</v>
       </c>
       <c r="W16" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X16" t="n">
         <v>9.4</v>
@@ -4527,7 +4527,7 @@
         <v>7.6</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AS16" t="n">
         <v>5.7</v>
@@ -4539,7 +4539,7 @@
         <v>6.4</v>
       </c>
       <c r="AV16" t="n">
-        <v>5.2</v>
+        <v>11</v>
       </c>
       <c r="AW16" t="n">
         <v>5.9</v>
@@ -4551,7 +4551,7 @@
         <v>12.5</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5.3</v>
+        <v>18.5</v>
       </c>
       <c r="BA16" t="n">
         <v>5.9</v>
@@ -4636,7 +4636,7 @@
       </c>
       <c r="CB16" t="inlineStr">
         <is>
-          <t>2026-06-23 03:47:57</t>
+          <t>2026-06-23 05:55:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.54</v>
+        <v>1.03</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="H2" t="n">
-        <v>2.52</v>
+        <v>75</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88</v>
+        <v>1000</v>
       </c>
       <c r="J2" t="n">
-        <v>3.45</v>
+        <v>27</v>
       </c>
       <c r="K2" t="n">
-        <v>3.95</v>
+        <v>40</v>
       </c>
       <c r="L2" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="T2" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W2" t="n">
+        <v>23</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>46</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>7</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>260</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AX2" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q2" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="X2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AY2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>29</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="BC2" t="n">
         <v>18</v>
       </c>
-      <c r="AE2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AF2" t="n">
+      <c r="BD2" t="n">
+        <v>10</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>110</v>
+      </c>
+      <c r="BF2" t="n">
         <v>30</v>
       </c>
-      <c r="AG2" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>970</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>500</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>900</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>180</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>290</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>600</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>9</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>80</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BG2" t="n">
-        <v>9</v>
+        <v>220</v>
       </c>
       <c r="BH2" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BP2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="BV2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1111,230 +1111,230 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>4.5</v>
+        <v>7.8</v>
       </c>
       <c r="G3" t="n">
-        <v>5.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>1.86</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>1.97</v>
+        <v>3.85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>1.61</v>
       </c>
       <c r="K3" t="n">
-        <v>3.85</v>
+        <v>1.67</v>
       </c>
       <c r="L3" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.08</v>
+        <v>2.48</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>1.09</v>
       </c>
       <c r="O3" t="n">
-        <v>1.38</v>
+        <v>11</v>
       </c>
       <c r="P3" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.14</v>
+        <v>50</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>3.9</v>
+        <v>280</v>
       </c>
       <c r="T3" t="n">
-        <v>1.92</v>
+        <v>14.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.53</v>
+        <v>1.05</v>
       </c>
       <c r="V3" t="n">
-        <v>2.36</v>
+        <v>1.33</v>
       </c>
       <c r="W3" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="X3" t="n">
-        <v>12</v>
+        <v>1.72</v>
       </c>
       <c r="Y3" t="n">
-        <v>8.4</v>
+        <v>4.7</v>
       </c>
       <c r="Z3" t="n">
+        <v>38</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>560</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>990</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>160</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>520</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>25</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>21</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>120</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>95</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>180</v>
+      </c>
+      <c r="AZ3" t="n">
         <v>11.5</v>
       </c>
-      <c r="AA3" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>27</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>55</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>29</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>290</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>240</v>
-      </c>
-      <c r="AL3" t="n">
+      <c r="BA3" t="n">
+        <v>230</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>210</v>
+      </c>
+      <c r="BD3" t="n">
         <v>120</v>
       </c>
-      <c r="AM3" t="n">
-        <v>580</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>600</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>20</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>26</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>70</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>55</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>29</v>
-      </c>
       <c r="BE3" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BF3" t="n">
-        <v>55</v>
+        <v>16.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>8.800000000000001</v>
+        <v>15</v>
       </c>
       <c r="BH3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="BN3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.56</v>
+        <v>2.14</v>
       </c>
       <c r="G4" t="n">
-        <v>2.6</v>
+        <v>2.16</v>
       </c>
       <c r="H4" t="n">
-        <v>3.05</v>
+        <v>3.9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="M4" t="n">
         <v>1.08</v>
@@ -1392,193 +1392,193 @@
         <v>3.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="P4" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R4" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S4" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="T4" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="U4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="V4" t="n">
-        <v>1.46</v>
+        <v>1.33</v>
       </c>
       <c r="W4" t="n">
-        <v>1.62</v>
+        <v>1.86</v>
       </c>
       <c r="X4" t="n">
         <v>13.5</v>
       </c>
       <c r="Y4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>28</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>48</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>27</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>42</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
         <v>12.5</v>
       </c>
-      <c r="Z4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>55</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AE4" t="n">
+      <c r="AR4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>46</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AW4" t="n">
         <v>38</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AX4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AZ4" t="n">
         <v>16.5</v>
       </c>
-      <c r="AG4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>50</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK4" t="n">
+      <c r="BA4" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>21</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>32</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="BG4" t="n">
         <v>30</v>
       </c>
-      <c r="AL4" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>36</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>27</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AU4" t="n">
+      <c r="BH4" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK4" t="n">
         <v>7</v>
       </c>
-      <c r="AV4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>27</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>22</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>25</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>34</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>21</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>5.1</v>
-      </c>
       <c r="BL4" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM4" t="n">
         <v>24</v>
       </c>
       <c r="BN4" t="n">
-        <v>5.7</v>
+        <v>1000</v>
       </c>
       <c r="BO4" t="n">
-        <v>4.7</v>
+        <v>2.32</v>
       </c>
       <c r="BP4" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>7</v>
+        <v>2.32</v>
       </c>
       <c r="BR4" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="BS4" t="n">
-        <v>8.199999999999999</v>
+        <v>1.28</v>
       </c>
       <c r="BT4" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="BU4" t="n">
-        <v>5.2</v>
+        <v>1.89</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.4</v>
+        <v>2.02</v>
       </c>
       <c r="BX4" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BY4" t="n">
-        <v>8.4</v>
+        <v>2.1</v>
       </c>
       <c r="BZ4" t="n">
         <v>0</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1619,19 +1619,19 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="G5" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="I5" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
         <v>3.95</v>
@@ -1640,19 +1640,19 @@
         <v>1.4</v>
       </c>
       <c r="M5" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P5" t="n">
         <v>2.04</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="R5" t="n">
         <v>1.39</v>
@@ -1667,151 +1667,151 @@
         <v>2.12</v>
       </c>
       <c r="V5" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="W5" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="X5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z5" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AA5" t="n">
-        <v>120</v>
+        <v>200</v>
       </c>
       <c r="AB5" t="n">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI5" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ5" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>20</v>
       </c>
       <c r="AL5" t="n">
         <v>36</v>
       </c>
       <c r="AM5" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AN5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO5" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AP5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AQ5" t="n">
         <v>14.5</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AR5" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>90</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AV5" t="n">
         <v>16.5</v>
       </c>
-      <c r="AR5" t="n">
-        <v>34</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>18</v>
-      </c>
       <c r="AW5" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AX5" t="n">
         <v>10</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ5" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA5" t="n">
         <v>60</v>
       </c>
       <c r="BB5" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE5" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="BF5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BG5" t="n">
         <v>55</v>
       </c>
       <c r="BH5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BK5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BL5" t="n">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="BM5" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="BN5" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BO5" t="n">
         <v>4</v>
       </c>
       <c r="BP5" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BR5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BS5" t="n">
         <v>21</v>
@@ -1823,16 +1823,16 @@
         <v>7.4</v>
       </c>
       <c r="BV5" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW5" t="n">
-        <v>13.5</v>
+        <v>28</v>
       </c>
       <c r="BX5" t="n">
         <v>55</v>
       </c>
       <c r="BY5" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ5" t="n">
         <v>0</v>
@@ -1842,7 +1842,7 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -1873,22 +1873,22 @@
         </is>
       </c>
       <c r="F6" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="G6" t="n">
         <v>1.7</v>
       </c>
-      <c r="G6" t="n">
-        <v>1.72</v>
-      </c>
       <c r="H6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I6" t="n">
         <v>5.6</v>
       </c>
       <c r="J6" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
         <v>1.34</v>
@@ -1897,22 +1897,22 @@
         <v>1.05</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="P6" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="R6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S6" t="n">
-        <v>2.82</v>
+        <v>2.74</v>
       </c>
       <c r="T6" t="n">
         <v>1.73</v>
@@ -1924,7 +1924,7 @@
         <v>1.21</v>
       </c>
       <c r="W6" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X6" t="n">
         <v>21</v>
@@ -1933,7 +1933,7 @@
         <v>24</v>
       </c>
       <c r="Z6" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
         <v>130</v>
@@ -1942,7 +1942,7 @@
         <v>11</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6" t="n">
         <v>21</v>
@@ -1957,55 +1957,55 @@
         <v>9.6</v>
       </c>
       <c r="AH6" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL6" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM6" t="n">
         <v>85</v>
       </c>
       <c r="AN6" t="n">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AO6" t="n">
         <v>60</v>
       </c>
       <c r="AP6" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AR6" t="n">
         <v>40</v>
       </c>
       <c r="AS6" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AT6" t="n">
         <v>10</v>
       </c>
       <c r="AU6" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW6" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AY6" t="n">
         <v>9.199999999999999</v>
@@ -2014,7 +2014,7 @@
         <v>16.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BB6" t="n">
         <v>15.5</v>
@@ -2023,70 +2023,70 @@
         <v>14.5</v>
       </c>
       <c r="BD6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="BE6" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BF6" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BG6" t="n">
         <v>48</v>
       </c>
       <c r="BH6" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BI6" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BJ6" t="n">
         <v>9.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BL6" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BM6" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BN6" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BP6" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.8</v>
+        <v>8.6</v>
       </c>
       <c r="BR6" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BS6" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT6" t="n">
         <v>9</v>
       </c>
       <c r="BU6" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="BV6" t="n">
         <v>42</v>
       </c>
       <c r="BW6" t="n">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="BX6" t="n">
         <v>44</v>
       </c>
       <c r="BY6" t="n">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="BZ6" t="n">
         <v>0</v>
@@ -2096,7 +2096,7 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2127,230 +2127,230 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="G7" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="H7" t="n">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="I7" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="J7" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="M7" t="n">
         <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P7" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R7" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="T7" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="U7" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="V7" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="X7" t="n">
+        <v>32</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>95</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>160</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>950</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>130</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>370</v>
+      </c>
+      <c r="AF7" t="n">
         <v>970</v>
       </c>
-      <c r="Y7" t="n">
-        <v>950</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>150</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>530</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>8</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>42</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>220</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>40</v>
-      </c>
       <c r="AG7" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="AH7" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="AI7" t="n">
+        <v>300</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>180</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AK7" t="n">
+        <v>970</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>120</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>370</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>650</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC7" t="n">
         <v>14</v>
       </c>
-      <c r="AK7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>500</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>260</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="AU7" t="n">
+      <c r="BD7" t="n">
+        <v>15</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>16</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>28</v>
+      </c>
+      <c r="BS7" t="n">
         <v>10.5</v>
       </c>
-      <c r="AV7" t="n">
-        <v>36</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>34</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>15</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>3</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>25</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>9.4</v>
-      </c>
       <c r="BT7" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BU7" t="n">
-        <v>7.2</v>
+        <v>10.5</v>
       </c>
       <c r="BV7" t="n">
         <v>1000</v>
       </c>
       <c r="BW7" t="n">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BX7" t="n">
         <v>1000</v>
       </c>
       <c r="BY7" t="n">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BZ7" t="n">
         <v>13</v>
       </c>
       <c r="CA7" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2381,220 +2381,220 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="G8" t="n">
-        <v>1.6</v>
+        <v>1.69</v>
       </c>
       <c r="H8" t="n">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="I8" t="n">
-        <v>6.6</v>
+        <v>5.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N8" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="O8" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="R8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="S8" t="n">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="T8" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="U8" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="V8" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="X8" t="n">
         <v>22</v>
       </c>
       <c r="Y8" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Z8" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AA8" t="n">
-        <v>700</v>
+        <v>140</v>
       </c>
       <c r="AB8" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>65</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AG8" t="n">
         <v>10.5</v>
       </c>
-      <c r="AC8" t="n">
-        <v>10</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>80</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>10</v>
-      </c>
       <c r="AH8" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI8" t="n">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="AJ8" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="AK8" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="AL8" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AM8" t="n">
+        <v>85</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AS8" t="n">
         <v>95</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>90</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>46</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>44</v>
       </c>
       <c r="AT8" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AU8" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AW8" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>15</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>46</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BS8" t="n">
         <v>9.6</v>
       </c>
-      <c r="AY8" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>55</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>14</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>26</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>60</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>36</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>23</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>6.6</v>
-      </c>
       <c r="BT8" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BU8" t="n">
-        <v>5</v>
+        <v>7.8</v>
       </c>
       <c r="BV8" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW8" t="n">
-        <v>8</v>
+        <v>1.04</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY8" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="BZ8" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2635,58 +2635,58 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="H9" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="I9" t="n">
-        <v>2.08</v>
+        <v>1.97</v>
       </c>
       <c r="J9" t="n">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="M9" t="n">
         <v>1.05</v>
       </c>
       <c r="N9" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="O9" t="n">
         <v>1.24</v>
       </c>
       <c r="P9" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="S9" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="T9" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="U9" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="X9" t="n">
         <v>21</v>
@@ -2695,91 +2695,91 @@
         <v>12</v>
       </c>
       <c r="Z9" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AB9" t="n">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>8.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD9" t="n">
         <v>10.5</v>
       </c>
       <c r="AE9" t="n">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="AG9" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="AH9" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AI9" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="AJ9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="AK9" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AL9" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM9" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN9" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO9" t="n">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="AQ9" t="n">
         <v>10.5</v>
       </c>
       <c r="AR9" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW9" t="n">
         <v>16</v>
       </c>
-      <c r="AU9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>18</v>
-      </c>
       <c r="AX9" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AY9" t="n">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AZ9" t="n">
         <v>14.5</v>
       </c>
       <c r="BA9" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="BB9" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="BC9" t="n">
         <v>36</v>
@@ -2788,67 +2788,67 @@
         <v>40</v>
       </c>
       <c r="BE9" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="BF9" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="BG9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BH9" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BK9" t="n">
-        <v>5.9</v>
+        <v>1.04</v>
       </c>
       <c r="BL9" t="n">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="BM9" t="n">
-        <v>9.4</v>
+        <v>20</v>
       </c>
       <c r="BN9" t="n">
-        <v>7.4</v>
+        <v>1000</v>
       </c>
       <c r="BO9" t="n">
-        <v>6</v>
+        <v>1.04</v>
       </c>
       <c r="BP9" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ9" t="n">
-        <v>7.6</v>
+        <v>1.04</v>
       </c>
       <c r="BR9" t="n">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BS9" t="n">
-        <v>8</v>
+        <v>12.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="BU9" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV9" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="BX9" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="BY9" t="n">
-        <v>7.4</v>
+        <v>1.04</v>
       </c>
       <c r="BZ9" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2889,16 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G10" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H10" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="I10" t="n">
         <v>1.38</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.39</v>
       </c>
       <c r="J10" t="n">
         <v>6</v>
@@ -2913,58 +2913,58 @@
         <v>1.03</v>
       </c>
       <c r="N10" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="O10" t="n">
         <v>1.16</v>
       </c>
       <c r="P10" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R10" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T10" t="n">
         <v>1.76</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1.8</v>
-      </c>
       <c r="U10" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V10" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="W10" t="n">
         <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="Y10" t="n">
         <v>12.5</v>
       </c>
       <c r="Z10" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>13</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>40</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>14</v>
+      </c>
+      <c r="AD10" t="n">
         <v>10.5</v>
       </c>
-      <c r="AA10" t="n">
-        <v>12</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>10</v>
-      </c>
       <c r="AE10" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AF10" t="n">
         <v>85</v>
@@ -2973,40 +2973,40 @@
         <v>32</v>
       </c>
       <c r="AH10" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AI10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>300</v>
+        <v>260</v>
       </c>
       <c r="AK10" t="n">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AL10" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>90</v>
+      </c>
+      <c r="AN10" t="n">
         <v>85</v>
       </c>
-      <c r="AM10" t="n">
-        <v>100</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>95</v>
-      </c>
       <c r="AO10" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AP10" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AQ10" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AR10" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AS10" t="n">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AT10" t="n">
         <v>34</v>
@@ -3015,43 +3015,43 @@
         <v>13</v>
       </c>
       <c r="AV10" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW10" t="n">
         <v>12</v>
       </c>
       <c r="AX10" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="AY10" t="n">
         <v>29</v>
       </c>
       <c r="AZ10" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BA10" t="n">
         <v>24</v>
       </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="BC10" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="BD10" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="BE10" t="n">
         <v>55</v>
       </c>
       <c r="BF10" t="n">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="BG10" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BH10" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BI10" t="n">
         <v>4.2</v>
@@ -3060,7 +3060,7 @@
         <v>11</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL10" t="n">
         <v>110</v>
@@ -3069,40 +3069,40 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BO10" t="n">
-        <v>5.8</v>
+        <v>10</v>
       </c>
       <c r="BP10" t="n">
         <v>65</v>
       </c>
       <c r="BQ10" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BR10" t="n">
         <v>60</v>
       </c>
       <c r="BS10" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT10" t="n">
         <v>4.4</v>
       </c>
       <c r="BU10" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="BV10" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="BW10" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="BX10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BY10" t="n">
-        <v>6.8</v>
+        <v>14</v>
       </c>
       <c r="BZ10" t="n">
         <v>0</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -3143,49 +3143,49 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="G11" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="H11" t="n">
         <v>5</v>
       </c>
       <c r="I11" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J11" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K11" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="M11" t="n">
         <v>1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P11" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="R11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="T11" t="n">
-        <v>1.81</v>
+        <v>1.64</v>
       </c>
       <c r="U11" t="n">
         <v>1.6</v>
@@ -3194,179 +3194,179 @@
         <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="X11" t="n">
-        <v>32</v>
+        <v>970</v>
       </c>
       <c r="Y11" t="n">
-        <v>970</v>
+        <v>23</v>
       </c>
       <c r="Z11" t="n">
-        <v>500</v>
+        <v>95</v>
       </c>
       <c r="AA11" t="n">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="AB11" t="n">
         <v>10</v>
       </c>
       <c r="AC11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AD11" t="n">
-        <v>75</v>
+        <v>950</v>
       </c>
       <c r="AE11" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AF11" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG11" t="n">
         <v>12.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>60</v>
+        <v>950</v>
       </c>
       <c r="AI11" t="n">
-        <v>700</v>
+        <v>160</v>
       </c>
       <c r="AJ11" t="n">
-        <v>120</v>
+        <v>970</v>
       </c>
       <c r="AK11" t="n">
         <v>24</v>
       </c>
       <c r="AL11" t="n">
-        <v>500</v>
+        <v>85</v>
       </c>
       <c r="AM11" t="n">
-        <v>580</v>
+        <v>1000</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>10.5</v>
       </c>
       <c r="AO11" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AP11" t="n">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14</v>
+        <v>3.8</v>
       </c>
       <c r="AR11" t="n">
-        <v>5.7</v>
+        <v>3.9</v>
       </c>
       <c r="AS11" t="n">
-        <v>6.2</v>
+        <v>2.9</v>
       </c>
       <c r="AT11" t="n">
         <v>4.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV11" t="n">
-        <v>10</v>
+        <v>3.4</v>
       </c>
       <c r="AW11" t="n">
-        <v>5.7</v>
+        <v>3.1</v>
       </c>
       <c r="AX11" t="n">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ11" t="n">
-        <v>9.199999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="BA11" t="n">
-        <v>5.6</v>
+        <v>3.15</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.199999999999999</v>
+        <v>4.5</v>
       </c>
       <c r="BC11" t="n">
-        <v>7.8</v>
+        <v>3.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="BE11" t="n">
-        <v>5.9</v>
+        <v>3.15</v>
       </c>
       <c r="BF11" t="n">
         <v>7.6</v>
       </c>
       <c r="BG11" t="n">
-        <v>5.7</v>
+        <v>2.76</v>
       </c>
       <c r="BH11" t="n">
-        <v>3.8</v>
+        <v>1000</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.92</v>
+        <v>1.13</v>
       </c>
       <c r="BJ11" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK11" t="n">
-        <v>5.1</v>
+        <v>1.13</v>
       </c>
       <c r="BL11" t="n">
         <v>1000</v>
       </c>
       <c r="BM11" t="n">
-        <v>9.4</v>
+        <v>1.13</v>
       </c>
       <c r="BN11" t="n">
-        <v>4.6</v>
+        <v>1000</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.4</v>
+        <v>1.13</v>
       </c>
       <c r="BP11" t="n">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5.4</v>
+        <v>1.13</v>
       </c>
       <c r="BR11" t="n">
         <v>1000</v>
       </c>
       <c r="BS11" t="n">
-        <v>7.2</v>
+        <v>1.13</v>
       </c>
       <c r="BT11" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="BU11" t="n">
-        <v>4.8</v>
+        <v>1.04</v>
       </c>
       <c r="BV11" t="n">
         <v>1000</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.199999999999999</v>
+        <v>1.13</v>
       </c>
       <c r="BX11" t="n">
         <v>1000</v>
       </c>
       <c r="BY11" t="n">
-        <v>8.4</v>
+        <v>1.13</v>
       </c>
       <c r="BZ11" t="n">
         <v>1000</v>
       </c>
       <c r="CA11" t="n">
-        <v>6.8</v>
+        <v>1.13</v>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="G12" t="n">
         <v>3.25</v>
@@ -3406,7 +3406,7 @@
         <v>2.68</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="J12" t="n">
         <v>3.1</v>
@@ -3415,7 +3415,7 @@
         <v>3.2</v>
       </c>
       <c r="L12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
         <v>1.12</v>
@@ -3424,34 +3424,34 @@
         <v>2.86</v>
       </c>
       <c r="O12" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="P12" t="n">
         <v>1.6</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R12" t="n">
         <v>1.21</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="U12" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V12" t="n">
         <v>1.56</v>
       </c>
       <c r="W12" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="X12" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="Y12" t="n">
         <v>970</v>
@@ -3475,7 +3475,7 @@
         <v>1000</v>
       </c>
       <c r="AF12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AG12" t="n">
         <v>970</v>
@@ -3496,13 +3496,13 @@
         <v>1000</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AO12" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP12" t="n">
         <v>8.199999999999999</v>
@@ -3511,13 +3511,13 @@
         <v>7.6</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.86</v>
+        <v>14.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AT12" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU12" t="n">
         <v>6.4</v>
@@ -3526,43 +3526,43 @@
         <v>11</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="AX12" t="n">
-        <v>17.5</v>
+        <v>3.65</v>
       </c>
       <c r="AY12" t="n">
         <v>12</v>
       </c>
       <c r="AZ12" t="n">
-        <v>18.5</v>
+        <v>1.85</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.51</v>
+        <v>1.85</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.51</v>
+        <v>2</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="BF12" t="n">
-        <v>2.22</v>
+        <v>1.95</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="BH12" t="n">
         <v>2.76</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="BJ12" t="n">
         <v>11</v>
@@ -3574,7 +3574,7 @@
         <v>1000</v>
       </c>
       <c r="BM12" t="n">
-        <v>12</v>
+        <v>2.32</v>
       </c>
       <c r="BN12" t="n">
         <v>6</v>
@@ -3586,7 +3586,7 @@
         <v>1000</v>
       </c>
       <c r="BQ12" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BR12" t="n">
         <v>1000</v>
@@ -3616,11 +3616,11 @@
         <v>1000</v>
       </c>
       <c r="CA12" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>2026-06-23 08:02:52</t>
+          <t>2026-06-23 10:10:04</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,13 +857,13 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="I2" t="n">
         <v>2.8</v>
@@ -875,19 +875,19 @@
         <v>3.2</v>
       </c>
       <c r="L2" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="M2" t="n">
         <v>1.12</v>
       </c>
       <c r="N2" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="O2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="P2" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="Q2" t="n">
         <v>2.56</v>
@@ -902,31 +902,31 @@
         <v>2.06</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="V2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="W2" t="n">
         <v>1.46</v>
       </c>
       <c r="X2" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="Y2" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>17</v>
       </c>
       <c r="AA2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AB2" t="n">
         <v>9.6</v>
       </c>
       <c r="AC2" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AD2" t="n">
         <v>13</v>
@@ -938,13 +938,13 @@
         <v>19.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AI2" t="n">
-        <v>65</v>
+        <v>110</v>
       </c>
       <c r="AJ2" t="n">
         <v>60</v>
@@ -953,16 +953,16 @@
         <v>55</v>
       </c>
       <c r="AL2" t="n">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="AM2" t="n">
-        <v>150</v>
+        <v>170</v>
       </c>
       <c r="AN2" t="n">
-        <v>55</v>
+        <v>990</v>
       </c>
       <c r="AO2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP2" t="n">
         <v>8.4</v>
@@ -980,13 +980,13 @@
         <v>8.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="AV2" t="n">
         <v>11.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
         <v>17</v>
@@ -995,37 +995,37 @@
         <v>12.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA2" t="n">
         <v>50</v>
       </c>
       <c r="BB2" t="n">
+        <v>48</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD2" t="n">
         <v>42</v>
       </c>
-      <c r="BC2" t="n">
-        <v>34</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>27</v>
-      </c>
       <c r="BE2" t="n">
-        <v>11.5</v>
+        <v>18</v>
       </c>
       <c r="BF2" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="BG2" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="BJ2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BK2" t="n">
         <v>9.4</v>
@@ -1046,13 +1046,13 @@
         <v>28</v>
       </c>
       <c r="BQ2" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>15.5</v>
+        <v>13.5</v>
       </c>
       <c r="BT2" t="n">
         <v>5.8</v>
@@ -1064,23 +1064,23 @@
         <v>24</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY2" t="n">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="BZ2" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="CA2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 16:32:01</t>
+          <t>2026-06-23 18:39:09</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -857,230 +857,230 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.05</v>
+        <v>13</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>14.5</v>
       </c>
       <c r="H2" t="n">
-        <v>2.78</v>
+        <v>1.41</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>1.44</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="R2" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S2" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="V2" t="n">
         <v>3.2</v>
       </c>
-      <c r="L2" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N2" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="S2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1.55</v>
-      </c>
       <c r="W2" t="n">
-        <v>1.46</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.800000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="Z2" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AA2" t="n">
         <v>17</v>
       </c>
-      <c r="AA2" t="n">
-        <v>50</v>
-      </c>
       <c r="AB2" t="n">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.8</v>
+        <v>5.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>13</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AE2" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AF2" t="n">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AG2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>95</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>140</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>160</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>430</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>460</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AS2" t="n">
         <v>14.5</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AT2" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AW2" t="n">
         <v>22</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AX2" t="n">
+        <v>20</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>65</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>20</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>75</v>
+      </c>
+      <c r="BD2" t="n">
         <v>110</v>
       </c>
-      <c r="AJ2" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>55</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>170</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>990</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>44</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>38</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>48</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>38</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>42</v>
-      </c>
       <c r="BE2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF2" t="n">
-        <v>15</v>
+        <v>200</v>
       </c>
       <c r="BG2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BH2" t="n">
-        <v>2.76</v>
+        <v>1000</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.64</v>
+        <v>6</v>
       </c>
       <c r="BJ2" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BK2" t="n">
-        <v>9.4</v>
+        <v>5.3</v>
       </c>
       <c r="BL2" t="n">
         <v>1000</v>
       </c>
       <c r="BM2" t="n">
-        <v>70</v>
+        <v>5.4</v>
       </c>
       <c r="BN2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="BO2" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BP2" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BR2" t="n">
         <v>1000</v>
       </c>
       <c r="BS2" t="n">
-        <v>13.5</v>
+        <v>5.4</v>
       </c>
       <c r="BT2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BU2" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BV2" t="n">
+        <v>890</v>
+      </c>
+      <c r="BW2" t="n">
         <v>5.8</v>
       </c>
-      <c r="BU2" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>24</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>10</v>
-      </c>
       <c r="BX2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="BY2" t="n">
-        <v>12.5</v>
+        <v>5.4</v>
       </c>
       <c r="BZ2" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="CA2" t="n">
-        <v>13</v>
+        <v>5.4</v>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>2026-06-23 18:39:09</t>
+          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-06-23.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -827,260 +827,6 @@
       <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>SnapshotTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Brazilian Serie B</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>20:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>America MG</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Criciuma</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>13</v>
-      </c>
-      <c r="G2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="I2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="J2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="K2" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="N2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O2" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="R2" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S2" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U2" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="V2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="W2" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>17</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>95</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>140</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>160</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>430</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>460</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>34</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>19</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>22</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>22</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>65</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>20</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>75</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>110</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>19</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>200</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>29</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>970</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>6</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>890</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>2026-06-23 20:46:34</t>
         </is>
       </c>
     </row>
